--- a/public/archivos/SmartTuClick-Plantilla-Importacion-Productos.xlsx
+++ b/public/archivos/SmartTuClick-Plantilla-Importacion-Productos.xlsx
@@ -73,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -82,6 +82,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:K1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -460,6 +463,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +517,11 @@
           <t>Stock mínimo</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de afectación IGV</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="F2" t="inlineStr">
@@ -524,6 +533,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="F3" t="inlineStr">
@@ -535,6 +545,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="F4" t="inlineStr">
@@ -546,6 +557,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="F5" t="inlineStr">
@@ -557,6 +569,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="F6" t="inlineStr">
@@ -568,6 +581,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="F7" t="inlineStr">
@@ -579,6 +593,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="F8" t="inlineStr">
@@ -590,6 +605,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="F9" t="inlineStr">
@@ -601,6 +617,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="F10" t="inlineStr">
@@ -612,6 +629,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="F11" t="inlineStr">
@@ -623,6 +641,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="F12" t="inlineStr">
@@ -634,6 +653,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="F13" t="inlineStr">
@@ -645,6 +665,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="F14" t="inlineStr">
@@ -656,6 +677,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="F15" t="inlineStr">
@@ -667,6 +689,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="F16" t="inlineStr">
@@ -678,6 +701,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="F17" t="inlineStr">
@@ -689,6 +713,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="F18" t="inlineStr">
@@ -700,6 +725,7 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="F19" t="inlineStr">
@@ -711,6 +737,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="F20" t="inlineStr">
@@ -722,6 +749,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="F21" t="inlineStr">
@@ -733,6 +761,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="F22" t="inlineStr">
@@ -744,6 +773,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="F23" t="inlineStr">
@@ -755,6 +785,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="F24" t="inlineStr">
@@ -766,6 +797,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="F25" t="inlineStr">
@@ -777,6 +809,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="F26" t="inlineStr">
@@ -788,6 +821,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="F27" t="inlineStr">
@@ -799,6 +833,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="F28" t="inlineStr">
@@ -810,6 +845,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="F29" t="inlineStr">
@@ -821,6 +857,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="F30" t="inlineStr">
@@ -832,6 +869,7 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="F31" t="inlineStr">
@@ -843,6 +881,7 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="F32" t="inlineStr">
@@ -854,6 +893,7 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="F33" t="inlineStr">
@@ -865,6 +905,7 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="F34" t="inlineStr">
@@ -876,6 +917,7 @@
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="F35" t="inlineStr">
@@ -887,6 +929,7 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="F36" t="inlineStr">
@@ -898,6 +941,7 @@
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="F37" t="inlineStr">
@@ -909,6 +953,7 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="F38" t="inlineStr">
@@ -920,6 +965,7 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="F39" t="inlineStr">
@@ -931,6 +977,7 @@
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="F40" t="inlineStr">
@@ -942,6 +989,7 @@
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="F41" t="inlineStr">
@@ -953,6 +1001,7 @@
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="F42" t="inlineStr">
@@ -964,6 +1013,7 @@
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="F43" t="inlineStr">
@@ -975,6 +1025,7 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="F44" t="inlineStr">
@@ -986,6 +1037,7 @@
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="F45" t="inlineStr">
@@ -997,6 +1049,7 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="F46" t="inlineStr">
@@ -1008,6 +1061,7 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="F47" t="inlineStr">
@@ -1019,6 +1073,7 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="F48" t="inlineStr">
@@ -1030,6 +1085,7 @@
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="F49" t="inlineStr">
@@ -1041,6 +1097,7 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="F50" t="inlineStr">
@@ -1052,6 +1109,7 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="F51" t="inlineStr">
@@ -1063,6 +1121,7 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="F52" t="inlineStr">
@@ -1074,6 +1133,7 @@
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="F53" t="inlineStr">
@@ -1085,6 +1145,7 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="F54" t="inlineStr">
@@ -1096,6 +1157,7 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="F55" t="inlineStr">
@@ -1107,6 +1169,7 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="F56" t="inlineStr">
@@ -1118,6 +1181,7 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="F57" t="inlineStr">
@@ -1129,6 +1193,7 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="F58" t="inlineStr">
@@ -1140,6 +1205,7 @@
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="F59" t="inlineStr">
@@ -1151,6 +1217,7 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="F60" t="inlineStr">
@@ -1162,6 +1229,7 @@
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="F61" t="inlineStr">
@@ -1173,6 +1241,7 @@
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="3" t="n"/>
       <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="F62" t="inlineStr">
@@ -1184,6 +1253,7 @@
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="F63" t="inlineStr">
@@ -1195,6 +1265,7 @@
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="F64" t="inlineStr">
@@ -1206,6 +1277,7 @@
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="3" t="n"/>
       <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="F65" t="inlineStr">
@@ -1217,6 +1289,7 @@
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="F66" t="inlineStr">
@@ -1228,6 +1301,7 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="F67" t="inlineStr">
@@ -1239,6 +1313,7 @@
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="F68" t="inlineStr">
@@ -1250,6 +1325,7 @@
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="F69" t="inlineStr">
@@ -1261,6 +1337,7 @@
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="F70" t="inlineStr">
@@ -1272,6 +1349,7 @@
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="F71" t="inlineStr">
@@ -1283,6 +1361,7 @@
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="F72" t="inlineStr">
@@ -1294,6 +1373,7 @@
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="3" t="n"/>
       <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="F73" t="inlineStr">
@@ -1305,6 +1385,7 @@
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="F74" t="inlineStr">
@@ -1316,6 +1397,7 @@
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="3" t="n"/>
       <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="F75" t="inlineStr">
@@ -1327,6 +1409,7 @@
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="F76" t="inlineStr">
@@ -1338,6 +1421,7 @@
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="F77" t="inlineStr">
@@ -1349,6 +1433,7 @@
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="F78" t="inlineStr">
@@ -1360,6 +1445,7 @@
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="F79" t="inlineStr">
@@ -1371,6 +1457,7 @@
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="F80" t="inlineStr">
@@ -1382,6 +1469,7 @@
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="F81" t="inlineStr">
@@ -1393,6 +1481,7 @@
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="F82" t="inlineStr">
@@ -1404,6 +1493,7 @@
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="F83" t="inlineStr">
@@ -1415,6 +1505,7 @@
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="F84" t="inlineStr">
@@ -1426,6 +1517,7 @@
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="3" t="n"/>
       <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="F85" t="inlineStr">
@@ -1437,6 +1529,7 @@
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="3" t="n"/>
       <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="F86" t="inlineStr">
@@ -1448,6 +1541,7 @@
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="3" t="n"/>
       <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="F87" t="inlineStr">
@@ -1459,6 +1553,7 @@
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="F88" t="inlineStr">
@@ -1470,6 +1565,7 @@
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="F89" t="inlineStr">
@@ -1481,6 +1577,7 @@
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="F90" t="inlineStr">
@@ -1492,6 +1589,7 @@
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="F91" t="inlineStr">
@@ -1503,6 +1601,7 @@
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="3" t="n"/>
       <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="F92" t="inlineStr">
@@ -1514,6 +1613,7 @@
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="3" t="n"/>
       <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="F93" t="inlineStr">
@@ -1525,6 +1625,7 @@
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="F94" t="inlineStr">
@@ -1536,6 +1637,7 @@
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="F95" t="inlineStr">
@@ -1547,6 +1649,7 @@
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="3" t="n"/>
       <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="F96" t="inlineStr">
@@ -1558,6 +1661,7 @@
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="3" t="n"/>
       <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="F97" t="inlineStr">
@@ -1569,6 +1673,7 @@
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="F98" t="inlineStr">
@@ -1580,6 +1685,7 @@
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="3" t="n"/>
       <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="F99" t="inlineStr">
@@ -1591,6 +1697,7 @@
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="3" t="n"/>
       <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="F100" t="inlineStr">
@@ -1602,6 +1709,7 @@
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="3" t="n"/>
       <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="F101" t="inlineStr">
@@ -1613,6 +1721,7 @@
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="3" t="n"/>
       <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="F102" t="inlineStr">
@@ -1624,6 +1733,7 @@
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="F103" t="inlineStr">
@@ -1635,6 +1745,7 @@
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="F104" t="inlineStr">
@@ -1646,6 +1757,7 @@
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="F105" t="inlineStr">
@@ -1657,6 +1769,7 @@
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="3" t="n"/>
       <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="F106" t="inlineStr">
@@ -1668,6 +1781,7 @@
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="F107" t="inlineStr">
@@ -1679,6 +1793,7 @@
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="F108" t="inlineStr">
@@ -1690,6 +1805,7 @@
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="F109" t="inlineStr">
@@ -1701,6 +1817,7 @@
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="F110" t="inlineStr">
@@ -1712,6 +1829,7 @@
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="F111" t="inlineStr">
@@ -1723,6 +1841,7 @@
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="F112" t="inlineStr">
@@ -1734,6 +1853,7 @@
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="3" t="n"/>
       <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="F113" t="inlineStr">
@@ -1745,6 +1865,7 @@
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="3" t="n"/>
       <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="F114" t="inlineStr">
@@ -1756,6 +1877,7 @@
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="F115" t="inlineStr">
@@ -1767,6 +1889,7 @@
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="F116" t="inlineStr">
@@ -1778,6 +1901,7 @@
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="F117" t="inlineStr">
@@ -1789,6 +1913,7 @@
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="F118" t="inlineStr">
@@ -1800,6 +1925,7 @@
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="F119" t="inlineStr">
@@ -1811,6 +1937,7 @@
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="F120" t="inlineStr">
@@ -1822,6 +1949,7 @@
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="F121" t="inlineStr">
@@ -1833,6 +1961,7 @@
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="F122" t="inlineStr">
@@ -1844,6 +1973,7 @@
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="F123" t="inlineStr">
@@ -1855,6 +1985,7 @@
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="F124" t="inlineStr">
@@ -1866,6 +1997,7 @@
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="3" t="n"/>
       <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="F125" t="inlineStr">
@@ -1877,6 +2009,7 @@
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="F126" t="inlineStr">
@@ -1888,6 +2021,7 @@
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="F127" t="inlineStr">
@@ -1899,6 +2033,7 @@
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="F128" t="inlineStr">
@@ -1910,6 +2045,7 @@
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="F129" t="inlineStr">
@@ -1921,6 +2057,7 @@
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="F130" t="inlineStr">
@@ -1932,6 +2069,7 @@
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="F131" t="inlineStr">
@@ -1943,6 +2081,7 @@
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="F132" t="inlineStr">
@@ -1954,6 +2093,7 @@
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="F133" t="inlineStr">
@@ -1965,6 +2105,7 @@
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="F134" t="inlineStr">
@@ -1976,6 +2117,7 @@
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="F135" t="inlineStr">
@@ -1987,6 +2129,7 @@
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="F136" t="inlineStr">
@@ -1998,6 +2141,7 @@
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="F137" t="inlineStr">
@@ -2009,6 +2153,7 @@
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="F138" t="inlineStr">
@@ -2020,6 +2165,7 @@
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="F139" t="inlineStr">
@@ -2031,6 +2177,7 @@
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="F140" t="inlineStr">
@@ -2042,6 +2189,7 @@
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="F141" t="inlineStr">
@@ -2053,6 +2201,7 @@
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="F142" t="inlineStr">
@@ -2064,6 +2213,7 @@
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="F143" t="inlineStr">
@@ -2075,6 +2225,7 @@
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="F144" t="inlineStr">
@@ -2086,6 +2237,7 @@
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="F145" t="inlineStr">
@@ -2097,6 +2249,7 @@
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="F146" t="inlineStr">
@@ -2108,6 +2261,7 @@
       <c r="H146" s="2" t="n"/>
       <c r="I146" s="3" t="n"/>
       <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="F147" t="inlineStr">
@@ -2119,6 +2273,7 @@
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="F148" t="inlineStr">
@@ -2130,6 +2285,7 @@
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="F149" t="inlineStr">
@@ -2141,6 +2297,7 @@
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="F150" t="inlineStr">
@@ -2152,6 +2309,7 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="F151" t="inlineStr">
@@ -2163,6 +2321,7 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="F152" t="inlineStr">
@@ -2174,6 +2333,7 @@
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="F153" t="inlineStr">
@@ -2185,6 +2345,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="F154" t="inlineStr">
@@ -2196,6 +2357,7 @@
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="F155" t="inlineStr">
@@ -2207,6 +2369,7 @@
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="F156" t="inlineStr">
@@ -2218,6 +2381,7 @@
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="F157" t="inlineStr">
@@ -2229,6 +2393,7 @@
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="F158" t="inlineStr">
@@ -2240,6 +2405,7 @@
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="F159" t="inlineStr">
@@ -2251,6 +2417,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="3" t="n"/>
       <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="F160" t="inlineStr">
@@ -2262,6 +2429,7 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="F161" t="inlineStr">
@@ -2273,6 +2441,7 @@
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="3" t="n"/>
       <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="F162" t="inlineStr">
@@ -2284,6 +2453,7 @@
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="3" t="n"/>
       <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="F163" t="inlineStr">
@@ -2295,6 +2465,7 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="3" t="n"/>
       <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="F164" t="inlineStr">
@@ -2306,6 +2477,7 @@
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="3" t="n"/>
       <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="F165" t="inlineStr">
@@ -2317,6 +2489,7 @@
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="3" t="n"/>
       <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="F166" t="inlineStr">
@@ -2328,6 +2501,7 @@
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="3" t="n"/>
       <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="F167" t="inlineStr">
@@ -2339,6 +2513,7 @@
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="3" t="n"/>
       <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="F168" t="inlineStr">
@@ -2350,6 +2525,7 @@
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="F169" t="inlineStr">
@@ -2361,6 +2537,7 @@
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="3" t="n"/>
       <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="F170" t="inlineStr">
@@ -2372,6 +2549,7 @@
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="F171" t="inlineStr">
@@ -2383,6 +2561,7 @@
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="3" t="n"/>
       <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="F172" t="inlineStr">
@@ -2394,6 +2573,7 @@
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="3" t="n"/>
       <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="F173" t="inlineStr">
@@ -2405,6 +2585,7 @@
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="3" t="n"/>
       <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="F174" t="inlineStr">
@@ -2416,6 +2597,7 @@
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="3" t="n"/>
       <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="F175" t="inlineStr">
@@ -2427,6 +2609,7 @@
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="F176" t="inlineStr">
@@ -2438,6 +2621,7 @@
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="3" t="n"/>
       <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="F177" t="inlineStr">
@@ -2449,6 +2633,7 @@
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="3" t="n"/>
       <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="F178" t="inlineStr">
@@ -2460,6 +2645,7 @@
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="3" t="n"/>
       <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="F179" t="inlineStr">
@@ -2471,6 +2657,7 @@
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="F180" t="inlineStr">
@@ -2482,6 +2669,7 @@
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="3" t="n"/>
       <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="F181" t="inlineStr">
@@ -2493,6 +2681,7 @@
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="3" t="n"/>
       <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="F182" t="inlineStr">
@@ -2504,6 +2693,7 @@
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="3" t="n"/>
       <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="F183" t="inlineStr">
@@ -2515,6 +2705,7 @@
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="3" t="n"/>
       <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="F184" t="inlineStr">
@@ -2526,6 +2717,7 @@
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="F185" t="inlineStr">
@@ -2537,6 +2729,7 @@
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="3" t="n"/>
       <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="F186" t="inlineStr">
@@ -2548,6 +2741,7 @@
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="3" t="n"/>
       <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="F187" t="inlineStr">
@@ -2559,6 +2753,7 @@
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="3" t="n"/>
       <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="F188" t="inlineStr">
@@ -2570,6 +2765,7 @@
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="3" t="n"/>
       <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="F189" t="inlineStr">
@@ -2581,6 +2777,7 @@
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="3" t="n"/>
       <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="F190" t="inlineStr">
@@ -2592,6 +2789,7 @@
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="3" t="n"/>
       <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="F191" t="inlineStr">
@@ -2603,6 +2801,7 @@
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="F192" t="inlineStr">
@@ -2614,6 +2813,7 @@
       <c r="H192" s="2" t="n"/>
       <c r="I192" s="3" t="n"/>
       <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="F193" t="inlineStr">
@@ -2625,6 +2825,7 @@
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="F194" t="inlineStr">
@@ -2636,6 +2837,7 @@
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="F195" t="inlineStr">
@@ -2647,6 +2849,7 @@
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="3" t="n"/>
       <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="F196" t="inlineStr">
@@ -2658,6 +2861,7 @@
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="3" t="n"/>
       <c r="J196" s="3" t="n"/>
+      <c r="K196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="F197" t="inlineStr">
@@ -2669,6 +2873,7 @@
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="n"/>
+      <c r="K197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="F198" t="inlineStr">
@@ -2680,6 +2885,7 @@
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n"/>
+      <c r="K198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="F199" t="inlineStr">
@@ -2691,6 +2897,7 @@
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
+      <c r="K199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="F200" t="inlineStr">
@@ -2702,6 +2909,7 @@
       <c r="H200" s="2" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="F201" t="inlineStr">
@@ -2713,6 +2921,7 @@
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="F202" t="inlineStr">
@@ -2724,6 +2933,7 @@
       <c r="H202" s="2" t="n"/>
       <c r="I202" s="3" t="n"/>
       <c r="J202" s="3" t="n"/>
+      <c r="K202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="F203" t="inlineStr">
@@ -2735,6 +2945,7 @@
       <c r="H203" s="2" t="n"/>
       <c r="I203" s="3" t="n"/>
       <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="F204" t="inlineStr">
@@ -2746,6 +2957,7 @@
       <c r="H204" s="2" t="n"/>
       <c r="I204" s="3" t="n"/>
       <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="F205" t="inlineStr">
@@ -2757,6 +2969,7 @@
       <c r="H205" s="2" t="n"/>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="F206" t="inlineStr">
@@ -2768,6 +2981,7 @@
       <c r="H206" s="2" t="n"/>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="F207" t="inlineStr">
@@ -2779,6 +2993,7 @@
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="3" t="n"/>
       <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="F208" t="inlineStr">
@@ -2790,6 +3005,7 @@
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n"/>
+      <c r="K208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="F209" t="inlineStr">
@@ -2801,6 +3017,7 @@
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="3" t="n"/>
       <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="F210" t="inlineStr">
@@ -2812,6 +3029,7 @@
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="3" t="n"/>
       <c r="J210" s="3" t="n"/>
+      <c r="K210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="F211" t="inlineStr">
@@ -2823,6 +3041,7 @@
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="3" t="n"/>
       <c r="J211" s="3" t="n"/>
+      <c r="K211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="F212" t="inlineStr">
@@ -2834,6 +3053,7 @@
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="3" t="n"/>
       <c r="J212" s="3" t="n"/>
+      <c r="K212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="F213" t="inlineStr">
@@ -2845,6 +3065,7 @@
       <c r="H213" s="2" t="n"/>
       <c r="I213" s="3" t="n"/>
       <c r="J213" s="3" t="n"/>
+      <c r="K213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="F214" t="inlineStr">
@@ -2856,6 +3077,7 @@
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="3" t="n"/>
       <c r="J214" s="3" t="n"/>
+      <c r="K214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="F215" t="inlineStr">
@@ -2867,6 +3089,7 @@
       <c r="H215" s="2" t="n"/>
       <c r="I215" s="3" t="n"/>
       <c r="J215" s="3" t="n"/>
+      <c r="K215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="F216" t="inlineStr">
@@ -2878,6 +3101,7 @@
       <c r="H216" s="2" t="n"/>
       <c r="I216" s="3" t="n"/>
       <c r="J216" s="3" t="n"/>
+      <c r="K216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="F217" t="inlineStr">
@@ -2889,6 +3113,7 @@
       <c r="H217" s="2" t="n"/>
       <c r="I217" s="3" t="n"/>
       <c r="J217" s="3" t="n"/>
+      <c r="K217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="F218" t="inlineStr">
@@ -2900,6 +3125,7 @@
       <c r="H218" s="2" t="n"/>
       <c r="I218" s="3" t="n"/>
       <c r="J218" s="3" t="n"/>
+      <c r="K218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="F219" t="inlineStr">
@@ -2911,6 +3137,7 @@
       <c r="H219" s="2" t="n"/>
       <c r="I219" s="3" t="n"/>
       <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="F220" t="inlineStr">
@@ -2922,6 +3149,7 @@
       <c r="H220" s="2" t="n"/>
       <c r="I220" s="3" t="n"/>
       <c r="J220" s="3" t="n"/>
+      <c r="K220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="F221" t="inlineStr">
@@ -2933,6 +3161,7 @@
       <c r="H221" s="2" t="n"/>
       <c r="I221" s="3" t="n"/>
       <c r="J221" s="3" t="n"/>
+      <c r="K221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="F222" t="inlineStr">
@@ -2944,6 +3173,7 @@
       <c r="H222" s="2" t="n"/>
       <c r="I222" s="3" t="n"/>
       <c r="J222" s="3" t="n"/>
+      <c r="K222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="F223" t="inlineStr">
@@ -2955,6 +3185,7 @@
       <c r="H223" s="2" t="n"/>
       <c r="I223" s="3" t="n"/>
       <c r="J223" s="3" t="n"/>
+      <c r="K223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="F224" t="inlineStr">
@@ -2966,6 +3197,7 @@
       <c r="H224" s="2" t="n"/>
       <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n"/>
+      <c r="K224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="F225" t="inlineStr">
@@ -2977,6 +3209,7 @@
       <c r="H225" s="2" t="n"/>
       <c r="I225" s="3" t="n"/>
       <c r="J225" s="3" t="n"/>
+      <c r="K225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="F226" t="inlineStr">
@@ -2988,6 +3221,7 @@
       <c r="H226" s="2" t="n"/>
       <c r="I226" s="3" t="n"/>
       <c r="J226" s="3" t="n"/>
+      <c r="K226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="F227" t="inlineStr">
@@ -2999,6 +3233,7 @@
       <c r="H227" s="2" t="n"/>
       <c r="I227" s="3" t="n"/>
       <c r="J227" s="3" t="n"/>
+      <c r="K227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="F228" t="inlineStr">
@@ -3010,6 +3245,7 @@
       <c r="H228" s="2" t="n"/>
       <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="n"/>
+      <c r="K228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="F229" t="inlineStr">
@@ -3021,6 +3257,7 @@
       <c r="H229" s="2" t="n"/>
       <c r="I229" s="3" t="n"/>
       <c r="J229" s="3" t="n"/>
+      <c r="K229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="F230" t="inlineStr">
@@ -3032,6 +3269,7 @@
       <c r="H230" s="2" t="n"/>
       <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="n"/>
+      <c r="K230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="F231" t="inlineStr">
@@ -3043,6 +3281,7 @@
       <c r="H231" s="2" t="n"/>
       <c r="I231" s="3" t="n"/>
       <c r="J231" s="3" t="n"/>
+      <c r="K231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="F232" t="inlineStr">
@@ -3054,6 +3293,7 @@
       <c r="H232" s="2" t="n"/>
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="3" t="n"/>
+      <c r="K232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="F233" t="inlineStr">
@@ -3065,6 +3305,7 @@
       <c r="H233" s="2" t="n"/>
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="n"/>
+      <c r="K233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="F234" t="inlineStr">
@@ -3076,6 +3317,7 @@
       <c r="H234" s="2" t="n"/>
       <c r="I234" s="3" t="n"/>
       <c r="J234" s="3" t="n"/>
+      <c r="K234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="F235" t="inlineStr">
@@ -3087,6 +3329,7 @@
       <c r="H235" s="2" t="n"/>
       <c r="I235" s="3" t="n"/>
       <c r="J235" s="3" t="n"/>
+      <c r="K235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="F236" t="inlineStr">
@@ -3098,6 +3341,7 @@
       <c r="H236" s="2" t="n"/>
       <c r="I236" s="3" t="n"/>
       <c r="J236" s="3" t="n"/>
+      <c r="K236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="F237" t="inlineStr">
@@ -3109,6 +3353,7 @@
       <c r="H237" s="2" t="n"/>
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="3" t="n"/>
+      <c r="K237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="F238" t="inlineStr">
@@ -3120,6 +3365,7 @@
       <c r="H238" s="2" t="n"/>
       <c r="I238" s="3" t="n"/>
       <c r="J238" s="3" t="n"/>
+      <c r="K238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="F239" t="inlineStr">
@@ -3131,6 +3377,7 @@
       <c r="H239" s="2" t="n"/>
       <c r="I239" s="3" t="n"/>
       <c r="J239" s="3" t="n"/>
+      <c r="K239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="F240" t="inlineStr">
@@ -3142,6 +3389,7 @@
       <c r="H240" s="2" t="n"/>
       <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="n"/>
+      <c r="K240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="F241" t="inlineStr">
@@ -3153,6 +3401,7 @@
       <c r="H241" s="2" t="n"/>
       <c r="I241" s="3" t="n"/>
       <c r="J241" s="3" t="n"/>
+      <c r="K241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="F242" t="inlineStr">
@@ -3164,6 +3413,7 @@
       <c r="H242" s="2" t="n"/>
       <c r="I242" s="3" t="n"/>
       <c r="J242" s="3" t="n"/>
+      <c r="K242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="F243" t="inlineStr">
@@ -3175,6 +3425,7 @@
       <c r="H243" s="2" t="n"/>
       <c r="I243" s="3" t="n"/>
       <c r="J243" s="3" t="n"/>
+      <c r="K243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="F244" t="inlineStr">
@@ -3186,6 +3437,7 @@
       <c r="H244" s="2" t="n"/>
       <c r="I244" s="3" t="n"/>
       <c r="J244" s="3" t="n"/>
+      <c r="K244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="F245" t="inlineStr">
@@ -3197,6 +3449,7 @@
       <c r="H245" s="2" t="n"/>
       <c r="I245" s="3" t="n"/>
       <c r="J245" s="3" t="n"/>
+      <c r="K245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="F246" t="inlineStr">
@@ -3208,6 +3461,7 @@
       <c r="H246" s="2" t="n"/>
       <c r="I246" s="3" t="n"/>
       <c r="J246" s="3" t="n"/>
+      <c r="K246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="F247" t="inlineStr">
@@ -3219,6 +3473,7 @@
       <c r="H247" s="2" t="n"/>
       <c r="I247" s="3" t="n"/>
       <c r="J247" s="3" t="n"/>
+      <c r="K247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="F248" t="inlineStr">
@@ -3230,6 +3485,7 @@
       <c r="H248" s="2" t="n"/>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="3" t="n"/>
+      <c r="K248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="F249" t="inlineStr">
@@ -3241,6 +3497,7 @@
       <c r="H249" s="2" t="n"/>
       <c r="I249" s="3" t="n"/>
       <c r="J249" s="3" t="n"/>
+      <c r="K249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="F250" t="inlineStr">
@@ -3252,6 +3509,7 @@
       <c r="H250" s="2" t="n"/>
       <c r="I250" s="3" t="n"/>
       <c r="J250" s="3" t="n"/>
+      <c r="K250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="F251" t="inlineStr">
@@ -3263,6 +3521,7 @@
       <c r="H251" s="2" t="n"/>
       <c r="I251" s="3" t="n"/>
       <c r="J251" s="3" t="n"/>
+      <c r="K251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="F252" t="inlineStr">
@@ -3274,6 +3533,7 @@
       <c r="H252" s="2" t="n"/>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="3" t="n"/>
+      <c r="K252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="F253" t="inlineStr">
@@ -3285,6 +3545,7 @@
       <c r="H253" s="2" t="n"/>
       <c r="I253" s="3" t="n"/>
       <c r="J253" s="3" t="n"/>
+      <c r="K253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="F254" t="inlineStr">
@@ -3296,6 +3557,7 @@
       <c r="H254" s="2" t="n"/>
       <c r="I254" s="3" t="n"/>
       <c r="J254" s="3" t="n"/>
+      <c r="K254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="F255" t="inlineStr">
@@ -3307,6 +3569,7 @@
       <c r="H255" s="2" t="n"/>
       <c r="I255" s="3" t="n"/>
       <c r="J255" s="3" t="n"/>
+      <c r="K255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="F256" t="inlineStr">
@@ -3318,6 +3581,7 @@
       <c r="H256" s="2" t="n"/>
       <c r="I256" s="3" t="n"/>
       <c r="J256" s="3" t="n"/>
+      <c r="K256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="F257" t="inlineStr">
@@ -3329,6 +3593,7 @@
       <c r="H257" s="2" t="n"/>
       <c r="I257" s="3" t="n"/>
       <c r="J257" s="3" t="n"/>
+      <c r="K257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="F258" t="inlineStr">
@@ -3340,6 +3605,7 @@
       <c r="H258" s="2" t="n"/>
       <c r="I258" s="3" t="n"/>
       <c r="J258" s="3" t="n"/>
+      <c r="K258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="F259" t="inlineStr">
@@ -3351,6 +3617,7 @@
       <c r="H259" s="2" t="n"/>
       <c r="I259" s="3" t="n"/>
       <c r="J259" s="3" t="n"/>
+      <c r="K259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="F260" t="inlineStr">
@@ -3362,6 +3629,7 @@
       <c r="H260" s="2" t="n"/>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="n"/>
+      <c r="K260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="F261" t="inlineStr">
@@ -3373,6 +3641,7 @@
       <c r="H261" s="2" t="n"/>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="n"/>
+      <c r="K261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="F262" t="inlineStr">
@@ -3384,6 +3653,7 @@
       <c r="H262" s="2" t="n"/>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="n"/>
+      <c r="K262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="F263" t="inlineStr">
@@ -3395,6 +3665,7 @@
       <c r="H263" s="2" t="n"/>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="n"/>
+      <c r="K263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="F264" t="inlineStr">
@@ -3406,6 +3677,7 @@
       <c r="H264" s="2" t="n"/>
       <c r="I264" s="3" t="n"/>
       <c r="J264" s="3" t="n"/>
+      <c r="K264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="F265" t="inlineStr">
@@ -3417,6 +3689,7 @@
       <c r="H265" s="2" t="n"/>
       <c r="I265" s="3" t="n"/>
       <c r="J265" s="3" t="n"/>
+      <c r="K265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="F266" t="inlineStr">
@@ -3428,6 +3701,7 @@
       <c r="H266" s="2" t="n"/>
       <c r="I266" s="3" t="n"/>
       <c r="J266" s="3" t="n"/>
+      <c r="K266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="F267" t="inlineStr">
@@ -3439,6 +3713,7 @@
       <c r="H267" s="2" t="n"/>
       <c r="I267" s="3" t="n"/>
       <c r="J267" s="3" t="n"/>
+      <c r="K267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="F268" t="inlineStr">
@@ -3450,6 +3725,7 @@
       <c r="H268" s="2" t="n"/>
       <c r="I268" s="3" t="n"/>
       <c r="J268" s="3" t="n"/>
+      <c r="K268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="F269" t="inlineStr">
@@ -3461,6 +3737,7 @@
       <c r="H269" s="2" t="n"/>
       <c r="I269" s="3" t="n"/>
       <c r="J269" s="3" t="n"/>
+      <c r="K269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="F270" t="inlineStr">
@@ -3472,6 +3749,7 @@
       <c r="H270" s="2" t="n"/>
       <c r="I270" s="3" t="n"/>
       <c r="J270" s="3" t="n"/>
+      <c r="K270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="F271" t="inlineStr">
@@ -3483,6 +3761,7 @@
       <c r="H271" s="2" t="n"/>
       <c r="I271" s="3" t="n"/>
       <c r="J271" s="3" t="n"/>
+      <c r="K271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="F272" t="inlineStr">
@@ -3494,6 +3773,7 @@
       <c r="H272" s="2" t="n"/>
       <c r="I272" s="3" t="n"/>
       <c r="J272" s="3" t="n"/>
+      <c r="K272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="F273" t="inlineStr">
@@ -3505,6 +3785,7 @@
       <c r="H273" s="2" t="n"/>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
+      <c r="K273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="F274" t="inlineStr">
@@ -3516,6 +3797,7 @@
       <c r="H274" s="2" t="n"/>
       <c r="I274" s="3" t="n"/>
       <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="F275" t="inlineStr">
@@ -3527,6 +3809,7 @@
       <c r="H275" s="2" t="n"/>
       <c r="I275" s="3" t="n"/>
       <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="F276" t="inlineStr">
@@ -3538,6 +3821,7 @@
       <c r="H276" s="2" t="n"/>
       <c r="I276" s="3" t="n"/>
       <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="F277" t="inlineStr">
@@ -3549,6 +3833,7 @@
       <c r="H277" s="2" t="n"/>
       <c r="I277" s="3" t="n"/>
       <c r="J277" s="3" t="n"/>
+      <c r="K277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="F278" t="inlineStr">
@@ -3560,6 +3845,7 @@
       <c r="H278" s="2" t="n"/>
       <c r="I278" s="3" t="n"/>
       <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="F279" t="inlineStr">
@@ -3571,6 +3857,7 @@
       <c r="H279" s="2" t="n"/>
       <c r="I279" s="3" t="n"/>
       <c r="J279" s="3" t="n"/>
+      <c r="K279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="F280" t="inlineStr">
@@ -3582,6 +3869,7 @@
       <c r="H280" s="2" t="n"/>
       <c r="I280" s="3" t="n"/>
       <c r="J280" s="3" t="n"/>
+      <c r="K280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="F281" t="inlineStr">
@@ -3593,6 +3881,7 @@
       <c r="H281" s="2" t="n"/>
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="n"/>
+      <c r="K281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="F282" t="inlineStr">
@@ -3604,6 +3893,7 @@
       <c r="H282" s="2" t="n"/>
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="F283" t="inlineStr">
@@ -3615,6 +3905,7 @@
       <c r="H283" s="2" t="n"/>
       <c r="I283" s="3" t="n"/>
       <c r="J283" s="3" t="n"/>
+      <c r="K283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="F284" t="inlineStr">
@@ -3626,6 +3917,7 @@
       <c r="H284" s="2" t="n"/>
       <c r="I284" s="3" t="n"/>
       <c r="J284" s="3" t="n"/>
+      <c r="K284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="F285" t="inlineStr">
@@ -3637,6 +3929,7 @@
       <c r="H285" s="2" t="n"/>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n"/>
+      <c r="K285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="F286" t="inlineStr">
@@ -3648,6 +3941,7 @@
       <c r="H286" s="2" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="n"/>
+      <c r="K286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="F287" t="inlineStr">
@@ -3659,6 +3953,7 @@
       <c r="H287" s="2" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="n"/>
+      <c r="K287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="F288" t="inlineStr">
@@ -3670,6 +3965,7 @@
       <c r="H288" s="2" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="n"/>
+      <c r="K288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="F289" t="inlineStr">
@@ -3681,6 +3977,7 @@
       <c r="H289" s="2" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="n"/>
+      <c r="K289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="F290" t="inlineStr">
@@ -3692,6 +3989,7 @@
       <c r="H290" s="2" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="n"/>
+      <c r="K290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="F291" t="inlineStr">
@@ -3703,6 +4001,7 @@
       <c r="H291" s="2" t="n"/>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="n"/>
+      <c r="K291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="F292" t="inlineStr">
@@ -3714,6 +4013,7 @@
       <c r="H292" s="2" t="n"/>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n"/>
+      <c r="K292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="F293" t="inlineStr">
@@ -3725,6 +4025,7 @@
       <c r="H293" s="2" t="n"/>
       <c r="I293" s="3" t="n"/>
       <c r="J293" s="3" t="n"/>
+      <c r="K293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="F294" t="inlineStr">
@@ -3736,6 +4037,7 @@
       <c r="H294" s="2" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="n"/>
+      <c r="K294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="F295" t="inlineStr">
@@ -3747,6 +4049,7 @@
       <c r="H295" s="2" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="n"/>
+      <c r="K295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="F296" t="inlineStr">
@@ -3758,6 +4061,7 @@
       <c r="H296" s="2" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="n"/>
+      <c r="K296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="F297" t="inlineStr">
@@ -3769,6 +4073,7 @@
       <c r="H297" s="2" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="n"/>
+      <c r="K297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="F298" t="inlineStr">
@@ -3780,6 +4085,7 @@
       <c r="H298" s="2" t="n"/>
       <c r="I298" s="3" t="n"/>
       <c r="J298" s="3" t="n"/>
+      <c r="K298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="F299" t="inlineStr">
@@ -3791,6 +4097,7 @@
       <c r="H299" s="2" t="n"/>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
+      <c r="K299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="F300" t="inlineStr">
@@ -3802,6 +4109,7 @@
       <c r="H300" s="2" t="n"/>
       <c r="I300" s="3" t="n"/>
       <c r="J300" s="3" t="n"/>
+      <c r="K300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="F301" t="inlineStr">
@@ -3813,6 +4121,7 @@
       <c r="H301" s="2" t="n"/>
       <c r="I301" s="3" t="n"/>
       <c r="J301" s="3" t="n"/>
+      <c r="K301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="F302" t="inlineStr">
@@ -3824,6 +4133,7 @@
       <c r="H302" s="2" t="n"/>
       <c r="I302" s="3" t="n"/>
       <c r="J302" s="3" t="n"/>
+      <c r="K302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="F303" t="inlineStr">
@@ -3835,6 +4145,7 @@
       <c r="H303" s="2" t="n"/>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
+      <c r="K303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="F304" t="inlineStr">
@@ -3846,6 +4157,7 @@
       <c r="H304" s="2" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
+      <c r="K304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="F305" t="inlineStr">
@@ -3857,6 +4169,7 @@
       <c r="H305" s="2" t="n"/>
       <c r="I305" s="3" t="n"/>
       <c r="J305" s="3" t="n"/>
+      <c r="K305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="F306" t="inlineStr">
@@ -3868,6 +4181,7 @@
       <c r="H306" s="2" t="n"/>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n"/>
+      <c r="K306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="F307" t="inlineStr">
@@ -3879,6 +4193,7 @@
       <c r="H307" s="2" t="n"/>
       <c r="I307" s="3" t="n"/>
       <c r="J307" s="3" t="n"/>
+      <c r="K307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="F308" t="inlineStr">
@@ -3890,6 +4205,7 @@
       <c r="H308" s="2" t="n"/>
       <c r="I308" s="3" t="n"/>
       <c r="J308" s="3" t="n"/>
+      <c r="K308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="F309" t="inlineStr">
@@ -3901,6 +4217,7 @@
       <c r="H309" s="2" t="n"/>
       <c r="I309" s="3" t="n"/>
       <c r="J309" s="3" t="n"/>
+      <c r="K309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="F310" t="inlineStr">
@@ -3912,6 +4229,7 @@
       <c r="H310" s="2" t="n"/>
       <c r="I310" s="3" t="n"/>
       <c r="J310" s="3" t="n"/>
+      <c r="K310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="F311" t="inlineStr">
@@ -3923,6 +4241,7 @@
       <c r="H311" s="2" t="n"/>
       <c r="I311" s="3" t="n"/>
       <c r="J311" s="3" t="n"/>
+      <c r="K311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="F312" t="inlineStr">
@@ -3934,6 +4253,7 @@
       <c r="H312" s="2" t="n"/>
       <c r="I312" s="3" t="n"/>
       <c r="J312" s="3" t="n"/>
+      <c r="K312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="F313" t="inlineStr">
@@ -3945,6 +4265,7 @@
       <c r="H313" s="2" t="n"/>
       <c r="I313" s="3" t="n"/>
       <c r="J313" s="3" t="n"/>
+      <c r="K313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="F314" t="inlineStr">
@@ -3956,6 +4277,7 @@
       <c r="H314" s="2" t="n"/>
       <c r="I314" s="3" t="n"/>
       <c r="J314" s="3" t="n"/>
+      <c r="K314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="F315" t="inlineStr">
@@ -3967,6 +4289,7 @@
       <c r="H315" s="2" t="n"/>
       <c r="I315" s="3" t="n"/>
       <c r="J315" s="3" t="n"/>
+      <c r="K315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="F316" t="inlineStr">
@@ -3978,6 +4301,7 @@
       <c r="H316" s="2" t="n"/>
       <c r="I316" s="3" t="n"/>
       <c r="J316" s="3" t="n"/>
+      <c r="K316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="F317" t="inlineStr">
@@ -3989,6 +4313,7 @@
       <c r="H317" s="2" t="n"/>
       <c r="I317" s="3" t="n"/>
       <c r="J317" s="3" t="n"/>
+      <c r="K317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="F318" t="inlineStr">
@@ -4000,6 +4325,7 @@
       <c r="H318" s="2" t="n"/>
       <c r="I318" s="3" t="n"/>
       <c r="J318" s="3" t="n"/>
+      <c r="K318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="F319" t="inlineStr">
@@ -4011,6 +4337,7 @@
       <c r="H319" s="2" t="n"/>
       <c r="I319" s="3" t="n"/>
       <c r="J319" s="3" t="n"/>
+      <c r="K319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="F320" t="inlineStr">
@@ -4022,6 +4349,7 @@
       <c r="H320" s="2" t="n"/>
       <c r="I320" s="3" t="n"/>
       <c r="J320" s="3" t="n"/>
+      <c r="K320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="F321" t="inlineStr">
@@ -4033,6 +4361,7 @@
       <c r="H321" s="2" t="n"/>
       <c r="I321" s="3" t="n"/>
       <c r="J321" s="3" t="n"/>
+      <c r="K321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="F322" t="inlineStr">
@@ -4044,6 +4373,7 @@
       <c r="H322" s="2" t="n"/>
       <c r="I322" s="3" t="n"/>
       <c r="J322" s="3" t="n"/>
+      <c r="K322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="F323" t="inlineStr">
@@ -4055,6 +4385,7 @@
       <c r="H323" s="2" t="n"/>
       <c r="I323" s="3" t="n"/>
       <c r="J323" s="3" t="n"/>
+      <c r="K323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="F324" t="inlineStr">
@@ -4066,6 +4397,7 @@
       <c r="H324" s="2" t="n"/>
       <c r="I324" s="3" t="n"/>
       <c r="J324" s="3" t="n"/>
+      <c r="K324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="F325" t="inlineStr">
@@ -4077,6 +4409,7 @@
       <c r="H325" s="2" t="n"/>
       <c r="I325" s="3" t="n"/>
       <c r="J325" s="3" t="n"/>
+      <c r="K325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="F326" t="inlineStr">
@@ -4088,6 +4421,7 @@
       <c r="H326" s="2" t="n"/>
       <c r="I326" s="3" t="n"/>
       <c r="J326" s="3" t="n"/>
+      <c r="K326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="F327" t="inlineStr">
@@ -4099,6 +4433,7 @@
       <c r="H327" s="2" t="n"/>
       <c r="I327" s="3" t="n"/>
       <c r="J327" s="3" t="n"/>
+      <c r="K327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="F328" t="inlineStr">
@@ -4110,6 +4445,7 @@
       <c r="H328" s="2" t="n"/>
       <c r="I328" s="3" t="n"/>
       <c r="J328" s="3" t="n"/>
+      <c r="K328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="F329" t="inlineStr">
@@ -4121,6 +4457,7 @@
       <c r="H329" s="2" t="n"/>
       <c r="I329" s="3" t="n"/>
       <c r="J329" s="3" t="n"/>
+      <c r="K329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="F330" t="inlineStr">
@@ -4132,6 +4469,7 @@
       <c r="H330" s="2" t="n"/>
       <c r="I330" s="3" t="n"/>
       <c r="J330" s="3" t="n"/>
+      <c r="K330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="F331" t="inlineStr">
@@ -4143,6 +4481,7 @@
       <c r="H331" s="2" t="n"/>
       <c r="I331" s="3" t="n"/>
       <c r="J331" s="3" t="n"/>
+      <c r="K331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="F332" t="inlineStr">
@@ -4154,6 +4493,7 @@
       <c r="H332" s="2" t="n"/>
       <c r="I332" s="3" t="n"/>
       <c r="J332" s="3" t="n"/>
+      <c r="K332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="F333" t="inlineStr">
@@ -4165,6 +4505,7 @@
       <c r="H333" s="2" t="n"/>
       <c r="I333" s="3" t="n"/>
       <c r="J333" s="3" t="n"/>
+      <c r="K333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="F334" t="inlineStr">
@@ -4176,6 +4517,7 @@
       <c r="H334" s="2" t="n"/>
       <c r="I334" s="3" t="n"/>
       <c r="J334" s="3" t="n"/>
+      <c r="K334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="F335" t="inlineStr">
@@ -4187,6 +4529,7 @@
       <c r="H335" s="2" t="n"/>
       <c r="I335" s="3" t="n"/>
       <c r="J335" s="3" t="n"/>
+      <c r="K335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="F336" t="inlineStr">
@@ -4198,6 +4541,7 @@
       <c r="H336" s="2" t="n"/>
       <c r="I336" s="3" t="n"/>
       <c r="J336" s="3" t="n"/>
+      <c r="K336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="F337" t="inlineStr">
@@ -4209,6 +4553,7 @@
       <c r="H337" s="2" t="n"/>
       <c r="I337" s="3" t="n"/>
       <c r="J337" s="3" t="n"/>
+      <c r="K337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="F338" t="inlineStr">
@@ -4220,6 +4565,7 @@
       <c r="H338" s="2" t="n"/>
       <c r="I338" s="3" t="n"/>
       <c r="J338" s="3" t="n"/>
+      <c r="K338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="F339" t="inlineStr">
@@ -4231,6 +4577,7 @@
       <c r="H339" s="2" t="n"/>
       <c r="I339" s="3" t="n"/>
       <c r="J339" s="3" t="n"/>
+      <c r="K339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="F340" t="inlineStr">
@@ -4242,6 +4589,7 @@
       <c r="H340" s="2" t="n"/>
       <c r="I340" s="3" t="n"/>
       <c r="J340" s="3" t="n"/>
+      <c r="K340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="F341" t="inlineStr">
@@ -4253,6 +4601,7 @@
       <c r="H341" s="2" t="n"/>
       <c r="I341" s="3" t="n"/>
       <c r="J341" s="3" t="n"/>
+      <c r="K341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="F342" t="inlineStr">
@@ -4264,6 +4613,7 @@
       <c r="H342" s="2" t="n"/>
       <c r="I342" s="3" t="n"/>
       <c r="J342" s="3" t="n"/>
+      <c r="K342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="F343" t="inlineStr">
@@ -4275,6 +4625,7 @@
       <c r="H343" s="2" t="n"/>
       <c r="I343" s="3" t="n"/>
       <c r="J343" s="3" t="n"/>
+      <c r="K343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="F344" t="inlineStr">
@@ -4286,6 +4637,7 @@
       <c r="H344" s="2" t="n"/>
       <c r="I344" s="3" t="n"/>
       <c r="J344" s="3" t="n"/>
+      <c r="K344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="F345" t="inlineStr">
@@ -4297,6 +4649,7 @@
       <c r="H345" s="2" t="n"/>
       <c r="I345" s="3" t="n"/>
       <c r="J345" s="3" t="n"/>
+      <c r="K345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="F346" t="inlineStr">
@@ -4308,6 +4661,7 @@
       <c r="H346" s="2" t="n"/>
       <c r="I346" s="3" t="n"/>
       <c r="J346" s="3" t="n"/>
+      <c r="K346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="F347" t="inlineStr">
@@ -4319,6 +4673,7 @@
       <c r="H347" s="2" t="n"/>
       <c r="I347" s="3" t="n"/>
       <c r="J347" s="3" t="n"/>
+      <c r="K347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="F348" t="inlineStr">
@@ -4330,6 +4685,7 @@
       <c r="H348" s="2" t="n"/>
       <c r="I348" s="3" t="n"/>
       <c r="J348" s="3" t="n"/>
+      <c r="K348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="F349" t="inlineStr">
@@ -4341,6 +4697,7 @@
       <c r="H349" s="2" t="n"/>
       <c r="I349" s="3" t="n"/>
       <c r="J349" s="3" t="n"/>
+      <c r="K349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="F350" t="inlineStr">
@@ -4352,6 +4709,7 @@
       <c r="H350" s="2" t="n"/>
       <c r="I350" s="3" t="n"/>
       <c r="J350" s="3" t="n"/>
+      <c r="K350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="F351" t="inlineStr">
@@ -4363,6 +4721,7 @@
       <c r="H351" s="2" t="n"/>
       <c r="I351" s="3" t="n"/>
       <c r="J351" s="3" t="n"/>
+      <c r="K351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="F352" t="inlineStr">
@@ -4374,6 +4733,7 @@
       <c r="H352" s="2" t="n"/>
       <c r="I352" s="3" t="n"/>
       <c r="J352" s="3" t="n"/>
+      <c r="K352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="F353" t="inlineStr">
@@ -4385,6 +4745,7 @@
       <c r="H353" s="2" t="n"/>
       <c r="I353" s="3" t="n"/>
       <c r="J353" s="3" t="n"/>
+      <c r="K353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="F354" t="inlineStr">
@@ -4396,6 +4757,7 @@
       <c r="H354" s="2" t="n"/>
       <c r="I354" s="3" t="n"/>
       <c r="J354" s="3" t="n"/>
+      <c r="K354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="F355" t="inlineStr">
@@ -4407,6 +4769,7 @@
       <c r="H355" s="2" t="n"/>
       <c r="I355" s="3" t="n"/>
       <c r="J355" s="3" t="n"/>
+      <c r="K355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="F356" t="inlineStr">
@@ -4418,6 +4781,7 @@
       <c r="H356" s="2" t="n"/>
       <c r="I356" s="3" t="n"/>
       <c r="J356" s="3" t="n"/>
+      <c r="K356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="F357" t="inlineStr">
@@ -4429,6 +4793,7 @@
       <c r="H357" s="2" t="n"/>
       <c r="I357" s="3" t="n"/>
       <c r="J357" s="3" t="n"/>
+      <c r="K357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="F358" t="inlineStr">
@@ -4440,6 +4805,7 @@
       <c r="H358" s="2" t="n"/>
       <c r="I358" s="3" t="n"/>
       <c r="J358" s="3" t="n"/>
+      <c r="K358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="F359" t="inlineStr">
@@ -4451,6 +4817,7 @@
       <c r="H359" s="2" t="n"/>
       <c r="I359" s="3" t="n"/>
       <c r="J359" s="3" t="n"/>
+      <c r="K359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="F360" t="inlineStr">
@@ -4462,6 +4829,7 @@
       <c r="H360" s="2" t="n"/>
       <c r="I360" s="3" t="n"/>
       <c r="J360" s="3" t="n"/>
+      <c r="K360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="F361" t="inlineStr">
@@ -4473,6 +4841,7 @@
       <c r="H361" s="2" t="n"/>
       <c r="I361" s="3" t="n"/>
       <c r="J361" s="3" t="n"/>
+      <c r="K361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="F362" t="inlineStr">
@@ -4484,6 +4853,7 @@
       <c r="H362" s="2" t="n"/>
       <c r="I362" s="3" t="n"/>
       <c r="J362" s="3" t="n"/>
+      <c r="K362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="F363" t="inlineStr">
@@ -4495,6 +4865,7 @@
       <c r="H363" s="2" t="n"/>
       <c r="I363" s="3" t="n"/>
       <c r="J363" s="3" t="n"/>
+      <c r="K363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="F364" t="inlineStr">
@@ -4506,6 +4877,7 @@
       <c r="H364" s="2" t="n"/>
       <c r="I364" s="3" t="n"/>
       <c r="J364" s="3" t="n"/>
+      <c r="K364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="F365" t="inlineStr">
@@ -4517,6 +4889,7 @@
       <c r="H365" s="2" t="n"/>
       <c r="I365" s="3" t="n"/>
       <c r="J365" s="3" t="n"/>
+      <c r="K365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="F366" t="inlineStr">
@@ -4528,6 +4901,7 @@
       <c r="H366" s="2" t="n"/>
       <c r="I366" s="3" t="n"/>
       <c r="J366" s="3" t="n"/>
+      <c r="K366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="F367" t="inlineStr">
@@ -4539,6 +4913,7 @@
       <c r="H367" s="2" t="n"/>
       <c r="I367" s="3" t="n"/>
       <c r="J367" s="3" t="n"/>
+      <c r="K367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="F368" t="inlineStr">
@@ -4550,6 +4925,7 @@
       <c r="H368" s="2" t="n"/>
       <c r="I368" s="3" t="n"/>
       <c r="J368" s="3" t="n"/>
+      <c r="K368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="F369" t="inlineStr">
@@ -4561,6 +4937,7 @@
       <c r="H369" s="2" t="n"/>
       <c r="I369" s="3" t="n"/>
       <c r="J369" s="3" t="n"/>
+      <c r="K369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="F370" t="inlineStr">
@@ -4572,6 +4949,7 @@
       <c r="H370" s="2" t="n"/>
       <c r="I370" s="3" t="n"/>
       <c r="J370" s="3" t="n"/>
+      <c r="K370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="F371" t="inlineStr">
@@ -4583,6 +4961,7 @@
       <c r="H371" s="2" t="n"/>
       <c r="I371" s="3" t="n"/>
       <c r="J371" s="3" t="n"/>
+      <c r="K371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="F372" t="inlineStr">
@@ -4594,6 +4973,7 @@
       <c r="H372" s="2" t="n"/>
       <c r="I372" s="3" t="n"/>
       <c r="J372" s="3" t="n"/>
+      <c r="K372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="F373" t="inlineStr">
@@ -4605,6 +4985,7 @@
       <c r="H373" s="2" t="n"/>
       <c r="I373" s="3" t="n"/>
       <c r="J373" s="3" t="n"/>
+      <c r="K373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="F374" t="inlineStr">
@@ -4616,6 +4997,7 @@
       <c r="H374" s="2" t="n"/>
       <c r="I374" s="3" t="n"/>
       <c r="J374" s="3" t="n"/>
+      <c r="K374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="F375" t="inlineStr">
@@ -4627,6 +5009,7 @@
       <c r="H375" s="2" t="n"/>
       <c r="I375" s="3" t="n"/>
       <c r="J375" s="3" t="n"/>
+      <c r="K375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="F376" t="inlineStr">
@@ -4638,6 +5021,7 @@
       <c r="H376" s="2" t="n"/>
       <c r="I376" s="3" t="n"/>
       <c r="J376" s="3" t="n"/>
+      <c r="K376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="F377" t="inlineStr">
@@ -4649,6 +5033,7 @@
       <c r="H377" s="2" t="n"/>
       <c r="I377" s="3" t="n"/>
       <c r="J377" s="3" t="n"/>
+      <c r="K377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="F378" t="inlineStr">
@@ -4660,6 +5045,7 @@
       <c r="H378" s="2" t="n"/>
       <c r="I378" s="3" t="n"/>
       <c r="J378" s="3" t="n"/>
+      <c r="K378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="F379" t="inlineStr">
@@ -4671,6 +5057,7 @@
       <c r="H379" s="2" t="n"/>
       <c r="I379" s="3" t="n"/>
       <c r="J379" s="3" t="n"/>
+      <c r="K379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="F380" t="inlineStr">
@@ -4682,6 +5069,7 @@
       <c r="H380" s="2" t="n"/>
       <c r="I380" s="3" t="n"/>
       <c r="J380" s="3" t="n"/>
+      <c r="K380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="F381" t="inlineStr">
@@ -4693,6 +5081,7 @@
       <c r="H381" s="2" t="n"/>
       <c r="I381" s="3" t="n"/>
       <c r="J381" s="3" t="n"/>
+      <c r="K381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="F382" t="inlineStr">
@@ -4704,6 +5093,7 @@
       <c r="H382" s="2" t="n"/>
       <c r="I382" s="3" t="n"/>
       <c r="J382" s="3" t="n"/>
+      <c r="K382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="F383" t="inlineStr">
@@ -4715,6 +5105,7 @@
       <c r="H383" s="2" t="n"/>
       <c r="I383" s="3" t="n"/>
       <c r="J383" s="3" t="n"/>
+      <c r="K383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="F384" t="inlineStr">
@@ -4726,6 +5117,7 @@
       <c r="H384" s="2" t="n"/>
       <c r="I384" s="3" t="n"/>
       <c r="J384" s="3" t="n"/>
+      <c r="K384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="F385" t="inlineStr">
@@ -4737,6 +5129,7 @@
       <c r="H385" s="2" t="n"/>
       <c r="I385" s="3" t="n"/>
       <c r="J385" s="3" t="n"/>
+      <c r="K385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="F386" t="inlineStr">
@@ -4748,6 +5141,7 @@
       <c r="H386" s="2" t="n"/>
       <c r="I386" s="3" t="n"/>
       <c r="J386" s="3" t="n"/>
+      <c r="K386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="F387" t="inlineStr">
@@ -4759,6 +5153,7 @@
       <c r="H387" s="2" t="n"/>
       <c r="I387" s="3" t="n"/>
       <c r="J387" s="3" t="n"/>
+      <c r="K387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="F388" t="inlineStr">
@@ -4770,6 +5165,7 @@
       <c r="H388" s="2" t="n"/>
       <c r="I388" s="3" t="n"/>
       <c r="J388" s="3" t="n"/>
+      <c r="K388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="F389" t="inlineStr">
@@ -4781,6 +5177,7 @@
       <c r="H389" s="2" t="n"/>
       <c r="I389" s="3" t="n"/>
       <c r="J389" s="3" t="n"/>
+      <c r="K389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="F390" t="inlineStr">
@@ -4792,6 +5189,7 @@
       <c r="H390" s="2" t="n"/>
       <c r="I390" s="3" t="n"/>
       <c r="J390" s="3" t="n"/>
+      <c r="K390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="F391" t="inlineStr">
@@ -4803,6 +5201,7 @@
       <c r="H391" s="2" t="n"/>
       <c r="I391" s="3" t="n"/>
       <c r="J391" s="3" t="n"/>
+      <c r="K391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="F392" t="inlineStr">
@@ -4814,6 +5213,7 @@
       <c r="H392" s="2" t="n"/>
       <c r="I392" s="3" t="n"/>
       <c r="J392" s="3" t="n"/>
+      <c r="K392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="F393" t="inlineStr">
@@ -4825,6 +5225,7 @@
       <c r="H393" s="2" t="n"/>
       <c r="I393" s="3" t="n"/>
       <c r="J393" s="3" t="n"/>
+      <c r="K393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="F394" t="inlineStr">
@@ -4836,6 +5237,7 @@
       <c r="H394" s="2" t="n"/>
       <c r="I394" s="3" t="n"/>
       <c r="J394" s="3" t="n"/>
+      <c r="K394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="F395" t="inlineStr">
@@ -4847,6 +5249,7 @@
       <c r="H395" s="2" t="n"/>
       <c r="I395" s="3" t="n"/>
       <c r="J395" s="3" t="n"/>
+      <c r="K395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="F396" t="inlineStr">
@@ -4858,6 +5261,7 @@
       <c r="H396" s="2" t="n"/>
       <c r="I396" s="3" t="n"/>
       <c r="J396" s="3" t="n"/>
+      <c r="K396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="F397" t="inlineStr">
@@ -4869,6 +5273,7 @@
       <c r="H397" s="2" t="n"/>
       <c r="I397" s="3" t="n"/>
       <c r="J397" s="3" t="n"/>
+      <c r="K397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="F398" t="inlineStr">
@@ -4880,6 +5285,7 @@
       <c r="H398" s="2" t="n"/>
       <c r="I398" s="3" t="n"/>
       <c r="J398" s="3" t="n"/>
+      <c r="K398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="F399" t="inlineStr">
@@ -4891,6 +5297,7 @@
       <c r="H399" s="2" t="n"/>
       <c r="I399" s="3" t="n"/>
       <c r="J399" s="3" t="n"/>
+      <c r="K399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="F400" t="inlineStr">
@@ -4902,6 +5309,7 @@
       <c r="H400" s="2" t="n"/>
       <c r="I400" s="3" t="n"/>
       <c r="J400" s="3" t="n"/>
+      <c r="K400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="F401" t="inlineStr">
@@ -4913,6 +5321,7 @@
       <c r="H401" s="2" t="n"/>
       <c r="I401" s="3" t="n"/>
       <c r="J401" s="3" t="n"/>
+      <c r="K401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="F402" t="inlineStr">
@@ -4924,6 +5333,7 @@
       <c r="H402" s="2" t="n"/>
       <c r="I402" s="3" t="n"/>
       <c r="J402" s="3" t="n"/>
+      <c r="K402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="F403" t="inlineStr">
@@ -4935,6 +5345,7 @@
       <c r="H403" s="2" t="n"/>
       <c r="I403" s="3" t="n"/>
       <c r="J403" s="3" t="n"/>
+      <c r="K403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="F404" t="inlineStr">
@@ -4946,6 +5357,7 @@
       <c r="H404" s="2" t="n"/>
       <c r="I404" s="3" t="n"/>
       <c r="J404" s="3" t="n"/>
+      <c r="K404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="F405" t="inlineStr">
@@ -4957,6 +5369,7 @@
       <c r="H405" s="2" t="n"/>
       <c r="I405" s="3" t="n"/>
       <c r="J405" s="3" t="n"/>
+      <c r="K405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="F406" t="inlineStr">
@@ -4968,6 +5381,7 @@
       <c r="H406" s="2" t="n"/>
       <c r="I406" s="3" t="n"/>
       <c r="J406" s="3" t="n"/>
+      <c r="K406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="F407" t="inlineStr">
@@ -4979,6 +5393,7 @@
       <c r="H407" s="2" t="n"/>
       <c r="I407" s="3" t="n"/>
       <c r="J407" s="3" t="n"/>
+      <c r="K407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="F408" t="inlineStr">
@@ -4990,6 +5405,7 @@
       <c r="H408" s="2" t="n"/>
       <c r="I408" s="3" t="n"/>
       <c r="J408" s="3" t="n"/>
+      <c r="K408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="F409" t="inlineStr">
@@ -5001,6 +5417,7 @@
       <c r="H409" s="2" t="n"/>
       <c r="I409" s="3" t="n"/>
       <c r="J409" s="3" t="n"/>
+      <c r="K409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="F410" t="inlineStr">
@@ -5012,6 +5429,7 @@
       <c r="H410" s="2" t="n"/>
       <c r="I410" s="3" t="n"/>
       <c r="J410" s="3" t="n"/>
+      <c r="K410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="F411" t="inlineStr">
@@ -5023,6 +5441,7 @@
       <c r="H411" s="2" t="n"/>
       <c r="I411" s="3" t="n"/>
       <c r="J411" s="3" t="n"/>
+      <c r="K411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="F412" t="inlineStr">
@@ -5034,6 +5453,7 @@
       <c r="H412" s="2" t="n"/>
       <c r="I412" s="3" t="n"/>
       <c r="J412" s="3" t="n"/>
+      <c r="K412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="F413" t="inlineStr">
@@ -5045,6 +5465,7 @@
       <c r="H413" s="2" t="n"/>
       <c r="I413" s="3" t="n"/>
       <c r="J413" s="3" t="n"/>
+      <c r="K413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="F414" t="inlineStr">
@@ -5056,6 +5477,7 @@
       <c r="H414" s="2" t="n"/>
       <c r="I414" s="3" t="n"/>
       <c r="J414" s="3" t="n"/>
+      <c r="K414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="F415" t="inlineStr">
@@ -5067,6 +5489,7 @@
       <c r="H415" s="2" t="n"/>
       <c r="I415" s="3" t="n"/>
       <c r="J415" s="3" t="n"/>
+      <c r="K415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="F416" t="inlineStr">
@@ -5078,6 +5501,7 @@
       <c r="H416" s="2" t="n"/>
       <c r="I416" s="3" t="n"/>
       <c r="J416" s="3" t="n"/>
+      <c r="K416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="F417" t="inlineStr">
@@ -5089,6 +5513,7 @@
       <c r="H417" s="2" t="n"/>
       <c r="I417" s="3" t="n"/>
       <c r="J417" s="3" t="n"/>
+      <c r="K417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="F418" t="inlineStr">
@@ -5100,6 +5525,7 @@
       <c r="H418" s="2" t="n"/>
       <c r="I418" s="3" t="n"/>
       <c r="J418" s="3" t="n"/>
+      <c r="K418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="F419" t="inlineStr">
@@ -5111,6 +5537,7 @@
       <c r="H419" s="2" t="n"/>
       <c r="I419" s="3" t="n"/>
       <c r="J419" s="3" t="n"/>
+      <c r="K419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="F420" t="inlineStr">
@@ -5122,6 +5549,7 @@
       <c r="H420" s="2" t="n"/>
       <c r="I420" s="3" t="n"/>
       <c r="J420" s="3" t="n"/>
+      <c r="K420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="F421" t="inlineStr">
@@ -5133,6 +5561,7 @@
       <c r="H421" s="2" t="n"/>
       <c r="I421" s="3" t="n"/>
       <c r="J421" s="3" t="n"/>
+      <c r="K421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="F422" t="inlineStr">
@@ -5144,6 +5573,7 @@
       <c r="H422" s="2" t="n"/>
       <c r="I422" s="3" t="n"/>
       <c r="J422" s="3" t="n"/>
+      <c r="K422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="F423" t="inlineStr">
@@ -5155,6 +5585,7 @@
       <c r="H423" s="2" t="n"/>
       <c r="I423" s="3" t="n"/>
       <c r="J423" s="3" t="n"/>
+      <c r="K423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="F424" t="inlineStr">
@@ -5166,6 +5597,7 @@
       <c r="H424" s="2" t="n"/>
       <c r="I424" s="3" t="n"/>
       <c r="J424" s="3" t="n"/>
+      <c r="K424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="F425" t="inlineStr">
@@ -5177,6 +5609,7 @@
       <c r="H425" s="2" t="n"/>
       <c r="I425" s="3" t="n"/>
       <c r="J425" s="3" t="n"/>
+      <c r="K425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="F426" t="inlineStr">
@@ -5188,6 +5621,7 @@
       <c r="H426" s="2" t="n"/>
       <c r="I426" s="3" t="n"/>
       <c r="J426" s="3" t="n"/>
+      <c r="K426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="F427" t="inlineStr">
@@ -5199,6 +5633,7 @@
       <c r="H427" s="2" t="n"/>
       <c r="I427" s="3" t="n"/>
       <c r="J427" s="3" t="n"/>
+      <c r="K427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="F428" t="inlineStr">
@@ -5210,6 +5645,7 @@
       <c r="H428" s="2" t="n"/>
       <c r="I428" s="3" t="n"/>
       <c r="J428" s="3" t="n"/>
+      <c r="K428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="F429" t="inlineStr">
@@ -5221,6 +5657,7 @@
       <c r="H429" s="2" t="n"/>
       <c r="I429" s="3" t="n"/>
       <c r="J429" s="3" t="n"/>
+      <c r="K429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="F430" t="inlineStr">
@@ -5232,6 +5669,7 @@
       <c r="H430" s="2" t="n"/>
       <c r="I430" s="3" t="n"/>
       <c r="J430" s="3" t="n"/>
+      <c r="K430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="F431" t="inlineStr">
@@ -5243,6 +5681,7 @@
       <c r="H431" s="2" t="n"/>
       <c r="I431" s="3" t="n"/>
       <c r="J431" s="3" t="n"/>
+      <c r="K431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="F432" t="inlineStr">
@@ -5254,6 +5693,7 @@
       <c r="H432" s="2" t="n"/>
       <c r="I432" s="3" t="n"/>
       <c r="J432" s="3" t="n"/>
+      <c r="K432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="F433" t="inlineStr">
@@ -5265,6 +5705,7 @@
       <c r="H433" s="2" t="n"/>
       <c r="I433" s="3" t="n"/>
       <c r="J433" s="3" t="n"/>
+      <c r="K433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="F434" t="inlineStr">
@@ -5276,6 +5717,7 @@
       <c r="H434" s="2" t="n"/>
       <c r="I434" s="3" t="n"/>
       <c r="J434" s="3" t="n"/>
+      <c r="K434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="F435" t="inlineStr">
@@ -5287,6 +5729,7 @@
       <c r="H435" s="2" t="n"/>
       <c r="I435" s="3" t="n"/>
       <c r="J435" s="3" t="n"/>
+      <c r="K435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="F436" t="inlineStr">
@@ -5298,6 +5741,7 @@
       <c r="H436" s="2" t="n"/>
       <c r="I436" s="3" t="n"/>
       <c r="J436" s="3" t="n"/>
+      <c r="K436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="F437" t="inlineStr">
@@ -5309,6 +5753,7 @@
       <c r="H437" s="2" t="n"/>
       <c r="I437" s="3" t="n"/>
       <c r="J437" s="3" t="n"/>
+      <c r="K437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="F438" t="inlineStr">
@@ -5320,6 +5765,7 @@
       <c r="H438" s="2" t="n"/>
       <c r="I438" s="3" t="n"/>
       <c r="J438" s="3" t="n"/>
+      <c r="K438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="F439" t="inlineStr">
@@ -5331,6 +5777,7 @@
       <c r="H439" s="2" t="n"/>
       <c r="I439" s="3" t="n"/>
       <c r="J439" s="3" t="n"/>
+      <c r="K439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="F440" t="inlineStr">
@@ -5342,6 +5789,7 @@
       <c r="H440" s="2" t="n"/>
       <c r="I440" s="3" t="n"/>
       <c r="J440" s="3" t="n"/>
+      <c r="K440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="F441" t="inlineStr">
@@ -5353,6 +5801,7 @@
       <c r="H441" s="2" t="n"/>
       <c r="I441" s="3" t="n"/>
       <c r="J441" s="3" t="n"/>
+      <c r="K441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="F442" t="inlineStr">
@@ -5364,6 +5813,7 @@
       <c r="H442" s="2" t="n"/>
       <c r="I442" s="3" t="n"/>
       <c r="J442" s="3" t="n"/>
+      <c r="K442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="F443" t="inlineStr">
@@ -5375,6 +5825,7 @@
       <c r="H443" s="2" t="n"/>
       <c r="I443" s="3" t="n"/>
       <c r="J443" s="3" t="n"/>
+      <c r="K443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="F444" t="inlineStr">
@@ -5386,6 +5837,7 @@
       <c r="H444" s="2" t="n"/>
       <c r="I444" s="3" t="n"/>
       <c r="J444" s="3" t="n"/>
+      <c r="K444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="F445" t="inlineStr">
@@ -5397,6 +5849,7 @@
       <c r="H445" s="2" t="n"/>
       <c r="I445" s="3" t="n"/>
       <c r="J445" s="3" t="n"/>
+      <c r="K445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="F446" t="inlineStr">
@@ -5408,6 +5861,7 @@
       <c r="H446" s="2" t="n"/>
       <c r="I446" s="3" t="n"/>
       <c r="J446" s="3" t="n"/>
+      <c r="K446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="F447" t="inlineStr">
@@ -5419,6 +5873,7 @@
       <c r="H447" s="2" t="n"/>
       <c r="I447" s="3" t="n"/>
       <c r="J447" s="3" t="n"/>
+      <c r="K447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="F448" t="inlineStr">
@@ -5430,6 +5885,7 @@
       <c r="H448" s="2" t="n"/>
       <c r="I448" s="3" t="n"/>
       <c r="J448" s="3" t="n"/>
+      <c r="K448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="F449" t="inlineStr">
@@ -5441,6 +5897,7 @@
       <c r="H449" s="2" t="n"/>
       <c r="I449" s="3" t="n"/>
       <c r="J449" s="3" t="n"/>
+      <c r="K449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="F450" t="inlineStr">
@@ -5452,6 +5909,7 @@
       <c r="H450" s="2" t="n"/>
       <c r="I450" s="3" t="n"/>
       <c r="J450" s="3" t="n"/>
+      <c r="K450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="F451" t="inlineStr">
@@ -5463,6 +5921,7 @@
       <c r="H451" s="2" t="n"/>
       <c r="I451" s="3" t="n"/>
       <c r="J451" s="3" t="n"/>
+      <c r="K451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="F452" t="inlineStr">
@@ -5474,6 +5933,7 @@
       <c r="H452" s="2" t="n"/>
       <c r="I452" s="3" t="n"/>
       <c r="J452" s="3" t="n"/>
+      <c r="K452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="F453" t="inlineStr">
@@ -5485,6 +5945,7 @@
       <c r="H453" s="2" t="n"/>
       <c r="I453" s="3" t="n"/>
       <c r="J453" s="3" t="n"/>
+      <c r="K453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="F454" t="inlineStr">
@@ -5496,6 +5957,7 @@
       <c r="H454" s="2" t="n"/>
       <c r="I454" s="3" t="n"/>
       <c r="J454" s="3" t="n"/>
+      <c r="K454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="F455" t="inlineStr">
@@ -5507,6 +5969,7 @@
       <c r="H455" s="2" t="n"/>
       <c r="I455" s="3" t="n"/>
       <c r="J455" s="3" t="n"/>
+      <c r="K455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="F456" t="inlineStr">
@@ -5518,6 +5981,7 @@
       <c r="H456" s="2" t="n"/>
       <c r="I456" s="3" t="n"/>
       <c r="J456" s="3" t="n"/>
+      <c r="K456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="F457" t="inlineStr">
@@ -5529,6 +5993,7 @@
       <c r="H457" s="2" t="n"/>
       <c r="I457" s="3" t="n"/>
       <c r="J457" s="3" t="n"/>
+      <c r="K457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="F458" t="inlineStr">
@@ -5540,6 +6005,7 @@
       <c r="H458" s="2" t="n"/>
       <c r="I458" s="3" t="n"/>
       <c r="J458" s="3" t="n"/>
+      <c r="K458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="F459" t="inlineStr">
@@ -5551,6 +6017,7 @@
       <c r="H459" s="2" t="n"/>
       <c r="I459" s="3" t="n"/>
       <c r="J459" s="3" t="n"/>
+      <c r="K459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="F460" t="inlineStr">
@@ -5562,6 +6029,7 @@
       <c r="H460" s="2" t="n"/>
       <c r="I460" s="3" t="n"/>
       <c r="J460" s="3" t="n"/>
+      <c r="K460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="F461" t="inlineStr">
@@ -5573,6 +6041,7 @@
       <c r="H461" s="2" t="n"/>
       <c r="I461" s="3" t="n"/>
       <c r="J461" s="3" t="n"/>
+      <c r="K461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="F462" t="inlineStr">
@@ -5584,6 +6053,7 @@
       <c r="H462" s="2" t="n"/>
       <c r="I462" s="3" t="n"/>
       <c r="J462" s="3" t="n"/>
+      <c r="K462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="F463" t="inlineStr">
@@ -5595,6 +6065,7 @@
       <c r="H463" s="2" t="n"/>
       <c r="I463" s="3" t="n"/>
       <c r="J463" s="3" t="n"/>
+      <c r="K463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="F464" t="inlineStr">
@@ -5606,6 +6077,7 @@
       <c r="H464" s="2" t="n"/>
       <c r="I464" s="3" t="n"/>
       <c r="J464" s="3" t="n"/>
+      <c r="K464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="F465" t="inlineStr">
@@ -5617,6 +6089,7 @@
       <c r="H465" s="2" t="n"/>
       <c r="I465" s="3" t="n"/>
       <c r="J465" s="3" t="n"/>
+      <c r="K465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="F466" t="inlineStr">
@@ -5628,6 +6101,7 @@
       <c r="H466" s="2" t="n"/>
       <c r="I466" s="3" t="n"/>
       <c r="J466" s="3" t="n"/>
+      <c r="K466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="F467" t="inlineStr">
@@ -5639,6 +6113,7 @@
       <c r="H467" s="2" t="n"/>
       <c r="I467" s="3" t="n"/>
       <c r="J467" s="3" t="n"/>
+      <c r="K467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="F468" t="inlineStr">
@@ -5650,6 +6125,7 @@
       <c r="H468" s="2" t="n"/>
       <c r="I468" s="3" t="n"/>
       <c r="J468" s="3" t="n"/>
+      <c r="K468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="F469" t="inlineStr">
@@ -5661,6 +6137,7 @@
       <c r="H469" s="2" t="n"/>
       <c r="I469" s="3" t="n"/>
       <c r="J469" s="3" t="n"/>
+      <c r="K469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="F470" t="inlineStr">
@@ -5672,6 +6149,7 @@
       <c r="H470" s="2" t="n"/>
       <c r="I470" s="3" t="n"/>
       <c r="J470" s="3" t="n"/>
+      <c r="K470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="F471" t="inlineStr">
@@ -5683,6 +6161,7 @@
       <c r="H471" s="2" t="n"/>
       <c r="I471" s="3" t="n"/>
       <c r="J471" s="3" t="n"/>
+      <c r="K471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="F472" t="inlineStr">
@@ -5694,6 +6173,7 @@
       <c r="H472" s="2" t="n"/>
       <c r="I472" s="3" t="n"/>
       <c r="J472" s="3" t="n"/>
+      <c r="K472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="F473" t="inlineStr">
@@ -5705,6 +6185,7 @@
       <c r="H473" s="2" t="n"/>
       <c r="I473" s="3" t="n"/>
       <c r="J473" s="3" t="n"/>
+      <c r="K473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="F474" t="inlineStr">
@@ -5716,6 +6197,7 @@
       <c r="H474" s="2" t="n"/>
       <c r="I474" s="3" t="n"/>
       <c r="J474" s="3" t="n"/>
+      <c r="K474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="F475" t="inlineStr">
@@ -5727,6 +6209,7 @@
       <c r="H475" s="2" t="n"/>
       <c r="I475" s="3" t="n"/>
       <c r="J475" s="3" t="n"/>
+      <c r="K475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="F476" t="inlineStr">
@@ -5738,6 +6221,7 @@
       <c r="H476" s="2" t="n"/>
       <c r="I476" s="3" t="n"/>
       <c r="J476" s="3" t="n"/>
+      <c r="K476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="F477" t="inlineStr">
@@ -5749,6 +6233,7 @@
       <c r="H477" s="2" t="n"/>
       <c r="I477" s="3" t="n"/>
       <c r="J477" s="3" t="n"/>
+      <c r="K477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="F478" t="inlineStr">
@@ -5760,6 +6245,7 @@
       <c r="H478" s="2" t="n"/>
       <c r="I478" s="3" t="n"/>
       <c r="J478" s="3" t="n"/>
+      <c r="K478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="F479" t="inlineStr">
@@ -5771,6 +6257,7 @@
       <c r="H479" s="2" t="n"/>
       <c r="I479" s="3" t="n"/>
       <c r="J479" s="3" t="n"/>
+      <c r="K479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="F480" t="inlineStr">
@@ -5782,6 +6269,7 @@
       <c r="H480" s="2" t="n"/>
       <c r="I480" s="3" t="n"/>
       <c r="J480" s="3" t="n"/>
+      <c r="K480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="F481" t="inlineStr">
@@ -5793,6 +6281,7 @@
       <c r="H481" s="2" t="n"/>
       <c r="I481" s="3" t="n"/>
       <c r="J481" s="3" t="n"/>
+      <c r="K481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="F482" t="inlineStr">
@@ -5804,6 +6293,7 @@
       <c r="H482" s="2" t="n"/>
       <c r="I482" s="3" t="n"/>
       <c r="J482" s="3" t="n"/>
+      <c r="K482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="F483" t="inlineStr">
@@ -5815,6 +6305,7 @@
       <c r="H483" s="2" t="n"/>
       <c r="I483" s="3" t="n"/>
       <c r="J483" s="3" t="n"/>
+      <c r="K483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="F484" t="inlineStr">
@@ -5826,6 +6317,7 @@
       <c r="H484" s="2" t="n"/>
       <c r="I484" s="3" t="n"/>
       <c r="J484" s="3" t="n"/>
+      <c r="K484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="F485" t="inlineStr">
@@ -5837,6 +6329,7 @@
       <c r="H485" s="2" t="n"/>
       <c r="I485" s="3" t="n"/>
       <c r="J485" s="3" t="n"/>
+      <c r="K485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="F486" t="inlineStr">
@@ -5848,6 +6341,7 @@
       <c r="H486" s="2" t="n"/>
       <c r="I486" s="3" t="n"/>
       <c r="J486" s="3" t="n"/>
+      <c r="K486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="F487" t="inlineStr">
@@ -5859,6 +6353,7 @@
       <c r="H487" s="2" t="n"/>
       <c r="I487" s="3" t="n"/>
       <c r="J487" s="3" t="n"/>
+      <c r="K487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="F488" t="inlineStr">
@@ -5870,6 +6365,7 @@
       <c r="H488" s="2" t="n"/>
       <c r="I488" s="3" t="n"/>
       <c r="J488" s="3" t="n"/>
+      <c r="K488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="F489" t="inlineStr">
@@ -5881,6 +6377,7 @@
       <c r="H489" s="2" t="n"/>
       <c r="I489" s="3" t="n"/>
       <c r="J489" s="3" t="n"/>
+      <c r="K489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="F490" t="inlineStr">
@@ -5892,6 +6389,7 @@
       <c r="H490" s="2" t="n"/>
       <c r="I490" s="3" t="n"/>
       <c r="J490" s="3" t="n"/>
+      <c r="K490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="F491" t="inlineStr">
@@ -5903,6 +6401,7 @@
       <c r="H491" s="2" t="n"/>
       <c r="I491" s="3" t="n"/>
       <c r="J491" s="3" t="n"/>
+      <c r="K491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="F492" t="inlineStr">
@@ -5914,6 +6413,7 @@
       <c r="H492" s="2" t="n"/>
       <c r="I492" s="3" t="n"/>
       <c r="J492" s="3" t="n"/>
+      <c r="K492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="F493" t="inlineStr">
@@ -5925,6 +6425,7 @@
       <c r="H493" s="2" t="n"/>
       <c r="I493" s="3" t="n"/>
       <c r="J493" s="3" t="n"/>
+      <c r="K493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="F494" t="inlineStr">
@@ -5936,6 +6437,7 @@
       <c r="H494" s="2" t="n"/>
       <c r="I494" s="3" t="n"/>
       <c r="J494" s="3" t="n"/>
+      <c r="K494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="F495" t="inlineStr">
@@ -5947,6 +6449,7 @@
       <c r="H495" s="2" t="n"/>
       <c r="I495" s="3" t="n"/>
       <c r="J495" s="3" t="n"/>
+      <c r="K495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="F496" t="inlineStr">
@@ -5958,6 +6461,7 @@
       <c r="H496" s="2" t="n"/>
       <c r="I496" s="3" t="n"/>
       <c r="J496" s="3" t="n"/>
+      <c r="K496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="F497" t="inlineStr">
@@ -5969,6 +6473,7 @@
       <c r="H497" s="2" t="n"/>
       <c r="I497" s="3" t="n"/>
       <c r="J497" s="3" t="n"/>
+      <c r="K497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="F498" t="inlineStr">
@@ -5980,6 +6485,7 @@
       <c r="H498" s="2" t="n"/>
       <c r="I498" s="3" t="n"/>
       <c r="J498" s="3" t="n"/>
+      <c r="K498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="F499" t="inlineStr">
@@ -5991,6 +6497,7 @@
       <c r="H499" s="2" t="n"/>
       <c r="I499" s="3" t="n"/>
       <c r="J499" s="3" t="n"/>
+      <c r="K499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="F500" t="inlineStr">
@@ -6002,6 +6509,7 @@
       <c r="H500" s="2" t="n"/>
       <c r="I500" s="3" t="n"/>
       <c r="J500" s="3" t="n"/>
+      <c r="K500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="F501" t="inlineStr">
@@ -6013,6 +6521,7 @@
       <c r="H501" s="2" t="n"/>
       <c r="I501" s="3" t="n"/>
       <c r="J501" s="3" t="n"/>
+      <c r="K501" s="3" t="n"/>
     </row>
     <row r="502">
       <c r="F502" t="inlineStr">
@@ -6024,6 +6533,7 @@
       <c r="H502" s="2" t="n"/>
       <c r="I502" s="3" t="n"/>
       <c r="J502" s="3" t="n"/>
+      <c r="K502" s="3" t="n"/>
     </row>
     <row r="503">
       <c r="F503" t="inlineStr">
@@ -6035,6 +6545,7 @@
       <c r="H503" s="2" t="n"/>
       <c r="I503" s="3" t="n"/>
       <c r="J503" s="3" t="n"/>
+      <c r="K503" s="3" t="n"/>
     </row>
     <row r="504">
       <c r="F504" t="inlineStr">
@@ -6046,6 +6557,7 @@
       <c r="H504" s="2" t="n"/>
       <c r="I504" s="3" t="n"/>
       <c r="J504" s="3" t="n"/>
+      <c r="K504" s="3" t="n"/>
     </row>
     <row r="505">
       <c r="F505" t="inlineStr">
@@ -6057,6 +6569,7 @@
       <c r="H505" s="2" t="n"/>
       <c r="I505" s="3" t="n"/>
       <c r="J505" s="3" t="n"/>
+      <c r="K505" s="3" t="n"/>
     </row>
     <row r="506">
       <c r="F506" t="inlineStr">
@@ -6068,6 +6581,7 @@
       <c r="H506" s="2" t="n"/>
       <c r="I506" s="3" t="n"/>
       <c r="J506" s="3" t="n"/>
+      <c r="K506" s="3" t="n"/>
     </row>
     <row r="507">
       <c r="F507" t="inlineStr">
@@ -6079,6 +6593,7 @@
       <c r="H507" s="2" t="n"/>
       <c r="I507" s="3" t="n"/>
       <c r="J507" s="3" t="n"/>
+      <c r="K507" s="3" t="n"/>
     </row>
     <row r="508">
       <c r="F508" t="inlineStr">
@@ -6090,6 +6605,7 @@
       <c r="H508" s="2" t="n"/>
       <c r="I508" s="3" t="n"/>
       <c r="J508" s="3" t="n"/>
+      <c r="K508" s="3" t="n"/>
     </row>
     <row r="509">
       <c r="F509" t="inlineStr">
@@ -6101,6 +6617,7 @@
       <c r="H509" s="2" t="n"/>
       <c r="I509" s="3" t="n"/>
       <c r="J509" s="3" t="n"/>
+      <c r="K509" s="3" t="n"/>
     </row>
     <row r="510">
       <c r="F510" t="inlineStr">
@@ -6112,6 +6629,7 @@
       <c r="H510" s="2" t="n"/>
       <c r="I510" s="3" t="n"/>
       <c r="J510" s="3" t="n"/>
+      <c r="K510" s="3" t="n"/>
     </row>
     <row r="511">
       <c r="F511" t="inlineStr">
@@ -6123,6 +6641,7 @@
       <c r="H511" s="2" t="n"/>
       <c r="I511" s="3" t="n"/>
       <c r="J511" s="3" t="n"/>
+      <c r="K511" s="3" t="n"/>
     </row>
     <row r="512">
       <c r="F512" t="inlineStr">
@@ -6134,6 +6653,7 @@
       <c r="H512" s="2" t="n"/>
       <c r="I512" s="3" t="n"/>
       <c r="J512" s="3" t="n"/>
+      <c r="K512" s="3" t="n"/>
     </row>
     <row r="513">
       <c r="F513" t="inlineStr">
@@ -6145,6 +6665,7 @@
       <c r="H513" s="2" t="n"/>
       <c r="I513" s="3" t="n"/>
       <c r="J513" s="3" t="n"/>
+      <c r="K513" s="3" t="n"/>
     </row>
     <row r="514">
       <c r="F514" t="inlineStr">
@@ -6156,6 +6677,7 @@
       <c r="H514" s="2" t="n"/>
       <c r="I514" s="3" t="n"/>
       <c r="J514" s="3" t="n"/>
+      <c r="K514" s="3" t="n"/>
     </row>
     <row r="515">
       <c r="F515" t="inlineStr">
@@ -6167,6 +6689,7 @@
       <c r="H515" s="2" t="n"/>
       <c r="I515" s="3" t="n"/>
       <c r="J515" s="3" t="n"/>
+      <c r="K515" s="3" t="n"/>
     </row>
     <row r="516">
       <c r="F516" t="inlineStr">
@@ -6178,6 +6701,7 @@
       <c r="H516" s="2" t="n"/>
       <c r="I516" s="3" t="n"/>
       <c r="J516" s="3" t="n"/>
+      <c r="K516" s="3" t="n"/>
     </row>
     <row r="517">
       <c r="F517" t="inlineStr">
@@ -6189,6 +6713,7 @@
       <c r="H517" s="2" t="n"/>
       <c r="I517" s="3" t="n"/>
       <c r="J517" s="3" t="n"/>
+      <c r="K517" s="3" t="n"/>
     </row>
     <row r="518">
       <c r="F518" t="inlineStr">
@@ -6200,6 +6725,7 @@
       <c r="H518" s="2" t="n"/>
       <c r="I518" s="3" t="n"/>
       <c r="J518" s="3" t="n"/>
+      <c r="K518" s="3" t="n"/>
     </row>
     <row r="519">
       <c r="F519" t="inlineStr">
@@ -6211,6 +6737,7 @@
       <c r="H519" s="2" t="n"/>
       <c r="I519" s="3" t="n"/>
       <c r="J519" s="3" t="n"/>
+      <c r="K519" s="3" t="n"/>
     </row>
     <row r="520">
       <c r="F520" t="inlineStr">
@@ -6222,6 +6749,7 @@
       <c r="H520" s="2" t="n"/>
       <c r="I520" s="3" t="n"/>
       <c r="J520" s="3" t="n"/>
+      <c r="K520" s="3" t="n"/>
     </row>
     <row r="521">
       <c r="F521" t="inlineStr">
@@ -6233,6 +6761,7 @@
       <c r="H521" s="2" t="n"/>
       <c r="I521" s="3" t="n"/>
       <c r="J521" s="3" t="n"/>
+      <c r="K521" s="3" t="n"/>
     </row>
     <row r="522">
       <c r="F522" t="inlineStr">
@@ -6244,6 +6773,7 @@
       <c r="H522" s="2" t="n"/>
       <c r="I522" s="3" t="n"/>
       <c r="J522" s="3" t="n"/>
+      <c r="K522" s="3" t="n"/>
     </row>
     <row r="523">
       <c r="F523" t="inlineStr">
@@ -6255,6 +6785,7 @@
       <c r="H523" s="2" t="n"/>
       <c r="I523" s="3" t="n"/>
       <c r="J523" s="3" t="n"/>
+      <c r="K523" s="3" t="n"/>
     </row>
     <row r="524">
       <c r="F524" t="inlineStr">
@@ -6266,6 +6797,7 @@
       <c r="H524" s="2" t="n"/>
       <c r="I524" s="3" t="n"/>
       <c r="J524" s="3" t="n"/>
+      <c r="K524" s="3" t="n"/>
     </row>
     <row r="525">
       <c r="F525" t="inlineStr">
@@ -6277,6 +6809,7 @@
       <c r="H525" s="2" t="n"/>
       <c r="I525" s="3" t="n"/>
       <c r="J525" s="3" t="n"/>
+      <c r="K525" s="3" t="n"/>
     </row>
     <row r="526">
       <c r="F526" t="inlineStr">
@@ -6288,6 +6821,7 @@
       <c r="H526" s="2" t="n"/>
       <c r="I526" s="3" t="n"/>
       <c r="J526" s="3" t="n"/>
+      <c r="K526" s="3" t="n"/>
     </row>
     <row r="527">
       <c r="F527" t="inlineStr">
@@ -6299,6 +6833,7 @@
       <c r="H527" s="2" t="n"/>
       <c r="I527" s="3" t="n"/>
       <c r="J527" s="3" t="n"/>
+      <c r="K527" s="3" t="n"/>
     </row>
     <row r="528">
       <c r="F528" t="inlineStr">
@@ -6310,6 +6845,7 @@
       <c r="H528" s="2" t="n"/>
       <c r="I528" s="3" t="n"/>
       <c r="J528" s="3" t="n"/>
+      <c r="K528" s="3" t="n"/>
     </row>
     <row r="529">
       <c r="F529" t="inlineStr">
@@ -6321,6 +6857,7 @@
       <c r="H529" s="2" t="n"/>
       <c r="I529" s="3" t="n"/>
       <c r="J529" s="3" t="n"/>
+      <c r="K529" s="3" t="n"/>
     </row>
     <row r="530">
       <c r="F530" t="inlineStr">
@@ -6332,6 +6869,7 @@
       <c r="H530" s="2" t="n"/>
       <c r="I530" s="3" t="n"/>
       <c r="J530" s="3" t="n"/>
+      <c r="K530" s="3" t="n"/>
     </row>
     <row r="531">
       <c r="F531" t="inlineStr">
@@ -6343,6 +6881,7 @@
       <c r="H531" s="2" t="n"/>
       <c r="I531" s="3" t="n"/>
       <c r="J531" s="3" t="n"/>
+      <c r="K531" s="3" t="n"/>
     </row>
     <row r="532">
       <c r="F532" t="inlineStr">
@@ -6354,6 +6893,7 @@
       <c r="H532" s="2" t="n"/>
       <c r="I532" s="3" t="n"/>
       <c r="J532" s="3" t="n"/>
+      <c r="K532" s="3" t="n"/>
     </row>
     <row r="533">
       <c r="F533" t="inlineStr">
@@ -6365,6 +6905,7 @@
       <c r="H533" s="2" t="n"/>
       <c r="I533" s="3" t="n"/>
       <c r="J533" s="3" t="n"/>
+      <c r="K533" s="3" t="n"/>
     </row>
     <row r="534">
       <c r="F534" t="inlineStr">
@@ -6376,6 +6917,7 @@
       <c r="H534" s="2" t="n"/>
       <c r="I534" s="3" t="n"/>
       <c r="J534" s="3" t="n"/>
+      <c r="K534" s="3" t="n"/>
     </row>
     <row r="535">
       <c r="F535" t="inlineStr">
@@ -6387,6 +6929,7 @@
       <c r="H535" s="2" t="n"/>
       <c r="I535" s="3" t="n"/>
       <c r="J535" s="3" t="n"/>
+      <c r="K535" s="3" t="n"/>
     </row>
     <row r="536">
       <c r="F536" t="inlineStr">
@@ -6398,6 +6941,7 @@
       <c r="H536" s="2" t="n"/>
       <c r="I536" s="3" t="n"/>
       <c r="J536" s="3" t="n"/>
+      <c r="K536" s="3" t="n"/>
     </row>
     <row r="537">
       <c r="F537" t="inlineStr">
@@ -6409,6 +6953,7 @@
       <c r="H537" s="2" t="n"/>
       <c r="I537" s="3" t="n"/>
       <c r="J537" s="3" t="n"/>
+      <c r="K537" s="3" t="n"/>
     </row>
     <row r="538">
       <c r="F538" t="inlineStr">
@@ -6420,6 +6965,7 @@
       <c r="H538" s="2" t="n"/>
       <c r="I538" s="3" t="n"/>
       <c r="J538" s="3" t="n"/>
+      <c r="K538" s="3" t="n"/>
     </row>
     <row r="539">
       <c r="F539" t="inlineStr">
@@ -6431,6 +6977,7 @@
       <c r="H539" s="2" t="n"/>
       <c r="I539" s="3" t="n"/>
       <c r="J539" s="3" t="n"/>
+      <c r="K539" s="3" t="n"/>
     </row>
     <row r="540">
       <c r="F540" t="inlineStr">
@@ -6442,6 +6989,7 @@
       <c r="H540" s="2" t="n"/>
       <c r="I540" s="3" t="n"/>
       <c r="J540" s="3" t="n"/>
+      <c r="K540" s="3" t="n"/>
     </row>
     <row r="541">
       <c r="F541" t="inlineStr">
@@ -6453,6 +7001,7 @@
       <c r="H541" s="2" t="n"/>
       <c r="I541" s="3" t="n"/>
       <c r="J541" s="3" t="n"/>
+      <c r="K541" s="3" t="n"/>
     </row>
     <row r="542">
       <c r="F542" t="inlineStr">
@@ -6464,6 +7013,7 @@
       <c r="H542" s="2" t="n"/>
       <c r="I542" s="3" t="n"/>
       <c r="J542" s="3" t="n"/>
+      <c r="K542" s="3" t="n"/>
     </row>
     <row r="543">
       <c r="F543" t="inlineStr">
@@ -6475,6 +7025,7 @@
       <c r="H543" s="2" t="n"/>
       <c r="I543" s="3" t="n"/>
       <c r="J543" s="3" t="n"/>
+      <c r="K543" s="3" t="n"/>
     </row>
     <row r="544">
       <c r="F544" t="inlineStr">
@@ -6486,6 +7037,7 @@
       <c r="H544" s="2" t="n"/>
       <c r="I544" s="3" t="n"/>
       <c r="J544" s="3" t="n"/>
+      <c r="K544" s="3" t="n"/>
     </row>
     <row r="545">
       <c r="F545" t="inlineStr">
@@ -6497,6 +7049,7 @@
       <c r="H545" s="2" t="n"/>
       <c r="I545" s="3" t="n"/>
       <c r="J545" s="3" t="n"/>
+      <c r="K545" s="3" t="n"/>
     </row>
     <row r="546">
       <c r="F546" t="inlineStr">
@@ -6508,6 +7061,7 @@
       <c r="H546" s="2" t="n"/>
       <c r="I546" s="3" t="n"/>
       <c r="J546" s="3" t="n"/>
+      <c r="K546" s="3" t="n"/>
     </row>
     <row r="547">
       <c r="F547" t="inlineStr">
@@ -6519,6 +7073,7 @@
       <c r="H547" s="2" t="n"/>
       <c r="I547" s="3" t="n"/>
       <c r="J547" s="3" t="n"/>
+      <c r="K547" s="3" t="n"/>
     </row>
     <row r="548">
       <c r="F548" t="inlineStr">
@@ -6530,6 +7085,7 @@
       <c r="H548" s="2" t="n"/>
       <c r="I548" s="3" t="n"/>
       <c r="J548" s="3" t="n"/>
+      <c r="K548" s="3" t="n"/>
     </row>
     <row r="549">
       <c r="F549" t="inlineStr">
@@ -6541,6 +7097,7 @@
       <c r="H549" s="2" t="n"/>
       <c r="I549" s="3" t="n"/>
       <c r="J549" s="3" t="n"/>
+      <c r="K549" s="3" t="n"/>
     </row>
     <row r="550">
       <c r="F550" t="inlineStr">
@@ -6552,6 +7109,7 @@
       <c r="H550" s="2" t="n"/>
       <c r="I550" s="3" t="n"/>
       <c r="J550" s="3" t="n"/>
+      <c r="K550" s="3" t="n"/>
     </row>
     <row r="551">
       <c r="F551" t="inlineStr">
@@ -6563,6 +7121,7 @@
       <c r="H551" s="2" t="n"/>
       <c r="I551" s="3" t="n"/>
       <c r="J551" s="3" t="n"/>
+      <c r="K551" s="3" t="n"/>
     </row>
     <row r="552">
       <c r="F552" t="inlineStr">
@@ -6574,6 +7133,7 @@
       <c r="H552" s="2" t="n"/>
       <c r="I552" s="3" t="n"/>
       <c r="J552" s="3" t="n"/>
+      <c r="K552" s="3" t="n"/>
     </row>
     <row r="553">
       <c r="F553" t="inlineStr">
@@ -6585,6 +7145,7 @@
       <c r="H553" s="2" t="n"/>
       <c r="I553" s="3" t="n"/>
       <c r="J553" s="3" t="n"/>
+      <c r="K553" s="3" t="n"/>
     </row>
     <row r="554">
       <c r="F554" t="inlineStr">
@@ -6596,6 +7157,7 @@
       <c r="H554" s="2" t="n"/>
       <c r="I554" s="3" t="n"/>
       <c r="J554" s="3" t="n"/>
+      <c r="K554" s="3" t="n"/>
     </row>
     <row r="555">
       <c r="F555" t="inlineStr">
@@ -6607,6 +7169,7 @@
       <c r="H555" s="2" t="n"/>
       <c r="I555" s="3" t="n"/>
       <c r="J555" s="3" t="n"/>
+      <c r="K555" s="3" t="n"/>
     </row>
     <row r="556">
       <c r="F556" t="inlineStr">
@@ -6618,6 +7181,7 @@
       <c r="H556" s="2" t="n"/>
       <c r="I556" s="3" t="n"/>
       <c r="J556" s="3" t="n"/>
+      <c r="K556" s="3" t="n"/>
     </row>
     <row r="557">
       <c r="F557" t="inlineStr">
@@ -6629,6 +7193,7 @@
       <c r="H557" s="2" t="n"/>
       <c r="I557" s="3" t="n"/>
       <c r="J557" s="3" t="n"/>
+      <c r="K557" s="3" t="n"/>
     </row>
     <row r="558">
       <c r="F558" t="inlineStr">
@@ -6640,6 +7205,7 @@
       <c r="H558" s="2" t="n"/>
       <c r="I558" s="3" t="n"/>
       <c r="J558" s="3" t="n"/>
+      <c r="K558" s="3" t="n"/>
     </row>
     <row r="559">
       <c r="F559" t="inlineStr">
@@ -6651,6 +7217,7 @@
       <c r="H559" s="2" t="n"/>
       <c r="I559" s="3" t="n"/>
       <c r="J559" s="3" t="n"/>
+      <c r="K559" s="3" t="n"/>
     </row>
     <row r="560">
       <c r="F560" t="inlineStr">
@@ -6662,6 +7229,7 @@
       <c r="H560" s="2" t="n"/>
       <c r="I560" s="3" t="n"/>
       <c r="J560" s="3" t="n"/>
+      <c r="K560" s="3" t="n"/>
     </row>
     <row r="561">
       <c r="F561" t="inlineStr">
@@ -6673,6 +7241,7 @@
       <c r="H561" s="2" t="n"/>
       <c r="I561" s="3" t="n"/>
       <c r="J561" s="3" t="n"/>
+      <c r="K561" s="3" t="n"/>
     </row>
     <row r="562">
       <c r="F562" t="inlineStr">
@@ -6684,6 +7253,7 @@
       <c r="H562" s="2" t="n"/>
       <c r="I562" s="3" t="n"/>
       <c r="J562" s="3" t="n"/>
+      <c r="K562" s="3" t="n"/>
     </row>
     <row r="563">
       <c r="F563" t="inlineStr">
@@ -6695,6 +7265,7 @@
       <c r="H563" s="2" t="n"/>
       <c r="I563" s="3" t="n"/>
       <c r="J563" s="3" t="n"/>
+      <c r="K563" s="3" t="n"/>
     </row>
     <row r="564">
       <c r="F564" t="inlineStr">
@@ -6706,6 +7277,7 @@
       <c r="H564" s="2" t="n"/>
       <c r="I564" s="3" t="n"/>
       <c r="J564" s="3" t="n"/>
+      <c r="K564" s="3" t="n"/>
     </row>
     <row r="565">
       <c r="F565" t="inlineStr">
@@ -6717,6 +7289,7 @@
       <c r="H565" s="2" t="n"/>
       <c r="I565" s="3" t="n"/>
       <c r="J565" s="3" t="n"/>
+      <c r="K565" s="3" t="n"/>
     </row>
     <row r="566">
       <c r="F566" t="inlineStr">
@@ -6728,6 +7301,7 @@
       <c r="H566" s="2" t="n"/>
       <c r="I566" s="3" t="n"/>
       <c r="J566" s="3" t="n"/>
+      <c r="K566" s="3" t="n"/>
     </row>
     <row r="567">
       <c r="F567" t="inlineStr">
@@ -6739,6 +7313,7 @@
       <c r="H567" s="2" t="n"/>
       <c r="I567" s="3" t="n"/>
       <c r="J567" s="3" t="n"/>
+      <c r="K567" s="3" t="n"/>
     </row>
     <row r="568">
       <c r="F568" t="inlineStr">
@@ -6750,6 +7325,7 @@
       <c r="H568" s="2" t="n"/>
       <c r="I568" s="3" t="n"/>
       <c r="J568" s="3" t="n"/>
+      <c r="K568" s="3" t="n"/>
     </row>
     <row r="569">
       <c r="F569" t="inlineStr">
@@ -6761,6 +7337,7 @@
       <c r="H569" s="2" t="n"/>
       <c r="I569" s="3" t="n"/>
       <c r="J569" s="3" t="n"/>
+      <c r="K569" s="3" t="n"/>
     </row>
     <row r="570">
       <c r="F570" t="inlineStr">
@@ -6772,6 +7349,7 @@
       <c r="H570" s="2" t="n"/>
       <c r="I570" s="3" t="n"/>
       <c r="J570" s="3" t="n"/>
+      <c r="K570" s="3" t="n"/>
     </row>
     <row r="571">
       <c r="F571" t="inlineStr">
@@ -6783,6 +7361,7 @@
       <c r="H571" s="2" t="n"/>
       <c r="I571" s="3" t="n"/>
       <c r="J571" s="3" t="n"/>
+      <c r="K571" s="3" t="n"/>
     </row>
     <row r="572">
       <c r="F572" t="inlineStr">
@@ -6794,6 +7373,7 @@
       <c r="H572" s="2" t="n"/>
       <c r="I572" s="3" t="n"/>
       <c r="J572" s="3" t="n"/>
+      <c r="K572" s="3" t="n"/>
     </row>
     <row r="573">
       <c r="F573" t="inlineStr">
@@ -6805,6 +7385,7 @@
       <c r="H573" s="2" t="n"/>
       <c r="I573" s="3" t="n"/>
       <c r="J573" s="3" t="n"/>
+      <c r="K573" s="3" t="n"/>
     </row>
     <row r="574">
       <c r="F574" t="inlineStr">
@@ -6816,6 +7397,7 @@
       <c r="H574" s="2" t="n"/>
       <c r="I574" s="3" t="n"/>
       <c r="J574" s="3" t="n"/>
+      <c r="K574" s="3" t="n"/>
     </row>
     <row r="575">
       <c r="F575" t="inlineStr">
@@ -6827,6 +7409,7 @@
       <c r="H575" s="2" t="n"/>
       <c r="I575" s="3" t="n"/>
       <c r="J575" s="3" t="n"/>
+      <c r="K575" s="3" t="n"/>
     </row>
     <row r="576">
       <c r="F576" t="inlineStr">
@@ -6838,6 +7421,7 @@
       <c r="H576" s="2" t="n"/>
       <c r="I576" s="3" t="n"/>
       <c r="J576" s="3" t="n"/>
+      <c r="K576" s="3" t="n"/>
     </row>
     <row r="577">
       <c r="F577" t="inlineStr">
@@ -6849,6 +7433,7 @@
       <c r="H577" s="2" t="n"/>
       <c r="I577" s="3" t="n"/>
       <c r="J577" s="3" t="n"/>
+      <c r="K577" s="3" t="n"/>
     </row>
     <row r="578">
       <c r="F578" t="inlineStr">
@@ -6860,6 +7445,7 @@
       <c r="H578" s="2" t="n"/>
       <c r="I578" s="3" t="n"/>
       <c r="J578" s="3" t="n"/>
+      <c r="K578" s="3" t="n"/>
     </row>
     <row r="579">
       <c r="F579" t="inlineStr">
@@ -6871,6 +7457,7 @@
       <c r="H579" s="2" t="n"/>
       <c r="I579" s="3" t="n"/>
       <c r="J579" s="3" t="n"/>
+      <c r="K579" s="3" t="n"/>
     </row>
     <row r="580">
       <c r="F580" t="inlineStr">
@@ -6882,6 +7469,7 @@
       <c r="H580" s="2" t="n"/>
       <c r="I580" s="3" t="n"/>
       <c r="J580" s="3" t="n"/>
+      <c r="K580" s="3" t="n"/>
     </row>
     <row r="581">
       <c r="F581" t="inlineStr">
@@ -6893,6 +7481,7 @@
       <c r="H581" s="2" t="n"/>
       <c r="I581" s="3" t="n"/>
       <c r="J581" s="3" t="n"/>
+      <c r="K581" s="3" t="n"/>
     </row>
     <row r="582">
       <c r="F582" t="inlineStr">
@@ -6904,6 +7493,7 @@
       <c r="H582" s="2" t="n"/>
       <c r="I582" s="3" t="n"/>
       <c r="J582" s="3" t="n"/>
+      <c r="K582" s="3" t="n"/>
     </row>
     <row r="583">
       <c r="F583" t="inlineStr">
@@ -6915,6 +7505,7 @@
       <c r="H583" s="2" t="n"/>
       <c r="I583" s="3" t="n"/>
       <c r="J583" s="3" t="n"/>
+      <c r="K583" s="3" t="n"/>
     </row>
     <row r="584">
       <c r="F584" t="inlineStr">
@@ -6926,6 +7517,7 @@
       <c r="H584" s="2" t="n"/>
       <c r="I584" s="3" t="n"/>
       <c r="J584" s="3" t="n"/>
+      <c r="K584" s="3" t="n"/>
     </row>
     <row r="585">
       <c r="F585" t="inlineStr">
@@ -6937,6 +7529,7 @@
       <c r="H585" s="2" t="n"/>
       <c r="I585" s="3" t="n"/>
       <c r="J585" s="3" t="n"/>
+      <c r="K585" s="3" t="n"/>
     </row>
     <row r="586">
       <c r="F586" t="inlineStr">
@@ -6948,6 +7541,7 @@
       <c r="H586" s="2" t="n"/>
       <c r="I586" s="3" t="n"/>
       <c r="J586" s="3" t="n"/>
+      <c r="K586" s="3" t="n"/>
     </row>
     <row r="587">
       <c r="F587" t="inlineStr">
@@ -6959,6 +7553,7 @@
       <c r="H587" s="2" t="n"/>
       <c r="I587" s="3" t="n"/>
       <c r="J587" s="3" t="n"/>
+      <c r="K587" s="3" t="n"/>
     </row>
     <row r="588">
       <c r="F588" t="inlineStr">
@@ -6970,6 +7565,7 @@
       <c r="H588" s="2" t="n"/>
       <c r="I588" s="3" t="n"/>
       <c r="J588" s="3" t="n"/>
+      <c r="K588" s="3" t="n"/>
     </row>
     <row r="589">
       <c r="F589" t="inlineStr">
@@ -6981,6 +7577,7 @@
       <c r="H589" s="2" t="n"/>
       <c r="I589" s="3" t="n"/>
       <c r="J589" s="3" t="n"/>
+      <c r="K589" s="3" t="n"/>
     </row>
     <row r="590">
       <c r="F590" t="inlineStr">
@@ -6992,6 +7589,7 @@
       <c r="H590" s="2" t="n"/>
       <c r="I590" s="3" t="n"/>
       <c r="J590" s="3" t="n"/>
+      <c r="K590" s="3" t="n"/>
     </row>
     <row r="591">
       <c r="F591" t="inlineStr">
@@ -7003,6 +7601,7 @@
       <c r="H591" s="2" t="n"/>
       <c r="I591" s="3" t="n"/>
       <c r="J591" s="3" t="n"/>
+      <c r="K591" s="3" t="n"/>
     </row>
     <row r="592">
       <c r="F592" t="inlineStr">
@@ -7014,6 +7613,7 @@
       <c r="H592" s="2" t="n"/>
       <c r="I592" s="3" t="n"/>
       <c r="J592" s="3" t="n"/>
+      <c r="K592" s="3" t="n"/>
     </row>
     <row r="593">
       <c r="F593" t="inlineStr">
@@ -7025,6 +7625,7 @@
       <c r="H593" s="2" t="n"/>
       <c r="I593" s="3" t="n"/>
       <c r="J593" s="3" t="n"/>
+      <c r="K593" s="3" t="n"/>
     </row>
     <row r="594">
       <c r="F594" t="inlineStr">
@@ -7036,6 +7637,7 @@
       <c r="H594" s="2" t="n"/>
       <c r="I594" s="3" t="n"/>
       <c r="J594" s="3" t="n"/>
+      <c r="K594" s="3" t="n"/>
     </row>
     <row r="595">
       <c r="F595" t="inlineStr">
@@ -7047,6 +7649,7 @@
       <c r="H595" s="2" t="n"/>
       <c r="I595" s="3" t="n"/>
       <c r="J595" s="3" t="n"/>
+      <c r="K595" s="3" t="n"/>
     </row>
     <row r="596">
       <c r="F596" t="inlineStr">
@@ -7058,6 +7661,7 @@
       <c r="H596" s="2" t="n"/>
       <c r="I596" s="3" t="n"/>
       <c r="J596" s="3" t="n"/>
+      <c r="K596" s="3" t="n"/>
     </row>
     <row r="597">
       <c r="F597" t="inlineStr">
@@ -7069,6 +7673,7 @@
       <c r="H597" s="2" t="n"/>
       <c r="I597" s="3" t="n"/>
       <c r="J597" s="3" t="n"/>
+      <c r="K597" s="3" t="n"/>
     </row>
     <row r="598">
       <c r="F598" t="inlineStr">
@@ -7080,6 +7685,7 @@
       <c r="H598" s="2" t="n"/>
       <c r="I598" s="3" t="n"/>
       <c r="J598" s="3" t="n"/>
+      <c r="K598" s="3" t="n"/>
     </row>
     <row r="599">
       <c r="F599" t="inlineStr">
@@ -7091,6 +7697,7 @@
       <c r="H599" s="2" t="n"/>
       <c r="I599" s="3" t="n"/>
       <c r="J599" s="3" t="n"/>
+      <c r="K599" s="3" t="n"/>
     </row>
     <row r="600">
       <c r="F600" t="inlineStr">
@@ -7102,6 +7709,7 @@
       <c r="H600" s="2" t="n"/>
       <c r="I600" s="3" t="n"/>
       <c r="J600" s="3" t="n"/>
+      <c r="K600" s="3" t="n"/>
     </row>
     <row r="601">
       <c r="F601" t="inlineStr">
@@ -7113,6 +7721,7 @@
       <c r="H601" s="2" t="n"/>
       <c r="I601" s="3" t="n"/>
       <c r="J601" s="3" t="n"/>
+      <c r="K601" s="3" t="n"/>
     </row>
     <row r="602">
       <c r="F602" t="inlineStr">
@@ -7124,6 +7733,7 @@
       <c r="H602" s="2" t="n"/>
       <c r="I602" s="3" t="n"/>
       <c r="J602" s="3" t="n"/>
+      <c r="K602" s="3" t="n"/>
     </row>
     <row r="603">
       <c r="F603" t="inlineStr">
@@ -7135,6 +7745,7 @@
       <c r="H603" s="2" t="n"/>
       <c r="I603" s="3" t="n"/>
       <c r="J603" s="3" t="n"/>
+      <c r="K603" s="3" t="n"/>
     </row>
     <row r="604">
       <c r="F604" t="inlineStr">
@@ -7146,6 +7757,7 @@
       <c r="H604" s="2" t="n"/>
       <c r="I604" s="3" t="n"/>
       <c r="J604" s="3" t="n"/>
+      <c r="K604" s="3" t="n"/>
     </row>
     <row r="605">
       <c r="F605" t="inlineStr">
@@ -7157,6 +7769,7 @@
       <c r="H605" s="2" t="n"/>
       <c r="I605" s="3" t="n"/>
       <c r="J605" s="3" t="n"/>
+      <c r="K605" s="3" t="n"/>
     </row>
     <row r="606">
       <c r="F606" t="inlineStr">
@@ -7168,6 +7781,7 @@
       <c r="H606" s="2" t="n"/>
       <c r="I606" s="3" t="n"/>
       <c r="J606" s="3" t="n"/>
+      <c r="K606" s="3" t="n"/>
     </row>
     <row r="607">
       <c r="F607" t="inlineStr">
@@ -7179,6 +7793,7 @@
       <c r="H607" s="2" t="n"/>
       <c r="I607" s="3" t="n"/>
       <c r="J607" s="3" t="n"/>
+      <c r="K607" s="3" t="n"/>
     </row>
     <row r="608">
       <c r="F608" t="inlineStr">
@@ -7190,6 +7805,7 @@
       <c r="H608" s="2" t="n"/>
       <c r="I608" s="3" t="n"/>
       <c r="J608" s="3" t="n"/>
+      <c r="K608" s="3" t="n"/>
     </row>
     <row r="609">
       <c r="F609" t="inlineStr">
@@ -7201,6 +7817,7 @@
       <c r="H609" s="2" t="n"/>
       <c r="I609" s="3" t="n"/>
       <c r="J609" s="3" t="n"/>
+      <c r="K609" s="3" t="n"/>
     </row>
     <row r="610">
       <c r="F610" t="inlineStr">
@@ -7212,6 +7829,7 @@
       <c r="H610" s="2" t="n"/>
       <c r="I610" s="3" t="n"/>
       <c r="J610" s="3" t="n"/>
+      <c r="K610" s="3" t="n"/>
     </row>
     <row r="611">
       <c r="F611" t="inlineStr">
@@ -7223,6 +7841,7 @@
       <c r="H611" s="2" t="n"/>
       <c r="I611" s="3" t="n"/>
       <c r="J611" s="3" t="n"/>
+      <c r="K611" s="3" t="n"/>
     </row>
     <row r="612">
       <c r="F612" t="inlineStr">
@@ -7234,6 +7853,7 @@
       <c r="H612" s="2" t="n"/>
       <c r="I612" s="3" t="n"/>
       <c r="J612" s="3" t="n"/>
+      <c r="K612" s="3" t="n"/>
     </row>
     <row r="613">
       <c r="F613" t="inlineStr">
@@ -7245,6 +7865,7 @@
       <c r="H613" s="2" t="n"/>
       <c r="I613" s="3" t="n"/>
       <c r="J613" s="3" t="n"/>
+      <c r="K613" s="3" t="n"/>
     </row>
     <row r="614">
       <c r="F614" t="inlineStr">
@@ -7256,6 +7877,7 @@
       <c r="H614" s="2" t="n"/>
       <c r="I614" s="3" t="n"/>
       <c r="J614" s="3" t="n"/>
+      <c r="K614" s="3" t="n"/>
     </row>
     <row r="615">
       <c r="F615" t="inlineStr">
@@ -7267,6 +7889,7 @@
       <c r="H615" s="2" t="n"/>
       <c r="I615" s="3" t="n"/>
       <c r="J615" s="3" t="n"/>
+      <c r="K615" s="3" t="n"/>
     </row>
     <row r="616">
       <c r="F616" t="inlineStr">
@@ -7278,6 +7901,7 @@
       <c r="H616" s="2" t="n"/>
       <c r="I616" s="3" t="n"/>
       <c r="J616" s="3" t="n"/>
+      <c r="K616" s="3" t="n"/>
     </row>
     <row r="617">
       <c r="F617" t="inlineStr">
@@ -7289,6 +7913,7 @@
       <c r="H617" s="2" t="n"/>
       <c r="I617" s="3" t="n"/>
       <c r="J617" s="3" t="n"/>
+      <c r="K617" s="3" t="n"/>
     </row>
     <row r="618">
       <c r="F618" t="inlineStr">
@@ -7300,6 +7925,7 @@
       <c r="H618" s="2" t="n"/>
       <c r="I618" s="3" t="n"/>
       <c r="J618" s="3" t="n"/>
+      <c r="K618" s="3" t="n"/>
     </row>
     <row r="619">
       <c r="F619" t="inlineStr">
@@ -7311,6 +7937,7 @@
       <c r="H619" s="2" t="n"/>
       <c r="I619" s="3" t="n"/>
       <c r="J619" s="3" t="n"/>
+      <c r="K619" s="3" t="n"/>
     </row>
     <row r="620">
       <c r="F620" t="inlineStr">
@@ -7322,6 +7949,7 @@
       <c r="H620" s="2" t="n"/>
       <c r="I620" s="3" t="n"/>
       <c r="J620" s="3" t="n"/>
+      <c r="K620" s="3" t="n"/>
     </row>
     <row r="621">
       <c r="F621" t="inlineStr">
@@ -7333,6 +7961,7 @@
       <c r="H621" s="2" t="n"/>
       <c r="I621" s="3" t="n"/>
       <c r="J621" s="3" t="n"/>
+      <c r="K621" s="3" t="n"/>
     </row>
     <row r="622">
       <c r="F622" t="inlineStr">
@@ -7344,6 +7973,7 @@
       <c r="H622" s="2" t="n"/>
       <c r="I622" s="3" t="n"/>
       <c r="J622" s="3" t="n"/>
+      <c r="K622" s="3" t="n"/>
     </row>
     <row r="623">
       <c r="F623" t="inlineStr">
@@ -7355,6 +7985,7 @@
       <c r="H623" s="2" t="n"/>
       <c r="I623" s="3" t="n"/>
       <c r="J623" s="3" t="n"/>
+      <c r="K623" s="3" t="n"/>
     </row>
     <row r="624">
       <c r="F624" t="inlineStr">
@@ -7366,6 +7997,7 @@
       <c r="H624" s="2" t="n"/>
       <c r="I624" s="3" t="n"/>
       <c r="J624" s="3" t="n"/>
+      <c r="K624" s="3" t="n"/>
     </row>
     <row r="625">
       <c r="F625" t="inlineStr">
@@ -7377,6 +8009,7 @@
       <c r="H625" s="2" t="n"/>
       <c r="I625" s="3" t="n"/>
       <c r="J625" s="3" t="n"/>
+      <c r="K625" s="3" t="n"/>
     </row>
     <row r="626">
       <c r="F626" t="inlineStr">
@@ -7388,6 +8021,7 @@
       <c r="H626" s="2" t="n"/>
       <c r="I626" s="3" t="n"/>
       <c r="J626" s="3" t="n"/>
+      <c r="K626" s="3" t="n"/>
     </row>
     <row r="627">
       <c r="F627" t="inlineStr">
@@ -7399,6 +8033,7 @@
       <c r="H627" s="2" t="n"/>
       <c r="I627" s="3" t="n"/>
       <c r="J627" s="3" t="n"/>
+      <c r="K627" s="3" t="n"/>
     </row>
     <row r="628">
       <c r="F628" t="inlineStr">
@@ -7410,6 +8045,7 @@
       <c r="H628" s="2" t="n"/>
       <c r="I628" s="3" t="n"/>
       <c r="J628" s="3" t="n"/>
+      <c r="K628" s="3" t="n"/>
     </row>
     <row r="629">
       <c r="F629" t="inlineStr">
@@ -7421,6 +8057,7 @@
       <c r="H629" s="2" t="n"/>
       <c r="I629" s="3" t="n"/>
       <c r="J629" s="3" t="n"/>
+      <c r="K629" s="3" t="n"/>
     </row>
     <row r="630">
       <c r="F630" t="inlineStr">
@@ -7432,6 +8069,7 @@
       <c r="H630" s="2" t="n"/>
       <c r="I630" s="3" t="n"/>
       <c r="J630" s="3" t="n"/>
+      <c r="K630" s="3" t="n"/>
     </row>
     <row r="631">
       <c r="F631" t="inlineStr">
@@ -7443,6 +8081,7 @@
       <c r="H631" s="2" t="n"/>
       <c r="I631" s="3" t="n"/>
       <c r="J631" s="3" t="n"/>
+      <c r="K631" s="3" t="n"/>
     </row>
     <row r="632">
       <c r="F632" t="inlineStr">
@@ -7454,6 +8093,7 @@
       <c r="H632" s="2" t="n"/>
       <c r="I632" s="3" t="n"/>
       <c r="J632" s="3" t="n"/>
+      <c r="K632" s="3" t="n"/>
     </row>
     <row r="633">
       <c r="F633" t="inlineStr">
@@ -7465,6 +8105,7 @@
       <c r="H633" s="2" t="n"/>
       <c r="I633" s="3" t="n"/>
       <c r="J633" s="3" t="n"/>
+      <c r="K633" s="3" t="n"/>
     </row>
     <row r="634">
       <c r="F634" t="inlineStr">
@@ -7476,6 +8117,7 @@
       <c r="H634" s="2" t="n"/>
       <c r="I634" s="3" t="n"/>
       <c r="J634" s="3" t="n"/>
+      <c r="K634" s="3" t="n"/>
     </row>
     <row r="635">
       <c r="F635" t="inlineStr">
@@ -7487,6 +8129,7 @@
       <c r="H635" s="2" t="n"/>
       <c r="I635" s="3" t="n"/>
       <c r="J635" s="3" t="n"/>
+      <c r="K635" s="3" t="n"/>
     </row>
     <row r="636">
       <c r="F636" t="inlineStr">
@@ -7498,6 +8141,7 @@
       <c r="H636" s="2" t="n"/>
       <c r="I636" s="3" t="n"/>
       <c r="J636" s="3" t="n"/>
+      <c r="K636" s="3" t="n"/>
     </row>
     <row r="637">
       <c r="F637" t="inlineStr">
@@ -7509,6 +8153,7 @@
       <c r="H637" s="2" t="n"/>
       <c r="I637" s="3" t="n"/>
       <c r="J637" s="3" t="n"/>
+      <c r="K637" s="3" t="n"/>
     </row>
     <row r="638">
       <c r="F638" t="inlineStr">
@@ -7520,6 +8165,7 @@
       <c r="H638" s="2" t="n"/>
       <c r="I638" s="3" t="n"/>
       <c r="J638" s="3" t="n"/>
+      <c r="K638" s="3" t="n"/>
     </row>
     <row r="639">
       <c r="F639" t="inlineStr">
@@ -7531,6 +8177,7 @@
       <c r="H639" s="2" t="n"/>
       <c r="I639" s="3" t="n"/>
       <c r="J639" s="3" t="n"/>
+      <c r="K639" s="3" t="n"/>
     </row>
     <row r="640">
       <c r="F640" t="inlineStr">
@@ -7542,6 +8189,7 @@
       <c r="H640" s="2" t="n"/>
       <c r="I640" s="3" t="n"/>
       <c r="J640" s="3" t="n"/>
+      <c r="K640" s="3" t="n"/>
     </row>
     <row r="641">
       <c r="F641" t="inlineStr">
@@ -7553,6 +8201,7 @@
       <c r="H641" s="2" t="n"/>
       <c r="I641" s="3" t="n"/>
       <c r="J641" s="3" t="n"/>
+      <c r="K641" s="3" t="n"/>
     </row>
     <row r="642">
       <c r="F642" t="inlineStr">
@@ -7564,6 +8213,7 @@
       <c r="H642" s="2" t="n"/>
       <c r="I642" s="3" t="n"/>
       <c r="J642" s="3" t="n"/>
+      <c r="K642" s="3" t="n"/>
     </row>
     <row r="643">
       <c r="F643" t="inlineStr">
@@ -7575,6 +8225,7 @@
       <c r="H643" s="2" t="n"/>
       <c r="I643" s="3" t="n"/>
       <c r="J643" s="3" t="n"/>
+      <c r="K643" s="3" t="n"/>
     </row>
     <row r="644">
       <c r="F644" t="inlineStr">
@@ -7586,6 +8237,7 @@
       <c r="H644" s="2" t="n"/>
       <c r="I644" s="3" t="n"/>
       <c r="J644" s="3" t="n"/>
+      <c r="K644" s="3" t="n"/>
     </row>
     <row r="645">
       <c r="F645" t="inlineStr">
@@ -7597,6 +8249,7 @@
       <c r="H645" s="2" t="n"/>
       <c r="I645" s="3" t="n"/>
       <c r="J645" s="3" t="n"/>
+      <c r="K645" s="3" t="n"/>
     </row>
     <row r="646">
       <c r="F646" t="inlineStr">
@@ -7608,6 +8261,7 @@
       <c r="H646" s="2" t="n"/>
       <c r="I646" s="3" t="n"/>
       <c r="J646" s="3" t="n"/>
+      <c r="K646" s="3" t="n"/>
     </row>
     <row r="647">
       <c r="F647" t="inlineStr">
@@ -7619,6 +8273,7 @@
       <c r="H647" s="2" t="n"/>
       <c r="I647" s="3" t="n"/>
       <c r="J647" s="3" t="n"/>
+      <c r="K647" s="3" t="n"/>
     </row>
     <row r="648">
       <c r="F648" t="inlineStr">
@@ -7630,6 +8285,7 @@
       <c r="H648" s="2" t="n"/>
       <c r="I648" s="3" t="n"/>
       <c r="J648" s="3" t="n"/>
+      <c r="K648" s="3" t="n"/>
     </row>
     <row r="649">
       <c r="F649" t="inlineStr">
@@ -7641,6 +8297,7 @@
       <c r="H649" s="2" t="n"/>
       <c r="I649" s="3" t="n"/>
       <c r="J649" s="3" t="n"/>
+      <c r="K649" s="3" t="n"/>
     </row>
     <row r="650">
       <c r="F650" t="inlineStr">
@@ -7652,6 +8309,7 @@
       <c r="H650" s="2" t="n"/>
       <c r="I650" s="3" t="n"/>
       <c r="J650" s="3" t="n"/>
+      <c r="K650" s="3" t="n"/>
     </row>
     <row r="651">
       <c r="F651" t="inlineStr">
@@ -7663,6 +8321,7 @@
       <c r="H651" s="2" t="n"/>
       <c r="I651" s="3" t="n"/>
       <c r="J651" s="3" t="n"/>
+      <c r="K651" s="3" t="n"/>
     </row>
     <row r="652">
       <c r="F652" t="inlineStr">
@@ -7674,6 +8333,7 @@
       <c r="H652" s="2" t="n"/>
       <c r="I652" s="3" t="n"/>
       <c r="J652" s="3" t="n"/>
+      <c r="K652" s="3" t="n"/>
     </row>
     <row r="653">
       <c r="F653" t="inlineStr">
@@ -7685,6 +8345,7 @@
       <c r="H653" s="2" t="n"/>
       <c r="I653" s="3" t="n"/>
       <c r="J653" s="3" t="n"/>
+      <c r="K653" s="3" t="n"/>
     </row>
     <row r="654">
       <c r="F654" t="inlineStr">
@@ -7696,6 +8357,7 @@
       <c r="H654" s="2" t="n"/>
       <c r="I654" s="3" t="n"/>
       <c r="J654" s="3" t="n"/>
+      <c r="K654" s="3" t="n"/>
     </row>
     <row r="655">
       <c r="F655" t="inlineStr">
@@ -7707,6 +8369,7 @@
       <c r="H655" s="2" t="n"/>
       <c r="I655" s="3" t="n"/>
       <c r="J655" s="3" t="n"/>
+      <c r="K655" s="3" t="n"/>
     </row>
     <row r="656">
       <c r="F656" t="inlineStr">
@@ -7718,6 +8381,7 @@
       <c r="H656" s="2" t="n"/>
       <c r="I656" s="3" t="n"/>
       <c r="J656" s="3" t="n"/>
+      <c r="K656" s="3" t="n"/>
     </row>
     <row r="657">
       <c r="F657" t="inlineStr">
@@ -7729,6 +8393,7 @@
       <c r="H657" s="2" t="n"/>
       <c r="I657" s="3" t="n"/>
       <c r="J657" s="3" t="n"/>
+      <c r="K657" s="3" t="n"/>
     </row>
     <row r="658">
       <c r="F658" t="inlineStr">
@@ -7740,6 +8405,7 @@
       <c r="H658" s="2" t="n"/>
       <c r="I658" s="3" t="n"/>
       <c r="J658" s="3" t="n"/>
+      <c r="K658" s="3" t="n"/>
     </row>
     <row r="659">
       <c r="F659" t="inlineStr">
@@ -7751,6 +8417,7 @@
       <c r="H659" s="2" t="n"/>
       <c r="I659" s="3" t="n"/>
       <c r="J659" s="3" t="n"/>
+      <c r="K659" s="3" t="n"/>
     </row>
     <row r="660">
       <c r="F660" t="inlineStr">
@@ -7762,6 +8429,7 @@
       <c r="H660" s="2" t="n"/>
       <c r="I660" s="3" t="n"/>
       <c r="J660" s="3" t="n"/>
+      <c r="K660" s="3" t="n"/>
     </row>
     <row r="661">
       <c r="F661" t="inlineStr">
@@ -7773,6 +8441,7 @@
       <c r="H661" s="2" t="n"/>
       <c r="I661" s="3" t="n"/>
       <c r="J661" s="3" t="n"/>
+      <c r="K661" s="3" t="n"/>
     </row>
     <row r="662">
       <c r="F662" t="inlineStr">
@@ -7784,6 +8453,7 @@
       <c r="H662" s="2" t="n"/>
       <c r="I662" s="3" t="n"/>
       <c r="J662" s="3" t="n"/>
+      <c r="K662" s="3" t="n"/>
     </row>
     <row r="663">
       <c r="F663" t="inlineStr">
@@ -7795,6 +8465,7 @@
       <c r="H663" s="2" t="n"/>
       <c r="I663" s="3" t="n"/>
       <c r="J663" s="3" t="n"/>
+      <c r="K663" s="3" t="n"/>
     </row>
     <row r="664">
       <c r="F664" t="inlineStr">
@@ -7806,6 +8477,7 @@
       <c r="H664" s="2" t="n"/>
       <c r="I664" s="3" t="n"/>
       <c r="J664" s="3" t="n"/>
+      <c r="K664" s="3" t="n"/>
     </row>
     <row r="665">
       <c r="F665" t="inlineStr">
@@ -7817,6 +8489,7 @@
       <c r="H665" s="2" t="n"/>
       <c r="I665" s="3" t="n"/>
       <c r="J665" s="3" t="n"/>
+      <c r="K665" s="3" t="n"/>
     </row>
     <row r="666">
       <c r="F666" t="inlineStr">
@@ -7828,6 +8501,7 @@
       <c r="H666" s="2" t="n"/>
       <c r="I666" s="3" t="n"/>
       <c r="J666" s="3" t="n"/>
+      <c r="K666" s="3" t="n"/>
     </row>
     <row r="667">
       <c r="F667" t="inlineStr">
@@ -7839,6 +8513,7 @@
       <c r="H667" s="2" t="n"/>
       <c r="I667" s="3" t="n"/>
       <c r="J667" s="3" t="n"/>
+      <c r="K667" s="3" t="n"/>
     </row>
     <row r="668">
       <c r="F668" t="inlineStr">
@@ -7850,6 +8525,7 @@
       <c r="H668" s="2" t="n"/>
       <c r="I668" s="3" t="n"/>
       <c r="J668" s="3" t="n"/>
+      <c r="K668" s="3" t="n"/>
     </row>
     <row r="669">
       <c r="F669" t="inlineStr">
@@ -7861,6 +8537,7 @@
       <c r="H669" s="2" t="n"/>
       <c r="I669" s="3" t="n"/>
       <c r="J669" s="3" t="n"/>
+      <c r="K669" s="3" t="n"/>
     </row>
     <row r="670">
       <c r="F670" t="inlineStr">
@@ -7872,6 +8549,7 @@
       <c r="H670" s="2" t="n"/>
       <c r="I670" s="3" t="n"/>
       <c r="J670" s="3" t="n"/>
+      <c r="K670" s="3" t="n"/>
     </row>
     <row r="671">
       <c r="F671" t="inlineStr">
@@ -7883,6 +8561,7 @@
       <c r="H671" s="2" t="n"/>
       <c r="I671" s="3" t="n"/>
       <c r="J671" s="3" t="n"/>
+      <c r="K671" s="3" t="n"/>
     </row>
     <row r="672">
       <c r="F672" t="inlineStr">
@@ -7894,6 +8573,7 @@
       <c r="H672" s="2" t="n"/>
       <c r="I672" s="3" t="n"/>
       <c r="J672" s="3" t="n"/>
+      <c r="K672" s="3" t="n"/>
     </row>
     <row r="673">
       <c r="F673" t="inlineStr">
@@ -7905,6 +8585,7 @@
       <c r="H673" s="2" t="n"/>
       <c r="I673" s="3" t="n"/>
       <c r="J673" s="3" t="n"/>
+      <c r="K673" s="3" t="n"/>
     </row>
     <row r="674">
       <c r="F674" t="inlineStr">
@@ -7916,6 +8597,7 @@
       <c r="H674" s="2" t="n"/>
       <c r="I674" s="3" t="n"/>
       <c r="J674" s="3" t="n"/>
+      <c r="K674" s="3" t="n"/>
     </row>
     <row r="675">
       <c r="F675" t="inlineStr">
@@ -7927,6 +8609,7 @@
       <c r="H675" s="2" t="n"/>
       <c r="I675" s="3" t="n"/>
       <c r="J675" s="3" t="n"/>
+      <c r="K675" s="3" t="n"/>
     </row>
     <row r="676">
       <c r="F676" t="inlineStr">
@@ -7938,6 +8621,7 @@
       <c r="H676" s="2" t="n"/>
       <c r="I676" s="3" t="n"/>
       <c r="J676" s="3" t="n"/>
+      <c r="K676" s="3" t="n"/>
     </row>
     <row r="677">
       <c r="F677" t="inlineStr">
@@ -7949,6 +8633,7 @@
       <c r="H677" s="2" t="n"/>
       <c r="I677" s="3" t="n"/>
       <c r="J677" s="3" t="n"/>
+      <c r="K677" s="3" t="n"/>
     </row>
     <row r="678">
       <c r="F678" t="inlineStr">
@@ -7960,6 +8645,7 @@
       <c r="H678" s="2" t="n"/>
       <c r="I678" s="3" t="n"/>
       <c r="J678" s="3" t="n"/>
+      <c r="K678" s="3" t="n"/>
     </row>
     <row r="679">
       <c r="F679" t="inlineStr">
@@ -7971,6 +8657,7 @@
       <c r="H679" s="2" t="n"/>
       <c r="I679" s="3" t="n"/>
       <c r="J679" s="3" t="n"/>
+      <c r="K679" s="3" t="n"/>
     </row>
     <row r="680">
       <c r="F680" t="inlineStr">
@@ -7982,6 +8669,7 @@
       <c r="H680" s="2" t="n"/>
       <c r="I680" s="3" t="n"/>
       <c r="J680" s="3" t="n"/>
+      <c r="K680" s="3" t="n"/>
     </row>
     <row r="681">
       <c r="F681" t="inlineStr">
@@ -7993,6 +8681,7 @@
       <c r="H681" s="2" t="n"/>
       <c r="I681" s="3" t="n"/>
       <c r="J681" s="3" t="n"/>
+      <c r="K681" s="3" t="n"/>
     </row>
     <row r="682">
       <c r="F682" t="inlineStr">
@@ -8004,6 +8693,7 @@
       <c r="H682" s="2" t="n"/>
       <c r="I682" s="3" t="n"/>
       <c r="J682" s="3" t="n"/>
+      <c r="K682" s="3" t="n"/>
     </row>
     <row r="683">
       <c r="F683" t="inlineStr">
@@ -8015,6 +8705,7 @@
       <c r="H683" s="2" t="n"/>
       <c r="I683" s="3" t="n"/>
       <c r="J683" s="3" t="n"/>
+      <c r="K683" s="3" t="n"/>
     </row>
     <row r="684">
       <c r="F684" t="inlineStr">
@@ -8026,6 +8717,7 @@
       <c r="H684" s="2" t="n"/>
       <c r="I684" s="3" t="n"/>
       <c r="J684" s="3" t="n"/>
+      <c r="K684" s="3" t="n"/>
     </row>
     <row r="685">
       <c r="F685" t="inlineStr">
@@ -8037,6 +8729,7 @@
       <c r="H685" s="2" t="n"/>
       <c r="I685" s="3" t="n"/>
       <c r="J685" s="3" t="n"/>
+      <c r="K685" s="3" t="n"/>
     </row>
     <row r="686">
       <c r="F686" t="inlineStr">
@@ -8048,6 +8741,7 @@
       <c r="H686" s="2" t="n"/>
       <c r="I686" s="3" t="n"/>
       <c r="J686" s="3" t="n"/>
+      <c r="K686" s="3" t="n"/>
     </row>
     <row r="687">
       <c r="F687" t="inlineStr">
@@ -8059,6 +8753,7 @@
       <c r="H687" s="2" t="n"/>
       <c r="I687" s="3" t="n"/>
       <c r="J687" s="3" t="n"/>
+      <c r="K687" s="3" t="n"/>
     </row>
     <row r="688">
       <c r="F688" t="inlineStr">
@@ -8070,6 +8765,7 @@
       <c r="H688" s="2" t="n"/>
       <c r="I688" s="3" t="n"/>
       <c r="J688" s="3" t="n"/>
+      <c r="K688" s="3" t="n"/>
     </row>
     <row r="689">
       <c r="F689" t="inlineStr">
@@ -8081,6 +8777,7 @@
       <c r="H689" s="2" t="n"/>
       <c r="I689" s="3" t="n"/>
       <c r="J689" s="3" t="n"/>
+      <c r="K689" s="3" t="n"/>
     </row>
     <row r="690">
       <c r="F690" t="inlineStr">
@@ -8092,6 +8789,7 @@
       <c r="H690" s="2" t="n"/>
       <c r="I690" s="3" t="n"/>
       <c r="J690" s="3" t="n"/>
+      <c r="K690" s="3" t="n"/>
     </row>
     <row r="691">
       <c r="F691" t="inlineStr">
@@ -8103,6 +8801,7 @@
       <c r="H691" s="2" t="n"/>
       <c r="I691" s="3" t="n"/>
       <c r="J691" s="3" t="n"/>
+      <c r="K691" s="3" t="n"/>
     </row>
     <row r="692">
       <c r="F692" t="inlineStr">
@@ -8114,6 +8813,7 @@
       <c r="H692" s="2" t="n"/>
       <c r="I692" s="3" t="n"/>
       <c r="J692" s="3" t="n"/>
+      <c r="K692" s="3" t="n"/>
     </row>
     <row r="693">
       <c r="F693" t="inlineStr">
@@ -8125,6 +8825,7 @@
       <c r="H693" s="2" t="n"/>
       <c r="I693" s="3" t="n"/>
       <c r="J693" s="3" t="n"/>
+      <c r="K693" s="3" t="n"/>
     </row>
     <row r="694">
       <c r="F694" t="inlineStr">
@@ -8136,6 +8837,7 @@
       <c r="H694" s="2" t="n"/>
       <c r="I694" s="3" t="n"/>
       <c r="J694" s="3" t="n"/>
+      <c r="K694" s="3" t="n"/>
     </row>
     <row r="695">
       <c r="F695" t="inlineStr">
@@ -8147,6 +8849,7 @@
       <c r="H695" s="2" t="n"/>
       <c r="I695" s="3" t="n"/>
       <c r="J695" s="3" t="n"/>
+      <c r="K695" s="3" t="n"/>
     </row>
     <row r="696">
       <c r="F696" t="inlineStr">
@@ -8158,6 +8861,7 @@
       <c r="H696" s="2" t="n"/>
       <c r="I696" s="3" t="n"/>
       <c r="J696" s="3" t="n"/>
+      <c r="K696" s="3" t="n"/>
     </row>
     <row r="697">
       <c r="F697" t="inlineStr">
@@ -8169,6 +8873,7 @@
       <c r="H697" s="2" t="n"/>
       <c r="I697" s="3" t="n"/>
       <c r="J697" s="3" t="n"/>
+      <c r="K697" s="3" t="n"/>
     </row>
     <row r="698">
       <c r="F698" t="inlineStr">
@@ -8180,6 +8885,7 @@
       <c r="H698" s="2" t="n"/>
       <c r="I698" s="3" t="n"/>
       <c r="J698" s="3" t="n"/>
+      <c r="K698" s="3" t="n"/>
     </row>
     <row r="699">
       <c r="F699" t="inlineStr">
@@ -8191,6 +8897,7 @@
       <c r="H699" s="2" t="n"/>
       <c r="I699" s="3" t="n"/>
       <c r="J699" s="3" t="n"/>
+      <c r="K699" s="3" t="n"/>
     </row>
     <row r="700">
       <c r="F700" t="inlineStr">
@@ -8202,6 +8909,7 @@
       <c r="H700" s="2" t="n"/>
       <c r="I700" s="3" t="n"/>
       <c r="J700" s="3" t="n"/>
+      <c r="K700" s="3" t="n"/>
     </row>
     <row r="701">
       <c r="F701" t="inlineStr">
@@ -8213,6 +8921,7 @@
       <c r="H701" s="2" t="n"/>
       <c r="I701" s="3" t="n"/>
       <c r="J701" s="3" t="n"/>
+      <c r="K701" s="3" t="n"/>
     </row>
     <row r="702">
       <c r="F702" t="inlineStr">
@@ -8224,6 +8933,7 @@
       <c r="H702" s="2" t="n"/>
       <c r="I702" s="3" t="n"/>
       <c r="J702" s="3" t="n"/>
+      <c r="K702" s="3" t="n"/>
     </row>
     <row r="703">
       <c r="F703" t="inlineStr">
@@ -8235,6 +8945,7 @@
       <c r="H703" s="2" t="n"/>
       <c r="I703" s="3" t="n"/>
       <c r="J703" s="3" t="n"/>
+      <c r="K703" s="3" t="n"/>
     </row>
     <row r="704">
       <c r="F704" t="inlineStr">
@@ -8246,6 +8957,7 @@
       <c r="H704" s="2" t="n"/>
       <c r="I704" s="3" t="n"/>
       <c r="J704" s="3" t="n"/>
+      <c r="K704" s="3" t="n"/>
     </row>
     <row r="705">
       <c r="F705" t="inlineStr">
@@ -8257,6 +8969,7 @@
       <c r="H705" s="2" t="n"/>
       <c r="I705" s="3" t="n"/>
       <c r="J705" s="3" t="n"/>
+      <c r="K705" s="3" t="n"/>
     </row>
     <row r="706">
       <c r="F706" t="inlineStr">
@@ -8268,6 +8981,7 @@
       <c r="H706" s="2" t="n"/>
       <c r="I706" s="3" t="n"/>
       <c r="J706" s="3" t="n"/>
+      <c r="K706" s="3" t="n"/>
     </row>
     <row r="707">
       <c r="F707" t="inlineStr">
@@ -8279,6 +8993,7 @@
       <c r="H707" s="2" t="n"/>
       <c r="I707" s="3" t="n"/>
       <c r="J707" s="3" t="n"/>
+      <c r="K707" s="3" t="n"/>
     </row>
     <row r="708">
       <c r="F708" t="inlineStr">
@@ -8290,6 +9005,7 @@
       <c r="H708" s="2" t="n"/>
       <c r="I708" s="3" t="n"/>
       <c r="J708" s="3" t="n"/>
+      <c r="K708" s="3" t="n"/>
     </row>
     <row r="709">
       <c r="F709" t="inlineStr">
@@ -8301,6 +9017,7 @@
       <c r="H709" s="2" t="n"/>
       <c r="I709" s="3" t="n"/>
       <c r="J709" s="3" t="n"/>
+      <c r="K709" s="3" t="n"/>
     </row>
     <row r="710">
       <c r="F710" t="inlineStr">
@@ -8312,6 +9029,7 @@
       <c r="H710" s="2" t="n"/>
       <c r="I710" s="3" t="n"/>
       <c r="J710" s="3" t="n"/>
+      <c r="K710" s="3" t="n"/>
     </row>
     <row r="711">
       <c r="F711" t="inlineStr">
@@ -8323,6 +9041,7 @@
       <c r="H711" s="2" t="n"/>
       <c r="I711" s="3" t="n"/>
       <c r="J711" s="3" t="n"/>
+      <c r="K711" s="3" t="n"/>
     </row>
     <row r="712">
       <c r="F712" t="inlineStr">
@@ -8334,6 +9053,7 @@
       <c r="H712" s="2" t="n"/>
       <c r="I712" s="3" t="n"/>
       <c r="J712" s="3" t="n"/>
+      <c r="K712" s="3" t="n"/>
     </row>
     <row r="713">
       <c r="F713" t="inlineStr">
@@ -8345,6 +9065,7 @@
       <c r="H713" s="2" t="n"/>
       <c r="I713" s="3" t="n"/>
       <c r="J713" s="3" t="n"/>
+      <c r="K713" s="3" t="n"/>
     </row>
     <row r="714">
       <c r="F714" t="inlineStr">
@@ -8356,6 +9077,7 @@
       <c r="H714" s="2" t="n"/>
       <c r="I714" s="3" t="n"/>
       <c r="J714" s="3" t="n"/>
+      <c r="K714" s="3" t="n"/>
     </row>
     <row r="715">
       <c r="F715" t="inlineStr">
@@ -8367,6 +9089,7 @@
       <c r="H715" s="2" t="n"/>
       <c r="I715" s="3" t="n"/>
       <c r="J715" s="3" t="n"/>
+      <c r="K715" s="3" t="n"/>
     </row>
     <row r="716">
       <c r="F716" t="inlineStr">
@@ -8378,6 +9101,7 @@
       <c r="H716" s="2" t="n"/>
       <c r="I716" s="3" t="n"/>
       <c r="J716" s="3" t="n"/>
+      <c r="K716" s="3" t="n"/>
     </row>
     <row r="717">
       <c r="F717" t="inlineStr">
@@ -8389,6 +9113,7 @@
       <c r="H717" s="2" t="n"/>
       <c r="I717" s="3" t="n"/>
       <c r="J717" s="3" t="n"/>
+      <c r="K717" s="3" t="n"/>
     </row>
     <row r="718">
       <c r="F718" t="inlineStr">
@@ -8400,6 +9125,7 @@
       <c r="H718" s="2" t="n"/>
       <c r="I718" s="3" t="n"/>
       <c r="J718" s="3" t="n"/>
+      <c r="K718" s="3" t="n"/>
     </row>
     <row r="719">
       <c r="F719" t="inlineStr">
@@ -8411,6 +9137,7 @@
       <c r="H719" s="2" t="n"/>
       <c r="I719" s="3" t="n"/>
       <c r="J719" s="3" t="n"/>
+      <c r="K719" s="3" t="n"/>
     </row>
     <row r="720">
       <c r="F720" t="inlineStr">
@@ -8422,6 +9149,7 @@
       <c r="H720" s="2" t="n"/>
       <c r="I720" s="3" t="n"/>
       <c r="J720" s="3" t="n"/>
+      <c r="K720" s="3" t="n"/>
     </row>
     <row r="721">
       <c r="F721" t="inlineStr">
@@ -8433,6 +9161,7 @@
       <c r="H721" s="2" t="n"/>
       <c r="I721" s="3" t="n"/>
       <c r="J721" s="3" t="n"/>
+      <c r="K721" s="3" t="n"/>
     </row>
     <row r="722">
       <c r="F722" t="inlineStr">
@@ -8444,6 +9173,7 @@
       <c r="H722" s="2" t="n"/>
       <c r="I722" s="3" t="n"/>
       <c r="J722" s="3" t="n"/>
+      <c r="K722" s="3" t="n"/>
     </row>
     <row r="723">
       <c r="F723" t="inlineStr">
@@ -8455,6 +9185,7 @@
       <c r="H723" s="2" t="n"/>
       <c r="I723" s="3" t="n"/>
       <c r="J723" s="3" t="n"/>
+      <c r="K723" s="3" t="n"/>
     </row>
     <row r="724">
       <c r="F724" t="inlineStr">
@@ -8466,6 +9197,7 @@
       <c r="H724" s="2" t="n"/>
       <c r="I724" s="3" t="n"/>
       <c r="J724" s="3" t="n"/>
+      <c r="K724" s="3" t="n"/>
     </row>
     <row r="725">
       <c r="F725" t="inlineStr">
@@ -8477,6 +9209,7 @@
       <c r="H725" s="2" t="n"/>
       <c r="I725" s="3" t="n"/>
       <c r="J725" s="3" t="n"/>
+      <c r="K725" s="3" t="n"/>
     </row>
     <row r="726">
       <c r="F726" t="inlineStr">
@@ -8488,6 +9221,7 @@
       <c r="H726" s="2" t="n"/>
       <c r="I726" s="3" t="n"/>
       <c r="J726" s="3" t="n"/>
+      <c r="K726" s="3" t="n"/>
     </row>
     <row r="727">
       <c r="F727" t="inlineStr">
@@ -8499,6 +9233,7 @@
       <c r="H727" s="2" t="n"/>
       <c r="I727" s="3" t="n"/>
       <c r="J727" s="3" t="n"/>
+      <c r="K727" s="3" t="n"/>
     </row>
     <row r="728">
       <c r="F728" t="inlineStr">
@@ -8510,6 +9245,7 @@
       <c r="H728" s="2" t="n"/>
       <c r="I728" s="3" t="n"/>
       <c r="J728" s="3" t="n"/>
+      <c r="K728" s="3" t="n"/>
     </row>
     <row r="729">
       <c r="F729" t="inlineStr">
@@ -8521,6 +9257,7 @@
       <c r="H729" s="2" t="n"/>
       <c r="I729" s="3" t="n"/>
       <c r="J729" s="3" t="n"/>
+      <c r="K729" s="3" t="n"/>
     </row>
     <row r="730">
       <c r="F730" t="inlineStr">
@@ -8532,6 +9269,7 @@
       <c r="H730" s="2" t="n"/>
       <c r="I730" s="3" t="n"/>
       <c r="J730" s="3" t="n"/>
+      <c r="K730" s="3" t="n"/>
     </row>
     <row r="731">
       <c r="F731" t="inlineStr">
@@ -8543,6 +9281,7 @@
       <c r="H731" s="2" t="n"/>
       <c r="I731" s="3" t="n"/>
       <c r="J731" s="3" t="n"/>
+      <c r="K731" s="3" t="n"/>
     </row>
     <row r="732">
       <c r="F732" t="inlineStr">
@@ -8554,6 +9293,7 @@
       <c r="H732" s="2" t="n"/>
       <c r="I732" s="3" t="n"/>
       <c r="J732" s="3" t="n"/>
+      <c r="K732" s="3" t="n"/>
     </row>
     <row r="733">
       <c r="F733" t="inlineStr">
@@ -8565,6 +9305,7 @@
       <c r="H733" s="2" t="n"/>
       <c r="I733" s="3" t="n"/>
       <c r="J733" s="3" t="n"/>
+      <c r="K733" s="3" t="n"/>
     </row>
     <row r="734">
       <c r="F734" t="inlineStr">
@@ -8576,6 +9317,7 @@
       <c r="H734" s="2" t="n"/>
       <c r="I734" s="3" t="n"/>
       <c r="J734" s="3" t="n"/>
+      <c r="K734" s="3" t="n"/>
     </row>
     <row r="735">
       <c r="F735" t="inlineStr">
@@ -8587,6 +9329,7 @@
       <c r="H735" s="2" t="n"/>
       <c r="I735" s="3" t="n"/>
       <c r="J735" s="3" t="n"/>
+      <c r="K735" s="3" t="n"/>
     </row>
     <row r="736">
       <c r="F736" t="inlineStr">
@@ -8598,6 +9341,7 @@
       <c r="H736" s="2" t="n"/>
       <c r="I736" s="3" t="n"/>
       <c r="J736" s="3" t="n"/>
+      <c r="K736" s="3" t="n"/>
     </row>
     <row r="737">
       <c r="F737" t="inlineStr">
@@ -8609,6 +9353,7 @@
       <c r="H737" s="2" t="n"/>
       <c r="I737" s="3" t="n"/>
       <c r="J737" s="3" t="n"/>
+      <c r="K737" s="3" t="n"/>
     </row>
     <row r="738">
       <c r="F738" t="inlineStr">
@@ -8620,6 +9365,7 @@
       <c r="H738" s="2" t="n"/>
       <c r="I738" s="3" t="n"/>
       <c r="J738" s="3" t="n"/>
+      <c r="K738" s="3" t="n"/>
     </row>
     <row r="739">
       <c r="F739" t="inlineStr">
@@ -8631,6 +9377,7 @@
       <c r="H739" s="2" t="n"/>
       <c r="I739" s="3" t="n"/>
       <c r="J739" s="3" t="n"/>
+      <c r="K739" s="3" t="n"/>
     </row>
     <row r="740">
       <c r="F740" t="inlineStr">
@@ -8642,6 +9389,7 @@
       <c r="H740" s="2" t="n"/>
       <c r="I740" s="3" t="n"/>
       <c r="J740" s="3" t="n"/>
+      <c r="K740" s="3" t="n"/>
     </row>
     <row r="741">
       <c r="F741" t="inlineStr">
@@ -8653,6 +9401,7 @@
       <c r="H741" s="2" t="n"/>
       <c r="I741" s="3" t="n"/>
       <c r="J741" s="3" t="n"/>
+      <c r="K741" s="3" t="n"/>
     </row>
     <row r="742">
       <c r="F742" t="inlineStr">
@@ -8664,6 +9413,7 @@
       <c r="H742" s="2" t="n"/>
       <c r="I742" s="3" t="n"/>
       <c r="J742" s="3" t="n"/>
+      <c r="K742" s="3" t="n"/>
     </row>
     <row r="743">
       <c r="F743" t="inlineStr">
@@ -8675,6 +9425,7 @@
       <c r="H743" s="2" t="n"/>
       <c r="I743" s="3" t="n"/>
       <c r="J743" s="3" t="n"/>
+      <c r="K743" s="3" t="n"/>
     </row>
     <row r="744">
       <c r="F744" t="inlineStr">
@@ -8686,6 +9437,7 @@
       <c r="H744" s="2" t="n"/>
       <c r="I744" s="3" t="n"/>
       <c r="J744" s="3" t="n"/>
+      <c r="K744" s="3" t="n"/>
     </row>
     <row r="745">
       <c r="F745" t="inlineStr">
@@ -8697,6 +9449,7 @@
       <c r="H745" s="2" t="n"/>
       <c r="I745" s="3" t="n"/>
       <c r="J745" s="3" t="n"/>
+      <c r="K745" s="3" t="n"/>
     </row>
     <row r="746">
       <c r="F746" t="inlineStr">
@@ -8708,6 +9461,7 @@
       <c r="H746" s="2" t="n"/>
       <c r="I746" s="3" t="n"/>
       <c r="J746" s="3" t="n"/>
+      <c r="K746" s="3" t="n"/>
     </row>
     <row r="747">
       <c r="F747" t="inlineStr">
@@ -8719,6 +9473,7 @@
       <c r="H747" s="2" t="n"/>
       <c r="I747" s="3" t="n"/>
       <c r="J747" s="3" t="n"/>
+      <c r="K747" s="3" t="n"/>
     </row>
     <row r="748">
       <c r="F748" t="inlineStr">
@@ -8730,6 +9485,7 @@
       <c r="H748" s="2" t="n"/>
       <c r="I748" s="3" t="n"/>
       <c r="J748" s="3" t="n"/>
+      <c r="K748" s="3" t="n"/>
     </row>
     <row r="749">
       <c r="F749" t="inlineStr">
@@ -8741,6 +9497,7 @@
       <c r="H749" s="2" t="n"/>
       <c r="I749" s="3" t="n"/>
       <c r="J749" s="3" t="n"/>
+      <c r="K749" s="3" t="n"/>
     </row>
     <row r="750">
       <c r="F750" t="inlineStr">
@@ -8752,6 +9509,7 @@
       <c r="H750" s="2" t="n"/>
       <c r="I750" s="3" t="n"/>
       <c r="J750" s="3" t="n"/>
+      <c r="K750" s="3" t="n"/>
     </row>
     <row r="751">
       <c r="F751" t="inlineStr">
@@ -8763,6 +9521,7 @@
       <c r="H751" s="2" t="n"/>
       <c r="I751" s="3" t="n"/>
       <c r="J751" s="3" t="n"/>
+      <c r="K751" s="3" t="n"/>
     </row>
     <row r="752">
       <c r="F752" t="inlineStr">
@@ -8774,6 +9533,7 @@
       <c r="H752" s="2" t="n"/>
       <c r="I752" s="3" t="n"/>
       <c r="J752" s="3" t="n"/>
+      <c r="K752" s="3" t="n"/>
     </row>
     <row r="753">
       <c r="F753" t="inlineStr">
@@ -8785,6 +9545,7 @@
       <c r="H753" s="2" t="n"/>
       <c r="I753" s="3" t="n"/>
       <c r="J753" s="3" t="n"/>
+      <c r="K753" s="3" t="n"/>
     </row>
     <row r="754">
       <c r="F754" t="inlineStr">
@@ -8796,6 +9557,7 @@
       <c r="H754" s="2" t="n"/>
       <c r="I754" s="3" t="n"/>
       <c r="J754" s="3" t="n"/>
+      <c r="K754" s="3" t="n"/>
     </row>
     <row r="755">
       <c r="F755" t="inlineStr">
@@ -8807,6 +9569,7 @@
       <c r="H755" s="2" t="n"/>
       <c r="I755" s="3" t="n"/>
       <c r="J755" s="3" t="n"/>
+      <c r="K755" s="3" t="n"/>
     </row>
     <row r="756">
       <c r="F756" t="inlineStr">
@@ -8818,6 +9581,7 @@
       <c r="H756" s="2" t="n"/>
       <c r="I756" s="3" t="n"/>
       <c r="J756" s="3" t="n"/>
+      <c r="K756" s="3" t="n"/>
     </row>
     <row r="757">
       <c r="F757" t="inlineStr">
@@ -8829,6 +9593,7 @@
       <c r="H757" s="2" t="n"/>
       <c r="I757" s="3" t="n"/>
       <c r="J757" s="3" t="n"/>
+      <c r="K757" s="3" t="n"/>
     </row>
     <row r="758">
       <c r="F758" t="inlineStr">
@@ -8840,6 +9605,7 @@
       <c r="H758" s="2" t="n"/>
       <c r="I758" s="3" t="n"/>
       <c r="J758" s="3" t="n"/>
+      <c r="K758" s="3" t="n"/>
     </row>
     <row r="759">
       <c r="F759" t="inlineStr">
@@ -8851,6 +9617,7 @@
       <c r="H759" s="2" t="n"/>
       <c r="I759" s="3" t="n"/>
       <c r="J759" s="3" t="n"/>
+      <c r="K759" s="3" t="n"/>
     </row>
     <row r="760">
       <c r="F760" t="inlineStr">
@@ -8862,6 +9629,7 @@
       <c r="H760" s="2" t="n"/>
       <c r="I760" s="3" t="n"/>
       <c r="J760" s="3" t="n"/>
+      <c r="K760" s="3" t="n"/>
     </row>
     <row r="761">
       <c r="F761" t="inlineStr">
@@ -8873,6 +9641,7 @@
       <c r="H761" s="2" t="n"/>
       <c r="I761" s="3" t="n"/>
       <c r="J761" s="3" t="n"/>
+      <c r="K761" s="3" t="n"/>
     </row>
     <row r="762">
       <c r="F762" t="inlineStr">
@@ -8884,6 +9653,7 @@
       <c r="H762" s="2" t="n"/>
       <c r="I762" s="3" t="n"/>
       <c r="J762" s="3" t="n"/>
+      <c r="K762" s="3" t="n"/>
     </row>
     <row r="763">
       <c r="F763" t="inlineStr">
@@ -8895,6 +9665,7 @@
       <c r="H763" s="2" t="n"/>
       <c r="I763" s="3" t="n"/>
       <c r="J763" s="3" t="n"/>
+      <c r="K763" s="3" t="n"/>
     </row>
     <row r="764">
       <c r="F764" t="inlineStr">
@@ -8906,6 +9677,7 @@
       <c r="H764" s="2" t="n"/>
       <c r="I764" s="3" t="n"/>
       <c r="J764" s="3" t="n"/>
+      <c r="K764" s="3" t="n"/>
     </row>
     <row r="765">
       <c r="F765" t="inlineStr">
@@ -8917,6 +9689,7 @@
       <c r="H765" s="2" t="n"/>
       <c r="I765" s="3" t="n"/>
       <c r="J765" s="3" t="n"/>
+      <c r="K765" s="3" t="n"/>
     </row>
     <row r="766">
       <c r="F766" t="inlineStr">
@@ -8928,6 +9701,7 @@
       <c r="H766" s="2" t="n"/>
       <c r="I766" s="3" t="n"/>
       <c r="J766" s="3" t="n"/>
+      <c r="K766" s="3" t="n"/>
     </row>
     <row r="767">
       <c r="F767" t="inlineStr">
@@ -8939,6 +9713,7 @@
       <c r="H767" s="2" t="n"/>
       <c r="I767" s="3" t="n"/>
       <c r="J767" s="3" t="n"/>
+      <c r="K767" s="3" t="n"/>
     </row>
     <row r="768">
       <c r="F768" t="inlineStr">
@@ -8950,6 +9725,7 @@
       <c r="H768" s="2" t="n"/>
       <c r="I768" s="3" t="n"/>
       <c r="J768" s="3" t="n"/>
+      <c r="K768" s="3" t="n"/>
     </row>
     <row r="769">
       <c r="F769" t="inlineStr">
@@ -8961,6 +9737,7 @@
       <c r="H769" s="2" t="n"/>
       <c r="I769" s="3" t="n"/>
       <c r="J769" s="3" t="n"/>
+      <c r="K769" s="3" t="n"/>
     </row>
     <row r="770">
       <c r="F770" t="inlineStr">
@@ -8972,6 +9749,7 @@
       <c r="H770" s="2" t="n"/>
       <c r="I770" s="3" t="n"/>
       <c r="J770" s="3" t="n"/>
+      <c r="K770" s="3" t="n"/>
     </row>
     <row r="771">
       <c r="F771" t="inlineStr">
@@ -8983,6 +9761,7 @@
       <c r="H771" s="2" t="n"/>
       <c r="I771" s="3" t="n"/>
       <c r="J771" s="3" t="n"/>
+      <c r="K771" s="3" t="n"/>
     </row>
     <row r="772">
       <c r="F772" t="inlineStr">
@@ -8994,6 +9773,7 @@
       <c r="H772" s="2" t="n"/>
       <c r="I772" s="3" t="n"/>
       <c r="J772" s="3" t="n"/>
+      <c r="K772" s="3" t="n"/>
     </row>
     <row r="773">
       <c r="F773" t="inlineStr">
@@ -9005,6 +9785,7 @@
       <c r="H773" s="2" t="n"/>
       <c r="I773" s="3" t="n"/>
       <c r="J773" s="3" t="n"/>
+      <c r="K773" s="3" t="n"/>
     </row>
     <row r="774">
       <c r="F774" t="inlineStr">
@@ -9016,6 +9797,7 @@
       <c r="H774" s="2" t="n"/>
       <c r="I774" s="3" t="n"/>
       <c r="J774" s="3" t="n"/>
+      <c r="K774" s="3" t="n"/>
     </row>
     <row r="775">
       <c r="F775" t="inlineStr">
@@ -9027,6 +9809,7 @@
       <c r="H775" s="2" t="n"/>
       <c r="I775" s="3" t="n"/>
       <c r="J775" s="3" t="n"/>
+      <c r="K775" s="3" t="n"/>
     </row>
     <row r="776">
       <c r="F776" t="inlineStr">
@@ -9038,6 +9821,7 @@
       <c r="H776" s="2" t="n"/>
       <c r="I776" s="3" t="n"/>
       <c r="J776" s="3" t="n"/>
+      <c r="K776" s="3" t="n"/>
     </row>
     <row r="777">
       <c r="F777" t="inlineStr">
@@ -9049,6 +9833,7 @@
       <c r="H777" s="2" t="n"/>
       <c r="I777" s="3" t="n"/>
       <c r="J777" s="3" t="n"/>
+      <c r="K777" s="3" t="n"/>
     </row>
     <row r="778">
       <c r="F778" t="inlineStr">
@@ -9060,6 +9845,7 @@
       <c r="H778" s="2" t="n"/>
       <c r="I778" s="3" t="n"/>
       <c r="J778" s="3" t="n"/>
+      <c r="K778" s="3" t="n"/>
     </row>
     <row r="779">
       <c r="F779" t="inlineStr">
@@ -9071,6 +9857,7 @@
       <c r="H779" s="2" t="n"/>
       <c r="I779" s="3" t="n"/>
       <c r="J779" s="3" t="n"/>
+      <c r="K779" s="3" t="n"/>
     </row>
     <row r="780">
       <c r="F780" t="inlineStr">
@@ -9082,6 +9869,7 @@
       <c r="H780" s="2" t="n"/>
       <c r="I780" s="3" t="n"/>
       <c r="J780" s="3" t="n"/>
+      <c r="K780" s="3" t="n"/>
     </row>
     <row r="781">
       <c r="F781" t="inlineStr">
@@ -9093,6 +9881,7 @@
       <c r="H781" s="2" t="n"/>
       <c r="I781" s="3" t="n"/>
       <c r="J781" s="3" t="n"/>
+      <c r="K781" s="3" t="n"/>
     </row>
     <row r="782">
       <c r="F782" t="inlineStr">
@@ -9104,6 +9893,7 @@
       <c r="H782" s="2" t="n"/>
       <c r="I782" s="3" t="n"/>
       <c r="J782" s="3" t="n"/>
+      <c r="K782" s="3" t="n"/>
     </row>
     <row r="783">
       <c r="F783" t="inlineStr">
@@ -9115,6 +9905,7 @@
       <c r="H783" s="2" t="n"/>
       <c r="I783" s="3" t="n"/>
       <c r="J783" s="3" t="n"/>
+      <c r="K783" s="3" t="n"/>
     </row>
     <row r="784">
       <c r="F784" t="inlineStr">
@@ -9126,6 +9917,7 @@
       <c r="H784" s="2" t="n"/>
       <c r="I784" s="3" t="n"/>
       <c r="J784" s="3" t="n"/>
+      <c r="K784" s="3" t="n"/>
     </row>
     <row r="785">
       <c r="F785" t="inlineStr">
@@ -9137,6 +9929,7 @@
       <c r="H785" s="2" t="n"/>
       <c r="I785" s="3" t="n"/>
       <c r="J785" s="3" t="n"/>
+      <c r="K785" s="3" t="n"/>
     </row>
     <row r="786">
       <c r="F786" t="inlineStr">
@@ -9148,6 +9941,7 @@
       <c r="H786" s="2" t="n"/>
       <c r="I786" s="3" t="n"/>
       <c r="J786" s="3" t="n"/>
+      <c r="K786" s="3" t="n"/>
     </row>
     <row r="787">
       <c r="F787" t="inlineStr">
@@ -9159,6 +9953,7 @@
       <c r="H787" s="2" t="n"/>
       <c r="I787" s="3" t="n"/>
       <c r="J787" s="3" t="n"/>
+      <c r="K787" s="3" t="n"/>
     </row>
     <row r="788">
       <c r="F788" t="inlineStr">
@@ -9170,6 +9965,7 @@
       <c r="H788" s="2" t="n"/>
       <c r="I788" s="3" t="n"/>
       <c r="J788" s="3" t="n"/>
+      <c r="K788" s="3" t="n"/>
     </row>
     <row r="789">
       <c r="F789" t="inlineStr">
@@ -9181,6 +9977,7 @@
       <c r="H789" s="2" t="n"/>
       <c r="I789" s="3" t="n"/>
       <c r="J789" s="3" t="n"/>
+      <c r="K789" s="3" t="n"/>
     </row>
     <row r="790">
       <c r="F790" t="inlineStr">
@@ -9192,6 +9989,7 @@
       <c r="H790" s="2" t="n"/>
       <c r="I790" s="3" t="n"/>
       <c r="J790" s="3" t="n"/>
+      <c r="K790" s="3" t="n"/>
     </row>
     <row r="791">
       <c r="F791" t="inlineStr">
@@ -9203,6 +10001,7 @@
       <c r="H791" s="2" t="n"/>
       <c r="I791" s="3" t="n"/>
       <c r="J791" s="3" t="n"/>
+      <c r="K791" s="3" t="n"/>
     </row>
     <row r="792">
       <c r="F792" t="inlineStr">
@@ -9214,6 +10013,7 @@
       <c r="H792" s="2" t="n"/>
       <c r="I792" s="3" t="n"/>
       <c r="J792" s="3" t="n"/>
+      <c r="K792" s="3" t="n"/>
     </row>
     <row r="793">
       <c r="F793" t="inlineStr">
@@ -9225,6 +10025,7 @@
       <c r="H793" s="2" t="n"/>
       <c r="I793" s="3" t="n"/>
       <c r="J793" s="3" t="n"/>
+      <c r="K793" s="3" t="n"/>
     </row>
     <row r="794">
       <c r="F794" t="inlineStr">
@@ -9236,6 +10037,7 @@
       <c r="H794" s="2" t="n"/>
       <c r="I794" s="3" t="n"/>
       <c r="J794" s="3" t="n"/>
+      <c r="K794" s="3" t="n"/>
     </row>
     <row r="795">
       <c r="F795" t="inlineStr">
@@ -9247,6 +10049,7 @@
       <c r="H795" s="2" t="n"/>
       <c r="I795" s="3" t="n"/>
       <c r="J795" s="3" t="n"/>
+      <c r="K795" s="3" t="n"/>
     </row>
     <row r="796">
       <c r="F796" t="inlineStr">
@@ -9258,6 +10061,7 @@
       <c r="H796" s="2" t="n"/>
       <c r="I796" s="3" t="n"/>
       <c r="J796" s="3" t="n"/>
+      <c r="K796" s="3" t="n"/>
     </row>
     <row r="797">
       <c r="F797" t="inlineStr">
@@ -9269,6 +10073,7 @@
       <c r="H797" s="2" t="n"/>
       <c r="I797" s="3" t="n"/>
       <c r="J797" s="3" t="n"/>
+      <c r="K797" s="3" t="n"/>
     </row>
     <row r="798">
       <c r="F798" t="inlineStr">
@@ -9280,6 +10085,7 @@
       <c r="H798" s="2" t="n"/>
       <c r="I798" s="3" t="n"/>
       <c r="J798" s="3" t="n"/>
+      <c r="K798" s="3" t="n"/>
     </row>
     <row r="799">
       <c r="F799" t="inlineStr">
@@ -9291,6 +10097,7 @@
       <c r="H799" s="2" t="n"/>
       <c r="I799" s="3" t="n"/>
       <c r="J799" s="3" t="n"/>
+      <c r="K799" s="3" t="n"/>
     </row>
     <row r="800">
       <c r="F800" t="inlineStr">
@@ -9302,6 +10109,7 @@
       <c r="H800" s="2" t="n"/>
       <c r="I800" s="3" t="n"/>
       <c r="J800" s="3" t="n"/>
+      <c r="K800" s="3" t="n"/>
     </row>
     <row r="801">
       <c r="F801" t="inlineStr">
@@ -9313,6 +10121,7 @@
       <c r="H801" s="2" t="n"/>
       <c r="I801" s="3" t="n"/>
       <c r="J801" s="3" t="n"/>
+      <c r="K801" s="3" t="n"/>
     </row>
     <row r="802">
       <c r="F802" t="inlineStr">
@@ -9324,6 +10133,7 @@
       <c r="H802" s="2" t="n"/>
       <c r="I802" s="3" t="n"/>
       <c r="J802" s="3" t="n"/>
+      <c r="K802" s="3" t="n"/>
     </row>
     <row r="803">
       <c r="F803" t="inlineStr">
@@ -9335,6 +10145,7 @@
       <c r="H803" s="2" t="n"/>
       <c r="I803" s="3" t="n"/>
       <c r="J803" s="3" t="n"/>
+      <c r="K803" s="3" t="n"/>
     </row>
     <row r="804">
       <c r="F804" t="inlineStr">
@@ -9346,6 +10157,7 @@
       <c r="H804" s="2" t="n"/>
       <c r="I804" s="3" t="n"/>
       <c r="J804" s="3" t="n"/>
+      <c r="K804" s="3" t="n"/>
     </row>
     <row r="805">
       <c r="F805" t="inlineStr">
@@ -9357,6 +10169,7 @@
       <c r="H805" s="2" t="n"/>
       <c r="I805" s="3" t="n"/>
       <c r="J805" s="3" t="n"/>
+      <c r="K805" s="3" t="n"/>
     </row>
     <row r="806">
       <c r="F806" t="inlineStr">
@@ -9368,6 +10181,7 @@
       <c r="H806" s="2" t="n"/>
       <c r="I806" s="3" t="n"/>
       <c r="J806" s="3" t="n"/>
+      <c r="K806" s="3" t="n"/>
     </row>
     <row r="807">
       <c r="F807" t="inlineStr">
@@ -9379,6 +10193,7 @@
       <c r="H807" s="2" t="n"/>
       <c r="I807" s="3" t="n"/>
       <c r="J807" s="3" t="n"/>
+      <c r="K807" s="3" t="n"/>
     </row>
     <row r="808">
       <c r="F808" t="inlineStr">
@@ -9390,6 +10205,7 @@
       <c r="H808" s="2" t="n"/>
       <c r="I808" s="3" t="n"/>
       <c r="J808" s="3" t="n"/>
+      <c r="K808" s="3" t="n"/>
     </row>
     <row r="809">
       <c r="F809" t="inlineStr">
@@ -9401,6 +10217,7 @@
       <c r="H809" s="2" t="n"/>
       <c r="I809" s="3" t="n"/>
       <c r="J809" s="3" t="n"/>
+      <c r="K809" s="3" t="n"/>
     </row>
     <row r="810">
       <c r="F810" t="inlineStr">
@@ -9412,6 +10229,7 @@
       <c r="H810" s="2" t="n"/>
       <c r="I810" s="3" t="n"/>
       <c r="J810" s="3" t="n"/>
+      <c r="K810" s="3" t="n"/>
     </row>
     <row r="811">
       <c r="F811" t="inlineStr">
@@ -9423,6 +10241,7 @@
       <c r="H811" s="2" t="n"/>
       <c r="I811" s="3" t="n"/>
       <c r="J811" s="3" t="n"/>
+      <c r="K811" s="3" t="n"/>
     </row>
     <row r="812">
       <c r="F812" t="inlineStr">
@@ -9434,6 +10253,7 @@
       <c r="H812" s="2" t="n"/>
       <c r="I812" s="3" t="n"/>
       <c r="J812" s="3" t="n"/>
+      <c r="K812" s="3" t="n"/>
     </row>
     <row r="813">
       <c r="F813" t="inlineStr">
@@ -9445,6 +10265,7 @@
       <c r="H813" s="2" t="n"/>
       <c r="I813" s="3" t="n"/>
       <c r="J813" s="3" t="n"/>
+      <c r="K813" s="3" t="n"/>
     </row>
     <row r="814">
       <c r="F814" t="inlineStr">
@@ -9456,6 +10277,7 @@
       <c r="H814" s="2" t="n"/>
       <c r="I814" s="3" t="n"/>
       <c r="J814" s="3" t="n"/>
+      <c r="K814" s="3" t="n"/>
     </row>
     <row r="815">
       <c r="F815" t="inlineStr">
@@ -9467,6 +10289,7 @@
       <c r="H815" s="2" t="n"/>
       <c r="I815" s="3" t="n"/>
       <c r="J815" s="3" t="n"/>
+      <c r="K815" s="3" t="n"/>
     </row>
     <row r="816">
       <c r="F816" t="inlineStr">
@@ -9478,6 +10301,7 @@
       <c r="H816" s="2" t="n"/>
       <c r="I816" s="3" t="n"/>
       <c r="J816" s="3" t="n"/>
+      <c r="K816" s="3" t="n"/>
     </row>
     <row r="817">
       <c r="F817" t="inlineStr">
@@ -9489,6 +10313,7 @@
       <c r="H817" s="2" t="n"/>
       <c r="I817" s="3" t="n"/>
       <c r="J817" s="3" t="n"/>
+      <c r="K817" s="3" t="n"/>
     </row>
     <row r="818">
       <c r="F818" t="inlineStr">
@@ -9500,6 +10325,7 @@
       <c r="H818" s="2" t="n"/>
       <c r="I818" s="3" t="n"/>
       <c r="J818" s="3" t="n"/>
+      <c r="K818" s="3" t="n"/>
     </row>
     <row r="819">
       <c r="F819" t="inlineStr">
@@ -9511,6 +10337,7 @@
       <c r="H819" s="2" t="n"/>
       <c r="I819" s="3" t="n"/>
       <c r="J819" s="3" t="n"/>
+      <c r="K819" s="3" t="n"/>
     </row>
     <row r="820">
       <c r="F820" t="inlineStr">
@@ -9522,6 +10349,7 @@
       <c r="H820" s="2" t="n"/>
       <c r="I820" s="3" t="n"/>
       <c r="J820" s="3" t="n"/>
+      <c r="K820" s="3" t="n"/>
     </row>
     <row r="821">
       <c r="F821" t="inlineStr">
@@ -9533,6 +10361,7 @@
       <c r="H821" s="2" t="n"/>
       <c r="I821" s="3" t="n"/>
       <c r="J821" s="3" t="n"/>
+      <c r="K821" s="3" t="n"/>
     </row>
     <row r="822">
       <c r="F822" t="inlineStr">
@@ -9544,6 +10373,7 @@
       <c r="H822" s="2" t="n"/>
       <c r="I822" s="3" t="n"/>
       <c r="J822" s="3" t="n"/>
+      <c r="K822" s="3" t="n"/>
     </row>
     <row r="823">
       <c r="F823" t="inlineStr">
@@ -9555,6 +10385,7 @@
       <c r="H823" s="2" t="n"/>
       <c r="I823" s="3" t="n"/>
       <c r="J823" s="3" t="n"/>
+      <c r="K823" s="3" t="n"/>
     </row>
     <row r="824">
       <c r="F824" t="inlineStr">
@@ -9566,6 +10397,7 @@
       <c r="H824" s="2" t="n"/>
       <c r="I824" s="3" t="n"/>
       <c r="J824" s="3" t="n"/>
+      <c r="K824" s="3" t="n"/>
     </row>
     <row r="825">
       <c r="F825" t="inlineStr">
@@ -9577,6 +10409,7 @@
       <c r="H825" s="2" t="n"/>
       <c r="I825" s="3" t="n"/>
       <c r="J825" s="3" t="n"/>
+      <c r="K825" s="3" t="n"/>
     </row>
     <row r="826">
       <c r="F826" t="inlineStr">
@@ -9588,6 +10421,7 @@
       <c r="H826" s="2" t="n"/>
       <c r="I826" s="3" t="n"/>
       <c r="J826" s="3" t="n"/>
+      <c r="K826" s="3" t="n"/>
     </row>
     <row r="827">
       <c r="F827" t="inlineStr">
@@ -9599,6 +10433,7 @@
       <c r="H827" s="2" t="n"/>
       <c r="I827" s="3" t="n"/>
       <c r="J827" s="3" t="n"/>
+      <c r="K827" s="3" t="n"/>
     </row>
     <row r="828">
       <c r="F828" t="inlineStr">
@@ -9610,6 +10445,7 @@
       <c r="H828" s="2" t="n"/>
       <c r="I828" s="3" t="n"/>
       <c r="J828" s="3" t="n"/>
+      <c r="K828" s="3" t="n"/>
     </row>
     <row r="829">
       <c r="F829" t="inlineStr">
@@ -9621,6 +10457,7 @@
       <c r="H829" s="2" t="n"/>
       <c r="I829" s="3" t="n"/>
       <c r="J829" s="3" t="n"/>
+      <c r="K829" s="3" t="n"/>
     </row>
     <row r="830">
       <c r="F830" t="inlineStr">
@@ -9632,6 +10469,7 @@
       <c r="H830" s="2" t="n"/>
       <c r="I830" s="3" t="n"/>
       <c r="J830" s="3" t="n"/>
+      <c r="K830" s="3" t="n"/>
     </row>
     <row r="831">
       <c r="F831" t="inlineStr">
@@ -9643,6 +10481,7 @@
       <c r="H831" s="2" t="n"/>
       <c r="I831" s="3" t="n"/>
       <c r="J831" s="3" t="n"/>
+      <c r="K831" s="3" t="n"/>
     </row>
     <row r="832">
       <c r="F832" t="inlineStr">
@@ -9654,6 +10493,7 @@
       <c r="H832" s="2" t="n"/>
       <c r="I832" s="3" t="n"/>
       <c r="J832" s="3" t="n"/>
+      <c r="K832" s="3" t="n"/>
     </row>
     <row r="833">
       <c r="F833" t="inlineStr">
@@ -9665,6 +10505,7 @@
       <c r="H833" s="2" t="n"/>
       <c r="I833" s="3" t="n"/>
       <c r="J833" s="3" t="n"/>
+      <c r="K833" s="3" t="n"/>
     </row>
     <row r="834">
       <c r="F834" t="inlineStr">
@@ -9676,6 +10517,7 @@
       <c r="H834" s="2" t="n"/>
       <c r="I834" s="3" t="n"/>
       <c r="J834" s="3" t="n"/>
+      <c r="K834" s="3" t="n"/>
     </row>
     <row r="835">
       <c r="F835" t="inlineStr">
@@ -9687,6 +10529,7 @@
       <c r="H835" s="2" t="n"/>
       <c r="I835" s="3" t="n"/>
       <c r="J835" s="3" t="n"/>
+      <c r="K835" s="3" t="n"/>
     </row>
     <row r="836">
       <c r="F836" t="inlineStr">
@@ -9698,6 +10541,7 @@
       <c r="H836" s="2" t="n"/>
       <c r="I836" s="3" t="n"/>
       <c r="J836" s="3" t="n"/>
+      <c r="K836" s="3" t="n"/>
     </row>
     <row r="837">
       <c r="F837" t="inlineStr">
@@ -9709,6 +10553,7 @@
       <c r="H837" s="2" t="n"/>
       <c r="I837" s="3" t="n"/>
       <c r="J837" s="3" t="n"/>
+      <c r="K837" s="3" t="n"/>
     </row>
     <row r="838">
       <c r="F838" t="inlineStr">
@@ -9720,6 +10565,7 @@
       <c r="H838" s="2" t="n"/>
       <c r="I838" s="3" t="n"/>
       <c r="J838" s="3" t="n"/>
+      <c r="K838" s="3" t="n"/>
     </row>
     <row r="839">
       <c r="F839" t="inlineStr">
@@ -9731,6 +10577,7 @@
       <c r="H839" s="2" t="n"/>
       <c r="I839" s="3" t="n"/>
       <c r="J839" s="3" t="n"/>
+      <c r="K839" s="3" t="n"/>
     </row>
     <row r="840">
       <c r="F840" t="inlineStr">
@@ -9742,6 +10589,7 @@
       <c r="H840" s="2" t="n"/>
       <c r="I840" s="3" t="n"/>
       <c r="J840" s="3" t="n"/>
+      <c r="K840" s="3" t="n"/>
     </row>
     <row r="841">
       <c r="F841" t="inlineStr">
@@ -9753,6 +10601,7 @@
       <c r="H841" s="2" t="n"/>
       <c r="I841" s="3" t="n"/>
       <c r="J841" s="3" t="n"/>
+      <c r="K841" s="3" t="n"/>
     </row>
     <row r="842">
       <c r="F842" t="inlineStr">
@@ -9764,6 +10613,7 @@
       <c r="H842" s="2" t="n"/>
       <c r="I842" s="3" t="n"/>
       <c r="J842" s="3" t="n"/>
+      <c r="K842" s="3" t="n"/>
     </row>
     <row r="843">
       <c r="F843" t="inlineStr">
@@ -9775,6 +10625,7 @@
       <c r="H843" s="2" t="n"/>
       <c r="I843" s="3" t="n"/>
       <c r="J843" s="3" t="n"/>
+      <c r="K843" s="3" t="n"/>
     </row>
     <row r="844">
       <c r="F844" t="inlineStr">
@@ -9786,6 +10637,7 @@
       <c r="H844" s="2" t="n"/>
       <c r="I844" s="3" t="n"/>
       <c r="J844" s="3" t="n"/>
+      <c r="K844" s="3" t="n"/>
     </row>
     <row r="845">
       <c r="F845" t="inlineStr">
@@ -9797,6 +10649,7 @@
       <c r="H845" s="2" t="n"/>
       <c r="I845" s="3" t="n"/>
       <c r="J845" s="3" t="n"/>
+      <c r="K845" s="3" t="n"/>
     </row>
     <row r="846">
       <c r="F846" t="inlineStr">
@@ -9808,6 +10661,7 @@
       <c r="H846" s="2" t="n"/>
       <c r="I846" s="3" t="n"/>
       <c r="J846" s="3" t="n"/>
+      <c r="K846" s="3" t="n"/>
     </row>
     <row r="847">
       <c r="F847" t="inlineStr">
@@ -9819,6 +10673,7 @@
       <c r="H847" s="2" t="n"/>
       <c r="I847" s="3" t="n"/>
       <c r="J847" s="3" t="n"/>
+      <c r="K847" s="3" t="n"/>
     </row>
     <row r="848">
       <c r="F848" t="inlineStr">
@@ -9830,6 +10685,7 @@
       <c r="H848" s="2" t="n"/>
       <c r="I848" s="3" t="n"/>
       <c r="J848" s="3" t="n"/>
+      <c r="K848" s="3" t="n"/>
     </row>
     <row r="849">
       <c r="F849" t="inlineStr">
@@ -9841,6 +10697,7 @@
       <c r="H849" s="2" t="n"/>
       <c r="I849" s="3" t="n"/>
       <c r="J849" s="3" t="n"/>
+      <c r="K849" s="3" t="n"/>
     </row>
     <row r="850">
       <c r="F850" t="inlineStr">
@@ -9852,6 +10709,7 @@
       <c r="H850" s="2" t="n"/>
       <c r="I850" s="3" t="n"/>
       <c r="J850" s="3" t="n"/>
+      <c r="K850" s="3" t="n"/>
     </row>
     <row r="851">
       <c r="F851" t="inlineStr">
@@ -9863,6 +10721,7 @@
       <c r="H851" s="2" t="n"/>
       <c r="I851" s="3" t="n"/>
       <c r="J851" s="3" t="n"/>
+      <c r="K851" s="3" t="n"/>
     </row>
     <row r="852">
       <c r="F852" t="inlineStr">
@@ -9874,6 +10733,7 @@
       <c r="H852" s="2" t="n"/>
       <c r="I852" s="3" t="n"/>
       <c r="J852" s="3" t="n"/>
+      <c r="K852" s="3" t="n"/>
     </row>
     <row r="853">
       <c r="F853" t="inlineStr">
@@ -9885,6 +10745,7 @@
       <c r="H853" s="2" t="n"/>
       <c r="I853" s="3" t="n"/>
       <c r="J853" s="3" t="n"/>
+      <c r="K853" s="3" t="n"/>
     </row>
     <row r="854">
       <c r="F854" t="inlineStr">
@@ -9896,6 +10757,7 @@
       <c r="H854" s="2" t="n"/>
       <c r="I854" s="3" t="n"/>
       <c r="J854" s="3" t="n"/>
+      <c r="K854" s="3" t="n"/>
     </row>
     <row r="855">
       <c r="F855" t="inlineStr">
@@ -9907,6 +10769,7 @@
       <c r="H855" s="2" t="n"/>
       <c r="I855" s="3" t="n"/>
       <c r="J855" s="3" t="n"/>
+      <c r="K855" s="3" t="n"/>
     </row>
     <row r="856">
       <c r="F856" t="inlineStr">
@@ -9918,6 +10781,7 @@
       <c r="H856" s="2" t="n"/>
       <c r="I856" s="3" t="n"/>
       <c r="J856" s="3" t="n"/>
+      <c r="K856" s="3" t="n"/>
     </row>
     <row r="857">
       <c r="F857" t="inlineStr">
@@ -9929,6 +10793,7 @@
       <c r="H857" s="2" t="n"/>
       <c r="I857" s="3" t="n"/>
       <c r="J857" s="3" t="n"/>
+      <c r="K857" s="3" t="n"/>
     </row>
     <row r="858">
       <c r="F858" t="inlineStr">
@@ -9940,6 +10805,7 @@
       <c r="H858" s="2" t="n"/>
       <c r="I858" s="3" t="n"/>
       <c r="J858" s="3" t="n"/>
+      <c r="K858" s="3" t="n"/>
     </row>
     <row r="859">
       <c r="F859" t="inlineStr">
@@ -9951,6 +10817,7 @@
       <c r="H859" s="2" t="n"/>
       <c r="I859" s="3" t="n"/>
       <c r="J859" s="3" t="n"/>
+      <c r="K859" s="3" t="n"/>
     </row>
     <row r="860">
       <c r="F860" t="inlineStr">
@@ -9962,6 +10829,7 @@
       <c r="H860" s="2" t="n"/>
       <c r="I860" s="3" t="n"/>
       <c r="J860" s="3" t="n"/>
+      <c r="K860" s="3" t="n"/>
     </row>
     <row r="861">
       <c r="F861" t="inlineStr">
@@ -9973,6 +10841,7 @@
       <c r="H861" s="2" t="n"/>
       <c r="I861" s="3" t="n"/>
       <c r="J861" s="3" t="n"/>
+      <c r="K861" s="3" t="n"/>
     </row>
     <row r="862">
       <c r="F862" t="inlineStr">
@@ -9984,6 +10853,7 @@
       <c r="H862" s="2" t="n"/>
       <c r="I862" s="3" t="n"/>
       <c r="J862" s="3" t="n"/>
+      <c r="K862" s="3" t="n"/>
     </row>
     <row r="863">
       <c r="F863" t="inlineStr">
@@ -9995,6 +10865,7 @@
       <c r="H863" s="2" t="n"/>
       <c r="I863" s="3" t="n"/>
       <c r="J863" s="3" t="n"/>
+      <c r="K863" s="3" t="n"/>
     </row>
     <row r="864">
       <c r="F864" t="inlineStr">
@@ -10006,6 +10877,7 @@
       <c r="H864" s="2" t="n"/>
       <c r="I864" s="3" t="n"/>
       <c r="J864" s="3" t="n"/>
+      <c r="K864" s="3" t="n"/>
     </row>
     <row r="865">
       <c r="F865" t="inlineStr">
@@ -10017,6 +10889,7 @@
       <c r="H865" s="2" t="n"/>
       <c r="I865" s="3" t="n"/>
       <c r="J865" s="3" t="n"/>
+      <c r="K865" s="3" t="n"/>
     </row>
     <row r="866">
       <c r="F866" t="inlineStr">
@@ -10028,6 +10901,7 @@
       <c r="H866" s="2" t="n"/>
       <c r="I866" s="3" t="n"/>
       <c r="J866" s="3" t="n"/>
+      <c r="K866" s="3" t="n"/>
     </row>
     <row r="867">
       <c r="F867" t="inlineStr">
@@ -10039,6 +10913,7 @@
       <c r="H867" s="2" t="n"/>
       <c r="I867" s="3" t="n"/>
       <c r="J867" s="3" t="n"/>
+      <c r="K867" s="3" t="n"/>
     </row>
     <row r="868">
       <c r="F868" t="inlineStr">
@@ -10050,6 +10925,7 @@
       <c r="H868" s="2" t="n"/>
       <c r="I868" s="3" t="n"/>
       <c r="J868" s="3" t="n"/>
+      <c r="K868" s="3" t="n"/>
     </row>
     <row r="869">
       <c r="F869" t="inlineStr">
@@ -10061,6 +10937,7 @@
       <c r="H869" s="2" t="n"/>
       <c r="I869" s="3" t="n"/>
       <c r="J869" s="3" t="n"/>
+      <c r="K869" s="3" t="n"/>
     </row>
     <row r="870">
       <c r="F870" t="inlineStr">
@@ -10072,6 +10949,7 @@
       <c r="H870" s="2" t="n"/>
       <c r="I870" s="3" t="n"/>
       <c r="J870" s="3" t="n"/>
+      <c r="K870" s="3" t="n"/>
     </row>
     <row r="871">
       <c r="F871" t="inlineStr">
@@ -10083,6 +10961,7 @@
       <c r="H871" s="2" t="n"/>
       <c r="I871" s="3" t="n"/>
       <c r="J871" s="3" t="n"/>
+      <c r="K871" s="3" t="n"/>
     </row>
     <row r="872">
       <c r="F872" t="inlineStr">
@@ -10094,6 +10973,7 @@
       <c r="H872" s="2" t="n"/>
       <c r="I872" s="3" t="n"/>
       <c r="J872" s="3" t="n"/>
+      <c r="K872" s="3" t="n"/>
     </row>
     <row r="873">
       <c r="F873" t="inlineStr">
@@ -10105,6 +10985,7 @@
       <c r="H873" s="2" t="n"/>
       <c r="I873" s="3" t="n"/>
       <c r="J873" s="3" t="n"/>
+      <c r="K873" s="3" t="n"/>
     </row>
     <row r="874">
       <c r="F874" t="inlineStr">
@@ -10116,6 +10997,7 @@
       <c r="H874" s="2" t="n"/>
       <c r="I874" s="3" t="n"/>
       <c r="J874" s="3" t="n"/>
+      <c r="K874" s="3" t="n"/>
     </row>
     <row r="875">
       <c r="F875" t="inlineStr">
@@ -10127,6 +11009,7 @@
       <c r="H875" s="2" t="n"/>
       <c r="I875" s="3" t="n"/>
       <c r="J875" s="3" t="n"/>
+      <c r="K875" s="3" t="n"/>
     </row>
     <row r="876">
       <c r="F876" t="inlineStr">
@@ -10138,6 +11021,7 @@
       <c r="H876" s="2" t="n"/>
       <c r="I876" s="3" t="n"/>
       <c r="J876" s="3" t="n"/>
+      <c r="K876" s="3" t="n"/>
     </row>
     <row r="877">
       <c r="F877" t="inlineStr">
@@ -10149,6 +11033,7 @@
       <c r="H877" s="2" t="n"/>
       <c r="I877" s="3" t="n"/>
       <c r="J877" s="3" t="n"/>
+      <c r="K877" s="3" t="n"/>
     </row>
     <row r="878">
       <c r="F878" t="inlineStr">
@@ -10160,6 +11045,7 @@
       <c r="H878" s="2" t="n"/>
       <c r="I878" s="3" t="n"/>
       <c r="J878" s="3" t="n"/>
+      <c r="K878" s="3" t="n"/>
     </row>
     <row r="879">
       <c r="F879" t="inlineStr">
@@ -10171,6 +11057,7 @@
       <c r="H879" s="2" t="n"/>
       <c r="I879" s="3" t="n"/>
       <c r="J879" s="3" t="n"/>
+      <c r="K879" s="3" t="n"/>
     </row>
     <row r="880">
       <c r="F880" t="inlineStr">
@@ -10182,6 +11069,7 @@
       <c r="H880" s="2" t="n"/>
       <c r="I880" s="3" t="n"/>
       <c r="J880" s="3" t="n"/>
+      <c r="K880" s="3" t="n"/>
     </row>
     <row r="881">
       <c r="F881" t="inlineStr">
@@ -10193,6 +11081,7 @@
       <c r="H881" s="2" t="n"/>
       <c r="I881" s="3" t="n"/>
       <c r="J881" s="3" t="n"/>
+      <c r="K881" s="3" t="n"/>
     </row>
     <row r="882">
       <c r="F882" t="inlineStr">
@@ -10204,6 +11093,7 @@
       <c r="H882" s="2" t="n"/>
       <c r="I882" s="3" t="n"/>
       <c r="J882" s="3" t="n"/>
+      <c r="K882" s="3" t="n"/>
     </row>
     <row r="883">
       <c r="F883" t="inlineStr">
@@ -10215,6 +11105,7 @@
       <c r="H883" s="2" t="n"/>
       <c r="I883" s="3" t="n"/>
       <c r="J883" s="3" t="n"/>
+      <c r="K883" s="3" t="n"/>
     </row>
     <row r="884">
       <c r="F884" t="inlineStr">
@@ -10226,6 +11117,7 @@
       <c r="H884" s="2" t="n"/>
       <c r="I884" s="3" t="n"/>
       <c r="J884" s="3" t="n"/>
+      <c r="K884" s="3" t="n"/>
     </row>
     <row r="885">
       <c r="F885" t="inlineStr">
@@ -10237,6 +11129,7 @@
       <c r="H885" s="2" t="n"/>
       <c r="I885" s="3" t="n"/>
       <c r="J885" s="3" t="n"/>
+      <c r="K885" s="3" t="n"/>
     </row>
     <row r="886">
       <c r="F886" t="inlineStr">
@@ -10248,6 +11141,7 @@
       <c r="H886" s="2" t="n"/>
       <c r="I886" s="3" t="n"/>
       <c r="J886" s="3" t="n"/>
+      <c r="K886" s="3" t="n"/>
     </row>
     <row r="887">
       <c r="F887" t="inlineStr">
@@ -10259,6 +11153,7 @@
       <c r="H887" s="2" t="n"/>
       <c r="I887" s="3" t="n"/>
       <c r="J887" s="3" t="n"/>
+      <c r="K887" s="3" t="n"/>
     </row>
     <row r="888">
       <c r="F888" t="inlineStr">
@@ -10270,6 +11165,7 @@
       <c r="H888" s="2" t="n"/>
       <c r="I888" s="3" t="n"/>
       <c r="J888" s="3" t="n"/>
+      <c r="K888" s="3" t="n"/>
     </row>
     <row r="889">
       <c r="F889" t="inlineStr">
@@ -10281,6 +11177,7 @@
       <c r="H889" s="2" t="n"/>
       <c r="I889" s="3" t="n"/>
       <c r="J889" s="3" t="n"/>
+      <c r="K889" s="3" t="n"/>
     </row>
     <row r="890">
       <c r="F890" t="inlineStr">
@@ -10292,6 +11189,7 @@
       <c r="H890" s="2" t="n"/>
       <c r="I890" s="3" t="n"/>
       <c r="J890" s="3" t="n"/>
+      <c r="K890" s="3" t="n"/>
     </row>
     <row r="891">
       <c r="F891" t="inlineStr">
@@ -10303,6 +11201,7 @@
       <c r="H891" s="2" t="n"/>
       <c r="I891" s="3" t="n"/>
       <c r="J891" s="3" t="n"/>
+      <c r="K891" s="3" t="n"/>
     </row>
     <row r="892">
       <c r="F892" t="inlineStr">
@@ -10314,6 +11213,7 @@
       <c r="H892" s="2" t="n"/>
       <c r="I892" s="3" t="n"/>
       <c r="J892" s="3" t="n"/>
+      <c r="K892" s="3" t="n"/>
     </row>
     <row r="893">
       <c r="F893" t="inlineStr">
@@ -10325,6 +11225,7 @@
       <c r="H893" s="2" t="n"/>
       <c r="I893" s="3" t="n"/>
       <c r="J893" s="3" t="n"/>
+      <c r="K893" s="3" t="n"/>
     </row>
     <row r="894">
       <c r="F894" t="inlineStr">
@@ -10336,6 +11237,7 @@
       <c r="H894" s="2" t="n"/>
       <c r="I894" s="3" t="n"/>
       <c r="J894" s="3" t="n"/>
+      <c r="K894" s="3" t="n"/>
     </row>
     <row r="895">
       <c r="F895" t="inlineStr">
@@ -10347,6 +11249,7 @@
       <c r="H895" s="2" t="n"/>
       <c r="I895" s="3" t="n"/>
       <c r="J895" s="3" t="n"/>
+      <c r="K895" s="3" t="n"/>
     </row>
     <row r="896">
       <c r="F896" t="inlineStr">
@@ -10358,6 +11261,7 @@
       <c r="H896" s="2" t="n"/>
       <c r="I896" s="3" t="n"/>
       <c r="J896" s="3" t="n"/>
+      <c r="K896" s="3" t="n"/>
     </row>
     <row r="897">
       <c r="F897" t="inlineStr">
@@ -10369,6 +11273,7 @@
       <c r="H897" s="2" t="n"/>
       <c r="I897" s="3" t="n"/>
       <c r="J897" s="3" t="n"/>
+      <c r="K897" s="3" t="n"/>
     </row>
     <row r="898">
       <c r="F898" t="inlineStr">
@@ -10380,6 +11285,7 @@
       <c r="H898" s="2" t="n"/>
       <c r="I898" s="3" t="n"/>
       <c r="J898" s="3" t="n"/>
+      <c r="K898" s="3" t="n"/>
     </row>
     <row r="899">
       <c r="F899" t="inlineStr">
@@ -10391,6 +11297,7 @@
       <c r="H899" s="2" t="n"/>
       <c r="I899" s="3" t="n"/>
       <c r="J899" s="3" t="n"/>
+      <c r="K899" s="3" t="n"/>
     </row>
     <row r="900">
       <c r="F900" t="inlineStr">
@@ -10402,6 +11309,7 @@
       <c r="H900" s="2" t="n"/>
       <c r="I900" s="3" t="n"/>
       <c r="J900" s="3" t="n"/>
+      <c r="K900" s="3" t="n"/>
     </row>
     <row r="901">
       <c r="F901" t="inlineStr">
@@ -10413,6 +11321,7 @@
       <c r="H901" s="2" t="n"/>
       <c r="I901" s="3" t="n"/>
       <c r="J901" s="3" t="n"/>
+      <c r="K901" s="3" t="n"/>
     </row>
     <row r="902">
       <c r="F902" t="inlineStr">
@@ -10424,6 +11333,7 @@
       <c r="H902" s="2" t="n"/>
       <c r="I902" s="3" t="n"/>
       <c r="J902" s="3" t="n"/>
+      <c r="K902" s="3" t="n"/>
     </row>
     <row r="903">
       <c r="F903" t="inlineStr">
@@ -10435,6 +11345,7 @@
       <c r="H903" s="2" t="n"/>
       <c r="I903" s="3" t="n"/>
       <c r="J903" s="3" t="n"/>
+      <c r="K903" s="3" t="n"/>
     </row>
     <row r="904">
       <c r="F904" t="inlineStr">
@@ -10446,6 +11357,7 @@
       <c r="H904" s="2" t="n"/>
       <c r="I904" s="3" t="n"/>
       <c r="J904" s="3" t="n"/>
+      <c r="K904" s="3" t="n"/>
     </row>
     <row r="905">
       <c r="F905" t="inlineStr">
@@ -10457,6 +11369,7 @@
       <c r="H905" s="2" t="n"/>
       <c r="I905" s="3" t="n"/>
       <c r="J905" s="3" t="n"/>
+      <c r="K905" s="3" t="n"/>
     </row>
     <row r="906">
       <c r="F906" t="inlineStr">
@@ -10468,6 +11381,7 @@
       <c r="H906" s="2" t="n"/>
       <c r="I906" s="3" t="n"/>
       <c r="J906" s="3" t="n"/>
+      <c r="K906" s="3" t="n"/>
     </row>
     <row r="907">
       <c r="F907" t="inlineStr">
@@ -10479,6 +11393,7 @@
       <c r="H907" s="2" t="n"/>
       <c r="I907" s="3" t="n"/>
       <c r="J907" s="3" t="n"/>
+      <c r="K907" s="3" t="n"/>
     </row>
     <row r="908">
       <c r="F908" t="inlineStr">
@@ -10490,6 +11405,7 @@
       <c r="H908" s="2" t="n"/>
       <c r="I908" s="3" t="n"/>
       <c r="J908" s="3" t="n"/>
+      <c r="K908" s="3" t="n"/>
     </row>
     <row r="909">
       <c r="F909" t="inlineStr">
@@ -10501,6 +11417,7 @@
       <c r="H909" s="2" t="n"/>
       <c r="I909" s="3" t="n"/>
       <c r="J909" s="3" t="n"/>
+      <c r="K909" s="3" t="n"/>
     </row>
     <row r="910">
       <c r="F910" t="inlineStr">
@@ -10512,6 +11429,7 @@
       <c r="H910" s="2" t="n"/>
       <c r="I910" s="3" t="n"/>
       <c r="J910" s="3" t="n"/>
+      <c r="K910" s="3" t="n"/>
     </row>
     <row r="911">
       <c r="F911" t="inlineStr">
@@ -10523,6 +11441,7 @@
       <c r="H911" s="2" t="n"/>
       <c r="I911" s="3" t="n"/>
       <c r="J911" s="3" t="n"/>
+      <c r="K911" s="3" t="n"/>
     </row>
     <row r="912">
       <c r="F912" t="inlineStr">
@@ -10534,6 +11453,7 @@
       <c r="H912" s="2" t="n"/>
       <c r="I912" s="3" t="n"/>
       <c r="J912" s="3" t="n"/>
+      <c r="K912" s="3" t="n"/>
     </row>
     <row r="913">
       <c r="F913" t="inlineStr">
@@ -10545,6 +11465,7 @@
       <c r="H913" s="2" t="n"/>
       <c r="I913" s="3" t="n"/>
       <c r="J913" s="3" t="n"/>
+      <c r="K913" s="3" t="n"/>
     </row>
     <row r="914">
       <c r="F914" t="inlineStr">
@@ -10556,6 +11477,7 @@
       <c r="H914" s="2" t="n"/>
       <c r="I914" s="3" t="n"/>
       <c r="J914" s="3" t="n"/>
+      <c r="K914" s="3" t="n"/>
     </row>
     <row r="915">
       <c r="F915" t="inlineStr">
@@ -10567,6 +11489,7 @@
       <c r="H915" s="2" t="n"/>
       <c r="I915" s="3" t="n"/>
       <c r="J915" s="3" t="n"/>
+      <c r="K915" s="3" t="n"/>
     </row>
     <row r="916">
       <c r="F916" t="inlineStr">
@@ -10578,6 +11501,7 @@
       <c r="H916" s="2" t="n"/>
       <c r="I916" s="3" t="n"/>
       <c r="J916" s="3" t="n"/>
+      <c r="K916" s="3" t="n"/>
     </row>
     <row r="917">
       <c r="F917" t="inlineStr">
@@ -10589,6 +11513,7 @@
       <c r="H917" s="2" t="n"/>
       <c r="I917" s="3" t="n"/>
       <c r="J917" s="3" t="n"/>
+      <c r="K917" s="3" t="n"/>
     </row>
     <row r="918">
       <c r="F918" t="inlineStr">
@@ -10600,6 +11525,7 @@
       <c r="H918" s="2" t="n"/>
       <c r="I918" s="3" t="n"/>
       <c r="J918" s="3" t="n"/>
+      <c r="K918" s="3" t="n"/>
     </row>
     <row r="919">
       <c r="F919" t="inlineStr">
@@ -10611,6 +11537,7 @@
       <c r="H919" s="2" t="n"/>
       <c r="I919" s="3" t="n"/>
       <c r="J919" s="3" t="n"/>
+      <c r="K919" s="3" t="n"/>
     </row>
     <row r="920">
       <c r="F920" t="inlineStr">
@@ -10622,6 +11549,7 @@
       <c r="H920" s="2" t="n"/>
       <c r="I920" s="3" t="n"/>
       <c r="J920" s="3" t="n"/>
+      <c r="K920" s="3" t="n"/>
     </row>
     <row r="921">
       <c r="F921" t="inlineStr">
@@ -10633,6 +11561,7 @@
       <c r="H921" s="2" t="n"/>
       <c r="I921" s="3" t="n"/>
       <c r="J921" s="3" t="n"/>
+      <c r="K921" s="3" t="n"/>
     </row>
     <row r="922">
       <c r="F922" t="inlineStr">
@@ -10644,6 +11573,7 @@
       <c r="H922" s="2" t="n"/>
       <c r="I922" s="3" t="n"/>
       <c r="J922" s="3" t="n"/>
+      <c r="K922" s="3" t="n"/>
     </row>
     <row r="923">
       <c r="F923" t="inlineStr">
@@ -10655,6 +11585,7 @@
       <c r="H923" s="2" t="n"/>
       <c r="I923" s="3" t="n"/>
       <c r="J923" s="3" t="n"/>
+      <c r="K923" s="3" t="n"/>
     </row>
     <row r="924">
       <c r="F924" t="inlineStr">
@@ -10666,6 +11597,7 @@
       <c r="H924" s="2" t="n"/>
       <c r="I924" s="3" t="n"/>
       <c r="J924" s="3" t="n"/>
+      <c r="K924" s="3" t="n"/>
     </row>
     <row r="925">
       <c r="F925" t="inlineStr">
@@ -10677,6 +11609,7 @@
       <c r="H925" s="2" t="n"/>
       <c r="I925" s="3" t="n"/>
       <c r="J925" s="3" t="n"/>
+      <c r="K925" s="3" t="n"/>
     </row>
     <row r="926">
       <c r="F926" t="inlineStr">
@@ -10688,6 +11621,7 @@
       <c r="H926" s="2" t="n"/>
       <c r="I926" s="3" t="n"/>
       <c r="J926" s="3" t="n"/>
+      <c r="K926" s="3" t="n"/>
     </row>
     <row r="927">
       <c r="F927" t="inlineStr">
@@ -10699,6 +11633,7 @@
       <c r="H927" s="2" t="n"/>
       <c r="I927" s="3" t="n"/>
       <c r="J927" s="3" t="n"/>
+      <c r="K927" s="3" t="n"/>
     </row>
     <row r="928">
       <c r="F928" t="inlineStr">
@@ -10710,6 +11645,7 @@
       <c r="H928" s="2" t="n"/>
       <c r="I928" s="3" t="n"/>
       <c r="J928" s="3" t="n"/>
+      <c r="K928" s="3" t="n"/>
     </row>
     <row r="929">
       <c r="F929" t="inlineStr">
@@ -10721,6 +11657,7 @@
       <c r="H929" s="2" t="n"/>
       <c r="I929" s="3" t="n"/>
       <c r="J929" s="3" t="n"/>
+      <c r="K929" s="3" t="n"/>
     </row>
     <row r="930">
       <c r="F930" t="inlineStr">
@@ -10732,6 +11669,7 @@
       <c r="H930" s="2" t="n"/>
       <c r="I930" s="3" t="n"/>
       <c r="J930" s="3" t="n"/>
+      <c r="K930" s="3" t="n"/>
     </row>
     <row r="931">
       <c r="F931" t="inlineStr">
@@ -10743,6 +11681,7 @@
       <c r="H931" s="2" t="n"/>
       <c r="I931" s="3" t="n"/>
       <c r="J931" s="3" t="n"/>
+      <c r="K931" s="3" t="n"/>
     </row>
     <row r="932">
       <c r="F932" t="inlineStr">
@@ -10754,6 +11693,7 @@
       <c r="H932" s="2" t="n"/>
       <c r="I932" s="3" t="n"/>
       <c r="J932" s="3" t="n"/>
+      <c r="K932" s="3" t="n"/>
     </row>
     <row r="933">
       <c r="F933" t="inlineStr">
@@ -10765,6 +11705,7 @@
       <c r="H933" s="2" t="n"/>
       <c r="I933" s="3" t="n"/>
       <c r="J933" s="3" t="n"/>
+      <c r="K933" s="3" t="n"/>
     </row>
     <row r="934">
       <c r="F934" t="inlineStr">
@@ -10776,6 +11717,7 @@
       <c r="H934" s="2" t="n"/>
       <c r="I934" s="3" t="n"/>
       <c r="J934" s="3" t="n"/>
+      <c r="K934" s="3" t="n"/>
     </row>
     <row r="935">
       <c r="F935" t="inlineStr">
@@ -10787,6 +11729,7 @@
       <c r="H935" s="2" t="n"/>
       <c r="I935" s="3" t="n"/>
       <c r="J935" s="3" t="n"/>
+      <c r="K935" s="3" t="n"/>
     </row>
     <row r="936">
       <c r="F936" t="inlineStr">
@@ -10798,6 +11741,7 @@
       <c r="H936" s="2" t="n"/>
       <c r="I936" s="3" t="n"/>
       <c r="J936" s="3" t="n"/>
+      <c r="K936" s="3" t="n"/>
     </row>
     <row r="937">
       <c r="F937" t="inlineStr">
@@ -10809,6 +11753,7 @@
       <c r="H937" s="2" t="n"/>
       <c r="I937" s="3" t="n"/>
       <c r="J937" s="3" t="n"/>
+      <c r="K937" s="3" t="n"/>
     </row>
     <row r="938">
       <c r="F938" t="inlineStr">
@@ -10820,6 +11765,7 @@
       <c r="H938" s="2" t="n"/>
       <c r="I938" s="3" t="n"/>
       <c r="J938" s="3" t="n"/>
+      <c r="K938" s="3" t="n"/>
     </row>
     <row r="939">
       <c r="F939" t="inlineStr">
@@ -10831,6 +11777,7 @@
       <c r="H939" s="2" t="n"/>
       <c r="I939" s="3" t="n"/>
       <c r="J939" s="3" t="n"/>
+      <c r="K939" s="3" t="n"/>
     </row>
     <row r="940">
       <c r="F940" t="inlineStr">
@@ -10842,6 +11789,7 @@
       <c r="H940" s="2" t="n"/>
       <c r="I940" s="3" t="n"/>
       <c r="J940" s="3" t="n"/>
+      <c r="K940" s="3" t="n"/>
     </row>
     <row r="941">
       <c r="F941" t="inlineStr">
@@ -10853,6 +11801,7 @@
       <c r="H941" s="2" t="n"/>
       <c r="I941" s="3" t="n"/>
       <c r="J941" s="3" t="n"/>
+      <c r="K941" s="3" t="n"/>
     </row>
     <row r="942">
       <c r="F942" t="inlineStr">
@@ -10864,6 +11813,7 @@
       <c r="H942" s="2" t="n"/>
       <c r="I942" s="3" t="n"/>
       <c r="J942" s="3" t="n"/>
+      <c r="K942" s="3" t="n"/>
     </row>
     <row r="943">
       <c r="F943" t="inlineStr">
@@ -10875,6 +11825,7 @@
       <c r="H943" s="2" t="n"/>
       <c r="I943" s="3" t="n"/>
       <c r="J943" s="3" t="n"/>
+      <c r="K943" s="3" t="n"/>
     </row>
     <row r="944">
       <c r="F944" t="inlineStr">
@@ -10886,6 +11837,7 @@
       <c r="H944" s="2" t="n"/>
       <c r="I944" s="3" t="n"/>
       <c r="J944" s="3" t="n"/>
+      <c r="K944" s="3" t="n"/>
     </row>
     <row r="945">
       <c r="F945" t="inlineStr">
@@ -10897,6 +11849,7 @@
       <c r="H945" s="2" t="n"/>
       <c r="I945" s="3" t="n"/>
       <c r="J945" s="3" t="n"/>
+      <c r="K945" s="3" t="n"/>
     </row>
     <row r="946">
       <c r="F946" t="inlineStr">
@@ -10908,6 +11861,7 @@
       <c r="H946" s="2" t="n"/>
       <c r="I946" s="3" t="n"/>
       <c r="J946" s="3" t="n"/>
+      <c r="K946" s="3" t="n"/>
     </row>
     <row r="947">
       <c r="F947" t="inlineStr">
@@ -10919,6 +11873,7 @@
       <c r="H947" s="2" t="n"/>
       <c r="I947" s="3" t="n"/>
       <c r="J947" s="3" t="n"/>
+      <c r="K947" s="3" t="n"/>
     </row>
     <row r="948">
       <c r="F948" t="inlineStr">
@@ -10930,6 +11885,7 @@
       <c r="H948" s="2" t="n"/>
       <c r="I948" s="3" t="n"/>
       <c r="J948" s="3" t="n"/>
+      <c r="K948" s="3" t="n"/>
     </row>
     <row r="949">
       <c r="F949" t="inlineStr">
@@ -10941,6 +11897,7 @@
       <c r="H949" s="2" t="n"/>
       <c r="I949" s="3" t="n"/>
       <c r="J949" s="3" t="n"/>
+      <c r="K949" s="3" t="n"/>
     </row>
     <row r="950">
       <c r="F950" t="inlineStr">
@@ -10952,6 +11909,7 @@
       <c r="H950" s="2" t="n"/>
       <c r="I950" s="3" t="n"/>
       <c r="J950" s="3" t="n"/>
+      <c r="K950" s="3" t="n"/>
     </row>
     <row r="951">
       <c r="F951" t="inlineStr">
@@ -10963,6 +11921,7 @@
       <c r="H951" s="2" t="n"/>
       <c r="I951" s="3" t="n"/>
       <c r="J951" s="3" t="n"/>
+      <c r="K951" s="3" t="n"/>
     </row>
     <row r="952">
       <c r="F952" t="inlineStr">
@@ -10974,6 +11933,7 @@
       <c r="H952" s="2" t="n"/>
       <c r="I952" s="3" t="n"/>
       <c r="J952" s="3" t="n"/>
+      <c r="K952" s="3" t="n"/>
     </row>
     <row r="953">
       <c r="F953" t="inlineStr">
@@ -10985,6 +11945,7 @@
       <c r="H953" s="2" t="n"/>
       <c r="I953" s="3" t="n"/>
       <c r="J953" s="3" t="n"/>
+      <c r="K953" s="3" t="n"/>
     </row>
     <row r="954">
       <c r="F954" t="inlineStr">
@@ -10996,6 +11957,7 @@
       <c r="H954" s="2" t="n"/>
       <c r="I954" s="3" t="n"/>
       <c r="J954" s="3" t="n"/>
+      <c r="K954" s="3" t="n"/>
     </row>
     <row r="955">
       <c r="F955" t="inlineStr">
@@ -11007,6 +11969,7 @@
       <c r="H955" s="2" t="n"/>
       <c r="I955" s="3" t="n"/>
       <c r="J955" s="3" t="n"/>
+      <c r="K955" s="3" t="n"/>
     </row>
     <row r="956">
       <c r="F956" t="inlineStr">
@@ -11018,6 +11981,7 @@
       <c r="H956" s="2" t="n"/>
       <c r="I956" s="3" t="n"/>
       <c r="J956" s="3" t="n"/>
+      <c r="K956" s="3" t="n"/>
     </row>
     <row r="957">
       <c r="F957" t="inlineStr">
@@ -11029,6 +11993,7 @@
       <c r="H957" s="2" t="n"/>
       <c r="I957" s="3" t="n"/>
       <c r="J957" s="3" t="n"/>
+      <c r="K957" s="3" t="n"/>
     </row>
     <row r="958">
       <c r="F958" t="inlineStr">
@@ -11040,6 +12005,7 @@
       <c r="H958" s="2" t="n"/>
       <c r="I958" s="3" t="n"/>
       <c r="J958" s="3" t="n"/>
+      <c r="K958" s="3" t="n"/>
     </row>
     <row r="959">
       <c r="F959" t="inlineStr">
@@ -11051,6 +12017,7 @@
       <c r="H959" s="2" t="n"/>
       <c r="I959" s="3" t="n"/>
       <c r="J959" s="3" t="n"/>
+      <c r="K959" s="3" t="n"/>
     </row>
     <row r="960">
       <c r="F960" t="inlineStr">
@@ -11062,6 +12029,7 @@
       <c r="H960" s="2" t="n"/>
       <c r="I960" s="3" t="n"/>
       <c r="J960" s="3" t="n"/>
+      <c r="K960" s="3" t="n"/>
     </row>
     <row r="961">
       <c r="F961" t="inlineStr">
@@ -11073,6 +12041,7 @@
       <c r="H961" s="2" t="n"/>
       <c r="I961" s="3" t="n"/>
       <c r="J961" s="3" t="n"/>
+      <c r="K961" s="3" t="n"/>
     </row>
     <row r="962">
       <c r="F962" t="inlineStr">
@@ -11084,6 +12053,7 @@
       <c r="H962" s="2" t="n"/>
       <c r="I962" s="3" t="n"/>
       <c r="J962" s="3" t="n"/>
+      <c r="K962" s="3" t="n"/>
     </row>
     <row r="963">
       <c r="F963" t="inlineStr">
@@ -11095,6 +12065,7 @@
       <c r="H963" s="2" t="n"/>
       <c r="I963" s="3" t="n"/>
       <c r="J963" s="3" t="n"/>
+      <c r="K963" s="3" t="n"/>
     </row>
     <row r="964">
       <c r="F964" t="inlineStr">
@@ -11106,6 +12077,7 @@
       <c r="H964" s="2" t="n"/>
       <c r="I964" s="3" t="n"/>
       <c r="J964" s="3" t="n"/>
+      <c r="K964" s="3" t="n"/>
     </row>
     <row r="965">
       <c r="F965" t="inlineStr">
@@ -11117,6 +12089,7 @@
       <c r="H965" s="2" t="n"/>
       <c r="I965" s="3" t="n"/>
       <c r="J965" s="3" t="n"/>
+      <c r="K965" s="3" t="n"/>
     </row>
     <row r="966">
       <c r="F966" t="inlineStr">
@@ -11128,6 +12101,7 @@
       <c r="H966" s="2" t="n"/>
       <c r="I966" s="3" t="n"/>
       <c r="J966" s="3" t="n"/>
+      <c r="K966" s="3" t="n"/>
     </row>
     <row r="967">
       <c r="F967" t="inlineStr">
@@ -11139,6 +12113,7 @@
       <c r="H967" s="2" t="n"/>
       <c r="I967" s="3" t="n"/>
       <c r="J967" s="3" t="n"/>
+      <c r="K967" s="3" t="n"/>
     </row>
     <row r="968">
       <c r="F968" t="inlineStr">
@@ -11150,6 +12125,7 @@
       <c r="H968" s="2" t="n"/>
       <c r="I968" s="3" t="n"/>
       <c r="J968" s="3" t="n"/>
+      <c r="K968" s="3" t="n"/>
     </row>
     <row r="969">
       <c r="F969" t="inlineStr">
@@ -11161,6 +12137,7 @@
       <c r="H969" s="2" t="n"/>
       <c r="I969" s="3" t="n"/>
       <c r="J969" s="3" t="n"/>
+      <c r="K969" s="3" t="n"/>
     </row>
     <row r="970">
       <c r="F970" t="inlineStr">
@@ -11172,6 +12149,7 @@
       <c r="H970" s="2" t="n"/>
       <c r="I970" s="3" t="n"/>
       <c r="J970" s="3" t="n"/>
+      <c r="K970" s="3" t="n"/>
     </row>
     <row r="971">
       <c r="F971" t="inlineStr">
@@ -11183,6 +12161,7 @@
       <c r="H971" s="2" t="n"/>
       <c r="I971" s="3" t="n"/>
       <c r="J971" s="3" t="n"/>
+      <c r="K971" s="3" t="n"/>
     </row>
     <row r="972">
       <c r="F972" t="inlineStr">
@@ -11194,6 +12173,7 @@
       <c r="H972" s="2" t="n"/>
       <c r="I972" s="3" t="n"/>
       <c r="J972" s="3" t="n"/>
+      <c r="K972" s="3" t="n"/>
     </row>
     <row r="973">
       <c r="F973" t="inlineStr">
@@ -11205,6 +12185,7 @@
       <c r="H973" s="2" t="n"/>
       <c r="I973" s="3" t="n"/>
       <c r="J973" s="3" t="n"/>
+      <c r="K973" s="3" t="n"/>
     </row>
     <row r="974">
       <c r="F974" t="inlineStr">
@@ -11216,6 +12197,7 @@
       <c r="H974" s="2" t="n"/>
       <c r="I974" s="3" t="n"/>
       <c r="J974" s="3" t="n"/>
+      <c r="K974" s="3" t="n"/>
     </row>
     <row r="975">
       <c r="F975" t="inlineStr">
@@ -11227,6 +12209,7 @@
       <c r="H975" s="2" t="n"/>
       <c r="I975" s="3" t="n"/>
       <c r="J975" s="3" t="n"/>
+      <c r="K975" s="3" t="n"/>
     </row>
     <row r="976">
       <c r="F976" t="inlineStr">
@@ -11238,6 +12221,7 @@
       <c r="H976" s="2" t="n"/>
       <c r="I976" s="3" t="n"/>
       <c r="J976" s="3" t="n"/>
+      <c r="K976" s="3" t="n"/>
     </row>
     <row r="977">
       <c r="F977" t="inlineStr">
@@ -11249,6 +12233,7 @@
       <c r="H977" s="2" t="n"/>
       <c r="I977" s="3" t="n"/>
       <c r="J977" s="3" t="n"/>
+      <c r="K977" s="3" t="n"/>
     </row>
     <row r="978">
       <c r="F978" t="inlineStr">
@@ -11260,6 +12245,7 @@
       <c r="H978" s="2" t="n"/>
       <c r="I978" s="3" t="n"/>
       <c r="J978" s="3" t="n"/>
+      <c r="K978" s="3" t="n"/>
     </row>
     <row r="979">
       <c r="F979" t="inlineStr">
@@ -11271,6 +12257,7 @@
       <c r="H979" s="2" t="n"/>
       <c r="I979" s="3" t="n"/>
       <c r="J979" s="3" t="n"/>
+      <c r="K979" s="3" t="n"/>
     </row>
     <row r="980">
       <c r="F980" t="inlineStr">
@@ -11282,6 +12269,7 @@
       <c r="H980" s="2" t="n"/>
       <c r="I980" s="3" t="n"/>
       <c r="J980" s="3" t="n"/>
+      <c r="K980" s="3" t="n"/>
     </row>
     <row r="981">
       <c r="F981" t="inlineStr">
@@ -11293,6 +12281,7 @@
       <c r="H981" s="2" t="n"/>
       <c r="I981" s="3" t="n"/>
       <c r="J981" s="3" t="n"/>
+      <c r="K981" s="3" t="n"/>
     </row>
     <row r="982">
       <c r="F982" t="inlineStr">
@@ -11304,6 +12293,7 @@
       <c r="H982" s="2" t="n"/>
       <c r="I982" s="3" t="n"/>
       <c r="J982" s="3" t="n"/>
+      <c r="K982" s="3" t="n"/>
     </row>
     <row r="983">
       <c r="F983" t="inlineStr">
@@ -11315,6 +12305,7 @@
       <c r="H983" s="2" t="n"/>
       <c r="I983" s="3" t="n"/>
       <c r="J983" s="3" t="n"/>
+      <c r="K983" s="3" t="n"/>
     </row>
     <row r="984">
       <c r="F984" t="inlineStr">
@@ -11326,6 +12317,7 @@
       <c r="H984" s="2" t="n"/>
       <c r="I984" s="3" t="n"/>
       <c r="J984" s="3" t="n"/>
+      <c r="K984" s="3" t="n"/>
     </row>
     <row r="985">
       <c r="F985" t="inlineStr">
@@ -11337,6 +12329,7 @@
       <c r="H985" s="2" t="n"/>
       <c r="I985" s="3" t="n"/>
       <c r="J985" s="3" t="n"/>
+      <c r="K985" s="3" t="n"/>
     </row>
     <row r="986">
       <c r="F986" t="inlineStr">
@@ -11348,6 +12341,7 @@
       <c r="H986" s="2" t="n"/>
       <c r="I986" s="3" t="n"/>
       <c r="J986" s="3" t="n"/>
+      <c r="K986" s="3" t="n"/>
     </row>
     <row r="987">
       <c r="F987" t="inlineStr">
@@ -11359,6 +12353,7 @@
       <c r="H987" s="2" t="n"/>
       <c r="I987" s="3" t="n"/>
       <c r="J987" s="3" t="n"/>
+      <c r="K987" s="3" t="n"/>
     </row>
     <row r="988">
       <c r="F988" t="inlineStr">
@@ -11370,6 +12365,7 @@
       <c r="H988" s="2" t="n"/>
       <c r="I988" s="3" t="n"/>
       <c r="J988" s="3" t="n"/>
+      <c r="K988" s="3" t="n"/>
     </row>
     <row r="989">
       <c r="F989" t="inlineStr">
@@ -11381,6 +12377,7 @@
       <c r="H989" s="2" t="n"/>
       <c r="I989" s="3" t="n"/>
       <c r="J989" s="3" t="n"/>
+      <c r="K989" s="3" t="n"/>
     </row>
     <row r="990">
       <c r="F990" t="inlineStr">
@@ -11392,6 +12389,7 @@
       <c r="H990" s="2" t="n"/>
       <c r="I990" s="3" t="n"/>
       <c r="J990" s="3" t="n"/>
+      <c r="K990" s="3" t="n"/>
     </row>
     <row r="991">
       <c r="F991" t="inlineStr">
@@ -11403,6 +12401,7 @@
       <c r="H991" s="2" t="n"/>
       <c r="I991" s="3" t="n"/>
       <c r="J991" s="3" t="n"/>
+      <c r="K991" s="3" t="n"/>
     </row>
     <row r="992">
       <c r="F992" t="inlineStr">
@@ -11414,6 +12413,7 @@
       <c r="H992" s="2" t="n"/>
       <c r="I992" s="3" t="n"/>
       <c r="J992" s="3" t="n"/>
+      <c r="K992" s="3" t="n"/>
     </row>
     <row r="993">
       <c r="F993" t="inlineStr">
@@ -11425,6 +12425,7 @@
       <c r="H993" s="2" t="n"/>
       <c r="I993" s="3" t="n"/>
       <c r="J993" s="3" t="n"/>
+      <c r="K993" s="3" t="n"/>
     </row>
     <row r="994">
       <c r="F994" t="inlineStr">
@@ -11436,6 +12437,7 @@
       <c r="H994" s="2" t="n"/>
       <c r="I994" s="3" t="n"/>
       <c r="J994" s="3" t="n"/>
+      <c r="K994" s="3" t="n"/>
     </row>
     <row r="995">
       <c r="F995" t="inlineStr">
@@ -11447,6 +12449,7 @@
       <c r="H995" s="2" t="n"/>
       <c r="I995" s="3" t="n"/>
       <c r="J995" s="3" t="n"/>
+      <c r="K995" s="3" t="n"/>
     </row>
     <row r="996">
       <c r="F996" t="inlineStr">
@@ -11458,6 +12461,7 @@
       <c r="H996" s="2" t="n"/>
       <c r="I996" s="3" t="n"/>
       <c r="J996" s="3" t="n"/>
+      <c r="K996" s="3" t="n"/>
     </row>
     <row r="997">
       <c r="F997" t="inlineStr">
@@ -11469,6 +12473,7 @@
       <c r="H997" s="2" t="n"/>
       <c r="I997" s="3" t="n"/>
       <c r="J997" s="3" t="n"/>
+      <c r="K997" s="3" t="n"/>
     </row>
     <row r="998">
       <c r="F998" t="inlineStr">
@@ -11480,6 +12485,7 @@
       <c r="H998" s="2" t="n"/>
       <c r="I998" s="3" t="n"/>
       <c r="J998" s="3" t="n"/>
+      <c r="K998" s="3" t="n"/>
     </row>
     <row r="999">
       <c r="F999" t="inlineStr">
@@ -11491,6 +12497,7 @@
       <c r="H999" s="2" t="n"/>
       <c r="I999" s="3" t="n"/>
       <c r="J999" s="3" t="n"/>
+      <c r="K999" s="3" t="n"/>
     </row>
     <row r="1000">
       <c r="F1000" t="inlineStr">
@@ -11502,6 +12509,7 @@
       <c r="H1000" s="2" t="n"/>
       <c r="I1000" s="3" t="n"/>
       <c r="J1000" s="3" t="n"/>
+      <c r="K1000" s="3" t="n"/>
     </row>
     <row r="1001">
       <c r="F1001" t="inlineStr">
@@ -11513,15 +12521,19 @@
       <c r="H1001" s="2" t="n"/>
       <c r="I1001" s="3" t="n"/>
       <c r="J1001" s="3" t="n"/>
+      <c r="K1001" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="G2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Ingresa un número igual o mayor a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unidad no válida" error="Selecciona una unidad de la lista." promptTitle="Unidad" prompt="Selecciona la unidad de medida del producto." type="list">
       <formula1>'Listas'!$A$2:$A$31</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tipo de afectación no válido" error="Selecciona una de las tres opciones de la lista." promptTitle="Tipo de afectación IGV" prompt="Selecciona el tipo de afectación IGV del producto." type="list">
+      <formula1>"Gravado - Operación onerosa,Exonerado - Operación onerosa,Inafecto - Operación onerosa"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11537,7 +12549,7 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -11548,7 +12560,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -11681,7 +12692,18 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tipo de afectación IGV</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Selecciona uno de estos nombres: Gravado - Operación onerosa; Exonerado - Operación onerosa; Inafecto - Operación onerosa. No escribas el código numérico en esta columna.</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
